--- a/INFORMAÇÕES_PROJETOS.xlsx
+++ b/INFORMAÇÕES_PROJETOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.furman\Desktop\Nova pasta (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HomePC\.gemini\antigravity-ide\scratch\analise-dre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782E7558-CABD-480E-90D8-72A78A3C6E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FB826C-3122-4368-9A26-D94C0D47D88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="706" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="706" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="10" state="hidden" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Custo Obras'!$A$1:$L$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prazo Obras'!$A$1:$V$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prazo Obras'!$A$1:$S$21</definedName>
     <definedName name="Estratégias">'[1]Estratégias (legenda)'!$A$2:$A$5</definedName>
     <definedName name="EstrategiasOport">'[1]Estratégias (legenda)'!$D$2:$D$5</definedName>
   </definedNames>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="98">
   <si>
     <t>Data</t>
   </si>
@@ -77,28 +77,13 @@
     <t>Término prev. (BASE)</t>
   </si>
   <si>
-    <t>Término prev. (REPLAN.)</t>
-  </si>
-  <si>
-    <t>Término real (CVCO)</t>
-  </si>
-  <si>
-    <t>Mês atraso</t>
-  </si>
-  <si>
     <t>Contrato</t>
   </si>
   <si>
     <t>Multa Contrato (%)</t>
   </si>
   <si>
-    <t>Valor Contrato</t>
-  </si>
-  <si>
     <t>Valor Multa (R$)</t>
-  </si>
-  <si>
-    <t>Multa (%)</t>
   </si>
   <si>
     <t>Varanda</t>
@@ -200,9 +185,6 @@
     <t>Obra e tipo</t>
   </si>
   <si>
-    <t>Término real</t>
-  </si>
-  <si>
     <t>Valor Contrato corrigido</t>
   </si>
   <si>
@@ -218,30 +200,15 @@
     <t>Mês inicial</t>
   </si>
   <si>
-    <t>Mês contrato</t>
-  </si>
-  <si>
     <t>% Receita liquida geral</t>
   </si>
   <si>
-    <t>Recebimento da assistência técnica</t>
-  </si>
-  <si>
     <t>Pagamento Multa</t>
   </si>
   <si>
-    <t>Meses inicial x CVCO</t>
-  </si>
-  <si>
     <t>Premio economia</t>
   </si>
   <si>
-    <t>Mês real (previsto + atraso)</t>
-  </si>
-  <si>
-    <t>Dias de chuva contabilizados no período</t>
-  </si>
-  <si>
     <t>Terceiros</t>
   </si>
   <si>
@@ -251,18 +218,12 @@
     <t>Interna</t>
   </si>
   <si>
-    <t>Entrega Cliente</t>
-  </si>
-  <si>
     <t>Inicio (BASE)</t>
   </si>
   <si>
     <t>Miragio</t>
   </si>
   <si>
-    <t>31/04/2025</t>
-  </si>
-  <si>
     <t>Orçamento total reajustado</t>
   </si>
   <si>
@@ -303,6 +264,84 @@
   </si>
   <si>
     <t>Clausula custo</t>
+  </si>
+  <si>
+    <t>Dias de chuva&gt;5mm</t>
+  </si>
+  <si>
+    <t>MÊS CVCO</t>
+  </si>
+  <si>
+    <t>MÊS ENTREGA UNIDADES</t>
+  </si>
+  <si>
+    <t>Custo equipe mensal</t>
+  </si>
+  <si>
+    <t>Hall Design</t>
+  </si>
+  <si>
+    <t>Pace</t>
+  </si>
+  <si>
+    <t>Platea - 108</t>
+  </si>
+  <si>
+    <t>Grand Lodge Batel - Partilha</t>
+  </si>
+  <si>
+    <t>Icaro F1 - AG7</t>
+  </si>
+  <si>
+    <t>Sem clausula de atraso</t>
+  </si>
+  <si>
+    <t>TérminoCVCO</t>
+  </si>
+  <si>
+    <t>Entrega cliente</t>
+  </si>
+  <si>
+    <t>Não finalizada</t>
+  </si>
+  <si>
+    <t>Multa possível (%)</t>
+  </si>
+  <si>
+    <t>Prazo orçamento</t>
+  </si>
+  <si>
+    <t>34/39</t>
+  </si>
+  <si>
+    <t>30/33</t>
+  </si>
+  <si>
+    <t>36/44</t>
+  </si>
+  <si>
+    <t>40/45</t>
+  </si>
+  <si>
+    <t>08/10</t>
+  </si>
+  <si>
+    <t>42/45</t>
+  </si>
+  <si>
+    <t>27/30</t>
+  </si>
+  <si>
+    <t>Contrato não encontrado</t>
+  </si>
+  <si>
+    <t>"19.1. Multa por atraso: 1% (um por cento) ao mês do Valor Global de Referência por dia de atraso no prazo de Conclusão da Obra, calculado proporcionalmente aos dias de atraso, limitada a 5% (cinco por cento) do Valor Global de Referência."</t>
+  </si>
+  <si>
+    <t>"Ressalvados os casos fortuitos ou de força maior, a parte que descumprir qualquer cláusula  ou condição estabelecida no presente contrato, ou que venha a dar causa à sua rescisão, ficará obrigada ao pagamento de multa punitiva não compensatória equivalente a 2% (dois por cento) do  valor total do contrato."</t>
+  </si>
+  <si>
+    <t>Custo orçamento</t>
   </si>
 </sst>
 </file>
@@ -313,9 +352,9 @@
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.000%"/>
-    <numFmt numFmtId="166" formatCode="[$-416]mmm\-yy;@"/>
-    <numFmt numFmtId="168" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="[$-416]mmm\-yy;@"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -388,7 +427,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -486,38 +525,8 @@
       <left style="dotted">
         <color theme="0" tint="-0.34998626667073579"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="dotted">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom style="dotted">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </left>
       <right style="dotted">
         <color theme="0" tint="-0.34998626667073579"/>
-      </right>
-      <top style="dotted">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
       </right>
       <top style="dotted">
         <color theme="0" tint="-0.34998626667073579"/>
@@ -587,19 +596,6 @@
       </top>
       <bottom style="medium">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="dotted">
-        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
@@ -722,6 +718,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -732,7 +739,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -752,10 +759,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -779,170 +783,131 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -966,8 +931,32 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1360,17 +1349,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BCC6A2B-3058-4004-816D-7182CED8014F}">
   <dimension ref="A1:I134"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1380,24 +1369,24 @@
       <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="33" t="s">
-        <v>48</v>
+      <c r="D1" s="25" t="s">
+        <v>43</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
       </c>
       <c r="F1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="35">
+        <v>46</v>
+      </c>
+      <c r="C2" s="27">
         <v>45170</v>
       </c>
       <c r="D2">
@@ -1411,14 +1400,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="35">
+        <v>46</v>
+      </c>
+      <c r="C3" s="27">
         <v>45200</v>
       </c>
       <c r="D3">
@@ -1432,14 +1421,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="35">
+        <v>46</v>
+      </c>
+      <c r="C4" s="27">
         <v>45231</v>
       </c>
       <c r="D4">
@@ -1453,14 +1442,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="35">
+        <v>46</v>
+      </c>
+      <c r="C5" s="27">
         <v>45261</v>
       </c>
       <c r="D5">
@@ -1474,14 +1463,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="35">
+        <v>46</v>
+      </c>
+      <c r="C6" s="27">
         <v>45292</v>
       </c>
       <c r="D6">
@@ -1495,14 +1484,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="35">
+        <v>46</v>
+      </c>
+      <c r="C7" s="27">
         <v>45323</v>
       </c>
       <c r="D7">
@@ -1516,14 +1505,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="35">
+        <v>46</v>
+      </c>
+      <c r="C8" s="27">
         <v>45352</v>
       </c>
       <c r="D8">
@@ -1537,14 +1526,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="35">
+        <v>46</v>
+      </c>
+      <c r="C9" s="27">
         <v>45383</v>
       </c>
       <c r="D9">
@@ -1558,14 +1547,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="35">
+        <v>46</v>
+      </c>
+      <c r="C10" s="27">
         <v>45413</v>
       </c>
       <c r="D10">
@@ -1579,14 +1568,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="35">
+        <v>46</v>
+      </c>
+      <c r="C11" s="27">
         <v>45444</v>
       </c>
       <c r="D11">
@@ -1600,14 +1589,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="35">
+        <v>46</v>
+      </c>
+      <c r="C12" s="27">
         <v>45474</v>
       </c>
       <c r="D12">
@@ -1621,14 +1610,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="35">
+        <v>46</v>
+      </c>
+      <c r="C13" s="27">
         <v>45505</v>
       </c>
       <c r="D13">
@@ -1642,14 +1631,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="35">
+        <v>46</v>
+      </c>
+      <c r="C14" s="27">
         <v>45536</v>
       </c>
       <c r="D14">
@@ -1663,14 +1652,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="35">
+        <v>46</v>
+      </c>
+      <c r="C15" s="27">
         <v>45566</v>
       </c>
       <c r="D15">
@@ -1684,14 +1673,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="35">
+        <v>46</v>
+      </c>
+      <c r="C16" s="27">
         <v>45597</v>
       </c>
       <c r="D16">
@@ -1705,14 +1694,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="35">
+        <v>46</v>
+      </c>
+      <c r="C17" s="27">
         <v>45627</v>
       </c>
       <c r="D17">
@@ -1726,14 +1715,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="35">
+        <v>46</v>
+      </c>
+      <c r="C18" s="27">
         <v>45658</v>
       </c>
       <c r="D18">
@@ -1747,14 +1736,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="35">
+        <v>46</v>
+      </c>
+      <c r="C19" s="27">
         <v>45689</v>
       </c>
       <c r="D19">
@@ -1768,14 +1757,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="35">
+        <v>46</v>
+      </c>
+      <c r="C20" s="27">
         <v>45717</v>
       </c>
       <c r="D20">
@@ -1789,14 +1778,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="35">
+        <v>46</v>
+      </c>
+      <c r="C21" s="27">
         <v>45748</v>
       </c>
       <c r="D21">
@@ -1810,14 +1799,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="35">
+        <v>46</v>
+      </c>
+      <c r="C22" s="27">
         <v>45778</v>
       </c>
       <c r="D22">
@@ -1831,14 +1820,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="35">
+        <v>46</v>
+      </c>
+      <c r="C23" s="27">
         <v>45809</v>
       </c>
       <c r="D23">
@@ -1852,14 +1841,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="35">
+        <v>46</v>
+      </c>
+      <c r="C24" s="27">
         <v>45839</v>
       </c>
       <c r="D24">
@@ -1873,14 +1862,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="35">
+        <v>46</v>
+      </c>
+      <c r="C25" s="27">
         <v>45870</v>
       </c>
       <c r="D25">
@@ -1894,14 +1883,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="35">
+        <v>46</v>
+      </c>
+      <c r="C26" s="27">
         <f>EDATE(C25,1)</f>
         <v>45901</v>
       </c>
@@ -1913,14 +1902,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="35">
+        <v>46</v>
+      </c>
+      <c r="C27" s="27">
         <f t="shared" ref="C27:C29" si="1">EDATE(C26,1)</f>
         <v>45931</v>
       </c>
@@ -1932,14 +1921,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="35">
+        <v>46</v>
+      </c>
+      <c r="C28" s="27">
         <f t="shared" si="1"/>
         <v>45962</v>
       </c>
@@ -1951,14 +1940,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="35">
+        <v>46</v>
+      </c>
+      <c r="C29" s="27">
         <f t="shared" si="1"/>
         <v>45992</v>
       </c>
@@ -1970,14 +1959,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="35">
+        <v>46</v>
+      </c>
+      <c r="C30" s="27">
         <f t="shared" ref="C30:C33" si="2">EDATE(C29,1)</f>
         <v>46023</v>
       </c>
@@ -1989,14 +1978,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="35">
+        <v>46</v>
+      </c>
+      <c r="C31" s="27">
         <f t="shared" si="2"/>
         <v>46054</v>
       </c>
@@ -2008,14 +1997,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="35">
+        <v>46</v>
+      </c>
+      <c r="C32" s="27">
         <f t="shared" si="2"/>
         <v>46082</v>
       </c>
@@ -2027,14 +2016,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="35">
+        <v>46</v>
+      </c>
+      <c r="C33" s="27">
         <f t="shared" si="2"/>
         <v>46113</v>
       </c>
@@ -2046,14 +2035,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="35">
+        <v>47</v>
+      </c>
+      <c r="C35" s="27">
         <v>45170</v>
       </c>
       <c r="D35">
@@ -2067,14 +2056,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="35">
+        <v>47</v>
+      </c>
+      <c r="C36" s="27">
         <v>45200</v>
       </c>
       <c r="D36">
@@ -2088,14 +2077,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="35">
+        <v>47</v>
+      </c>
+      <c r="C37" s="27">
         <v>45231</v>
       </c>
       <c r="D37">
@@ -2109,14 +2098,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="35">
+        <v>47</v>
+      </c>
+      <c r="C38" s="27">
         <v>45261</v>
       </c>
       <c r="D38">
@@ -2130,14 +2119,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="35">
+        <v>47</v>
+      </c>
+      <c r="C39" s="27">
         <v>45292</v>
       </c>
       <c r="D39">
@@ -2151,14 +2140,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" s="35">
+        <v>47</v>
+      </c>
+      <c r="C40" s="27">
         <v>45323</v>
       </c>
       <c r="D40">
@@ -2172,14 +2161,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" s="35">
+        <v>47</v>
+      </c>
+      <c r="C41" s="27">
         <v>45352</v>
       </c>
       <c r="D41">
@@ -2193,14 +2182,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="35">
+        <v>47</v>
+      </c>
+      <c r="C42" s="27">
         <v>45383</v>
       </c>
       <c r="D42">
@@ -2214,14 +2203,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="35">
+        <v>47</v>
+      </c>
+      <c r="C43" s="27">
         <v>45413</v>
       </c>
       <c r="D43">
@@ -2235,14 +2224,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="35">
+        <v>47</v>
+      </c>
+      <c r="C44" s="27">
         <v>45444</v>
       </c>
       <c r="D44">
@@ -2256,14 +2245,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="35">
+        <v>47</v>
+      </c>
+      <c r="C45" s="27">
         <v>45474</v>
       </c>
       <c r="D45">
@@ -2277,14 +2266,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="35">
+        <v>47</v>
+      </c>
+      <c r="C46" s="27">
         <v>45505</v>
       </c>
       <c r="D46">
@@ -2298,14 +2287,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" s="35">
+        <v>47</v>
+      </c>
+      <c r="C47" s="27">
         <v>45536</v>
       </c>
       <c r="D47">
@@ -2319,14 +2308,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
-      </c>
-      <c r="C48" s="35">
+        <v>47</v>
+      </c>
+      <c r="C48" s="27">
         <v>45566</v>
       </c>
       <c r="D48">
@@ -2340,14 +2329,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="35">
+        <v>47</v>
+      </c>
+      <c r="C49" s="27">
         <v>45597</v>
       </c>
       <c r="D49">
@@ -2361,14 +2350,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="35">
+        <v>47</v>
+      </c>
+      <c r="C50" s="27">
         <v>45627</v>
       </c>
       <c r="D50">
@@ -2382,14 +2371,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51" s="35">
+        <v>47</v>
+      </c>
+      <c r="C51" s="27">
         <v>45658</v>
       </c>
       <c r="D51">
@@ -2403,14 +2392,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="35">
+        <v>47</v>
+      </c>
+      <c r="C52" s="27">
         <v>45689</v>
       </c>
       <c r="D52">
@@ -2424,14 +2413,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>4</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" s="35">
+        <v>47</v>
+      </c>
+      <c r="C53" s="27">
         <v>45717</v>
       </c>
       <c r="D53">
@@ -2445,14 +2434,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>4</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
-      </c>
-      <c r="C54" s="35">
+        <v>47</v>
+      </c>
+      <c r="C54" s="27">
         <v>45748</v>
       </c>
       <c r="D54">
@@ -2466,14 +2455,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="35">
+        <v>47</v>
+      </c>
+      <c r="C55" s="27">
         <v>45778</v>
       </c>
       <c r="D55">
@@ -2487,14 +2476,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>4</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
-      </c>
-      <c r="C56" s="35">
+        <v>47</v>
+      </c>
+      <c r="C56" s="27">
         <v>45809</v>
       </c>
       <c r="D56">
@@ -2508,14 +2497,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
-      </c>
-      <c r="C57" s="35">
+        <v>47</v>
+      </c>
+      <c r="C57" s="27">
         <v>45839</v>
       </c>
       <c r="D57">
@@ -2529,14 +2518,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
-      </c>
-      <c r="C58" s="35">
+        <v>47</v>
+      </c>
+      <c r="C58" s="27">
         <v>45870</v>
       </c>
       <c r="D58">
@@ -2550,14 +2539,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>53</v>
-      </c>
-      <c r="C59" s="35">
+        <v>47</v>
+      </c>
+      <c r="C59" s="27">
         <f>EDATE(C58,1)</f>
         <v>45901</v>
       </c>
@@ -2569,14 +2558,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
-      </c>
-      <c r="C60" s="35">
+        <v>47</v>
+      </c>
+      <c r="C60" s="27">
         <f t="shared" ref="C60:C66" si="4">EDATE(C59,1)</f>
         <v>45931</v>
       </c>
@@ -2588,14 +2577,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
-      </c>
-      <c r="C61" s="35">
+        <v>47</v>
+      </c>
+      <c r="C61" s="27">
         <f t="shared" si="4"/>
         <v>45962</v>
       </c>
@@ -2607,14 +2596,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>4</v>
       </c>
       <c r="B62" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" s="35">
+        <v>47</v>
+      </c>
+      <c r="C62" s="27">
         <f t="shared" si="4"/>
         <v>45992</v>
       </c>
@@ -2626,14 +2615,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
-      </c>
-      <c r="C63" s="35">
+        <v>47</v>
+      </c>
+      <c r="C63" s="27">
         <f t="shared" si="4"/>
         <v>46023</v>
       </c>
@@ -2645,14 +2634,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>53</v>
-      </c>
-      <c r="C64" s="35">
+        <v>47</v>
+      </c>
+      <c r="C64" s="27">
         <f t="shared" si="4"/>
         <v>46054</v>
       </c>
@@ -2664,14 +2653,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>53</v>
-      </c>
-      <c r="C65" s="35">
+        <v>47</v>
+      </c>
+      <c r="C65" s="27">
         <f t="shared" si="4"/>
         <v>46082</v>
       </c>
@@ -2683,14 +2672,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>53</v>
-      </c>
-      <c r="C66" s="35">
+        <v>47</v>
+      </c>
+      <c r="C66" s="27">
         <f t="shared" si="4"/>
         <v>46113</v>
       </c>
@@ -2702,14 +2691,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>54</v>
-      </c>
-      <c r="C69" s="35">
+        <v>48</v>
+      </c>
+      <c r="C69" s="27">
         <v>45170</v>
       </c>
       <c r="E69" t="s">
@@ -2719,25 +2708,25 @@
         <f>A69&amp;" "&amp;B69</f>
         <v>HALL DESIGN Despesas ADM</v>
       </c>
-      <c r="G69" s="37">
+      <c r="G69" s="29">
         <v>58347.72</v>
       </c>
       <c r="H69">
         <v>2246195.4800000004</v>
       </c>
-      <c r="I69" s="38">
+      <c r="I69" s="30">
         <f>G69/H69</f>
         <v>2.5976243171854298E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>54</v>
-      </c>
-      <c r="C70" s="35">
+        <v>48</v>
+      </c>
+      <c r="C70" s="27">
         <v>45200</v>
       </c>
       <c r="E70" t="s">
@@ -2747,25 +2736,25 @@
         <f t="shared" ref="F70:F100" si="5">A70&amp;" "&amp;B70</f>
         <v>HALL DESIGN Despesas ADM</v>
       </c>
-      <c r="G70" s="37">
+      <c r="G70" s="29">
         <v>96382.45</v>
       </c>
       <c r="H70">
         <v>2166431.41</v>
       </c>
-      <c r="I70" s="38">
+      <c r="I70" s="30">
         <f t="shared" ref="I70:I73" si="6">G70/H70</f>
         <v>4.4489038312087614E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>54</v>
-      </c>
-      <c r="C71" s="35">
+        <v>48</v>
+      </c>
+      <c r="C71" s="27">
         <v>45231</v>
       </c>
       <c r="E71" t="s">
@@ -2775,25 +2764,25 @@
         <f t="shared" si="5"/>
         <v>HALL DESIGN Despesas ADM</v>
       </c>
-      <c r="G71" s="37">
+      <c r="G71" s="29">
         <v>96730.39</v>
       </c>
       <c r="H71">
         <v>1954414.9099999997</v>
       </c>
-      <c r="I71" s="38">
+      <c r="I71" s="30">
         <f t="shared" si="6"/>
         <v>4.9493272643934147E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>54</v>
-      </c>
-      <c r="C72" s="35">
+        <v>48</v>
+      </c>
+      <c r="C72" s="27">
         <v>45261</v>
       </c>
       <c r="E72" t="s">
@@ -2803,28 +2792,28 @@
         <f t="shared" si="5"/>
         <v>HALL DESIGN Despesas ADM</v>
       </c>
-      <c r="G72" s="37">
+      <c r="G72" s="29">
         <v>97200.11</v>
       </c>
       <c r="H72">
         <v>1979082.44</v>
       </c>
-      <c r="I72" s="38">
+      <c r="I72" s="30">
         <f t="shared" si="6"/>
         <v>4.9113724641000805E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
-      </c>
-      <c r="C73" s="35">
+        <v>48</v>
+      </c>
+      <c r="C73" s="27">
         <v>45292</v>
       </c>
-      <c r="D73" s="34">
+      <c r="D73" s="26">
         <v>2.5976243171854298E-2</v>
       </c>
       <c r="E73" t="s">
@@ -2834,28 +2823,28 @@
         <f t="shared" si="5"/>
         <v>HALL DESIGN Despesas ADM</v>
       </c>
-      <c r="G73" s="37">
+      <c r="G73" s="29">
         <v>138632.12</v>
       </c>
       <c r="H73">
         <v>2179211.41</v>
       </c>
-      <c r="I73" s="38">
+      <c r="I73" s="30">
         <f t="shared" si="6"/>
         <v>6.3615727856344131E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>54</v>
-      </c>
-      <c r="C74" s="35">
+        <v>48</v>
+      </c>
+      <c r="C74" s="27">
         <v>45323</v>
       </c>
-      <c r="D74" s="34">
+      <c r="D74" s="26">
         <v>4.4489038312087614E-2</v>
       </c>
       <c r="E74" t="s">
@@ -2866,17 +2855,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>54</v>
-      </c>
-      <c r="C75" s="35">
+        <v>48</v>
+      </c>
+      <c r="C75" s="27">
         <v>45352</v>
       </c>
-      <c r="D75" s="34">
+      <c r="D75" s="26">
         <v>4.9493272643934147E-2</v>
       </c>
       <c r="E75" t="s">
@@ -2887,17 +2876,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>4</v>
       </c>
       <c r="B76" t="s">
-        <v>54</v>
-      </c>
-      <c r="C76" s="35">
+        <v>48</v>
+      </c>
+      <c r="C76" s="27">
         <v>45383</v>
       </c>
-      <c r="D76" s="34">
+      <c r="D76" s="26">
         <v>4.9113724641000805E-2</v>
       </c>
       <c r="E76" t="s">
@@ -2908,17 +2897,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>4</v>
       </c>
       <c r="B77" t="s">
-        <v>54</v>
-      </c>
-      <c r="C77" s="35">
+        <v>48</v>
+      </c>
+      <c r="C77" s="27">
         <v>45413</v>
       </c>
-      <c r="D77" s="34">
+      <c r="D77" s="26">
         <v>6.3615727856344131E-2</v>
       </c>
       <c r="E77" t="s">
@@ -2929,17 +2918,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>4</v>
       </c>
       <c r="B78" t="s">
-        <v>54</v>
-      </c>
-      <c r="C78" s="35">
+        <v>48</v>
+      </c>
+      <c r="C78" s="27">
         <v>45444</v>
       </c>
-      <c r="D78" s="36"/>
+      <c r="D78" s="28"/>
       <c r="E78" t="s">
         <v>1</v>
       </c>
@@ -2948,17 +2937,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>4</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
-      </c>
-      <c r="C79" s="35">
+        <v>48</v>
+      </c>
+      <c r="C79" s="27">
         <v>45474</v>
       </c>
-      <c r="D79" s="36"/>
+      <c r="D79" s="28"/>
       <c r="E79" t="s">
         <v>1</v>
       </c>
@@ -2967,17 +2956,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
-      </c>
-      <c r="C80" s="35">
+        <v>48</v>
+      </c>
+      <c r="C80" s="27">
         <v>45505</v>
       </c>
-      <c r="D80" s="36"/>
+      <c r="D80" s="28"/>
       <c r="E80" t="s">
         <v>1</v>
       </c>
@@ -2986,17 +2975,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>4</v>
       </c>
       <c r="B81" t="s">
-        <v>54</v>
-      </c>
-      <c r="C81" s="35">
+        <v>48</v>
+      </c>
+      <c r="C81" s="27">
         <v>45536</v>
       </c>
-      <c r="D81" s="36"/>
+      <c r="D81" s="28"/>
       <c r="E81" t="s">
         <v>1</v>
       </c>
@@ -3005,17 +2994,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>4</v>
       </c>
       <c r="B82" t="s">
-        <v>54</v>
-      </c>
-      <c r="C82" s="35">
+        <v>48</v>
+      </c>
+      <c r="C82" s="27">
         <v>45566</v>
       </c>
-      <c r="D82" s="36"/>
+      <c r="D82" s="28"/>
       <c r="E82" t="s">
         <v>1</v>
       </c>
@@ -3024,17 +3013,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>4</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
-      </c>
-      <c r="C83" s="35">
+        <v>48</v>
+      </c>
+      <c r="C83" s="27">
         <v>45597</v>
       </c>
-      <c r="D83" s="36"/>
+      <c r="D83" s="28"/>
       <c r="E83" t="s">
         <v>1</v>
       </c>
@@ -3043,17 +3032,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>4</v>
       </c>
       <c r="B84" t="s">
-        <v>54</v>
-      </c>
-      <c r="C84" s="35">
+        <v>48</v>
+      </c>
+      <c r="C84" s="27">
         <v>45627</v>
       </c>
-      <c r="D84" s="36"/>
+      <c r="D84" s="28"/>
       <c r="E84" t="s">
         <v>1</v>
       </c>
@@ -3062,17 +3051,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>54</v>
-      </c>
-      <c r="C85" s="35">
+        <v>48</v>
+      </c>
+      <c r="C85" s="27">
         <v>45658</v>
       </c>
-      <c r="D85" s="36"/>
+      <c r="D85" s="28"/>
       <c r="E85" t="s">
         <v>1</v>
       </c>
@@ -3081,17 +3070,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>4</v>
       </c>
       <c r="B86" t="s">
-        <v>54</v>
-      </c>
-      <c r="C86" s="35">
+        <v>48</v>
+      </c>
+      <c r="C86" s="27">
         <v>45689</v>
       </c>
-      <c r="D86" s="36"/>
+      <c r="D86" s="28"/>
       <c r="E86" t="s">
         <v>1</v>
       </c>
@@ -3100,17 +3089,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>54</v>
-      </c>
-      <c r="C87" s="35">
+        <v>48</v>
+      </c>
+      <c r="C87" s="27">
         <v>45717</v>
       </c>
-      <c r="D87" s="36"/>
+      <c r="D87" s="28"/>
       <c r="E87" t="s">
         <v>1</v>
       </c>
@@ -3119,17 +3108,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>4</v>
       </c>
       <c r="B88" t="s">
-        <v>54</v>
-      </c>
-      <c r="C88" s="35">
+        <v>48</v>
+      </c>
+      <c r="C88" s="27">
         <v>45748</v>
       </c>
-      <c r="D88" s="36"/>
+      <c r="D88" s="28"/>
       <c r="E88" t="s">
         <v>1</v>
       </c>
@@ -3138,17 +3127,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>54</v>
-      </c>
-      <c r="C89" s="35">
+        <v>48</v>
+      </c>
+      <c r="C89" s="27">
         <v>45778</v>
       </c>
-      <c r="D89" s="36"/>
+      <c r="D89" s="28"/>
       <c r="E89" t="s">
         <v>1</v>
       </c>
@@ -3157,17 +3146,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>54</v>
-      </c>
-      <c r="C90" s="35">
+        <v>48</v>
+      </c>
+      <c r="C90" s="27">
         <v>45809</v>
       </c>
-      <c r="D90" s="36"/>
+      <c r="D90" s="28"/>
       <c r="E90" t="s">
         <v>1</v>
       </c>
@@ -3176,17 +3165,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>54</v>
-      </c>
-      <c r="C91" s="35">
+        <v>48</v>
+      </c>
+      <c r="C91" s="27">
         <v>45839</v>
       </c>
-      <c r="D91" s="36"/>
+      <c r="D91" s="28"/>
       <c r="E91" t="s">
         <v>1</v>
       </c>
@@ -3195,17 +3184,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>54</v>
-      </c>
-      <c r="C92" s="35">
+        <v>48</v>
+      </c>
+      <c r="C92" s="27">
         <v>45870</v>
       </c>
-      <c r="D92" s="36"/>
+      <c r="D92" s="28"/>
       <c r="E92" t="s">
         <v>1</v>
       </c>
@@ -3214,18 +3203,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>4</v>
       </c>
       <c r="B93" t="s">
-        <v>54</v>
-      </c>
-      <c r="C93" s="35">
+        <v>48</v>
+      </c>
+      <c r="C93" s="27">
         <f>EDATE(C92,1)</f>
         <v>45901</v>
       </c>
-      <c r="D93" s="36"/>
+      <c r="D93" s="28"/>
       <c r="E93" t="s">
         <v>1</v>
       </c>
@@ -3234,18 +3223,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>4</v>
       </c>
       <c r="B94" t="s">
-        <v>54</v>
-      </c>
-      <c r="C94" s="35">
+        <v>48</v>
+      </c>
+      <c r="C94" s="27">
         <f t="shared" ref="C94:C100" si="7">EDATE(C93,1)</f>
         <v>45931</v>
       </c>
-      <c r="D94" s="36"/>
+      <c r="D94" s="28"/>
       <c r="E94" t="s">
         <v>1</v>
       </c>
@@ -3254,18 +3243,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>4</v>
       </c>
       <c r="B95" t="s">
-        <v>54</v>
-      </c>
-      <c r="C95" s="35">
+        <v>48</v>
+      </c>
+      <c r="C95" s="27">
         <f t="shared" si="7"/>
         <v>45962</v>
       </c>
-      <c r="D95" s="36"/>
+      <c r="D95" s="28"/>
       <c r="E95" t="s">
         <v>1</v>
       </c>
@@ -3274,18 +3263,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>4</v>
       </c>
       <c r="B96" t="s">
-        <v>54</v>
-      </c>
-      <c r="C96" s="35">
+        <v>48</v>
+      </c>
+      <c r="C96" s="27">
         <f t="shared" si="7"/>
         <v>45992</v>
       </c>
-      <c r="D96" s="36"/>
+      <c r="D96" s="28"/>
       <c r="E96" t="s">
         <v>1</v>
       </c>
@@ -3294,18 +3283,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>4</v>
       </c>
       <c r="B97" t="s">
-        <v>54</v>
-      </c>
-      <c r="C97" s="35">
+        <v>48</v>
+      </c>
+      <c r="C97" s="27">
         <f t="shared" si="7"/>
         <v>46023</v>
       </c>
-      <c r="D97" s="36"/>
+      <c r="D97" s="28"/>
       <c r="E97" t="s">
         <v>1</v>
       </c>
@@ -3314,18 +3303,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>4</v>
       </c>
       <c r="B98" t="s">
-        <v>54</v>
-      </c>
-      <c r="C98" s="35">
+        <v>48</v>
+      </c>
+      <c r="C98" s="27">
         <f t="shared" si="7"/>
         <v>46054</v>
       </c>
-      <c r="D98" s="36"/>
+      <c r="D98" s="28"/>
       <c r="E98" t="s">
         <v>1</v>
       </c>
@@ -3334,18 +3323,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>4</v>
       </c>
       <c r="B99" t="s">
-        <v>54</v>
-      </c>
-      <c r="C99" s="35">
+        <v>48</v>
+      </c>
+      <c r="C99" s="27">
         <f t="shared" si="7"/>
         <v>46082</v>
       </c>
-      <c r="D99" s="36"/>
+      <c r="D99" s="28"/>
       <c r="E99" t="s">
         <v>1</v>
       </c>
@@ -3354,18 +3343,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>4</v>
       </c>
       <c r="B100" t="s">
-        <v>54</v>
-      </c>
-      <c r="C100" s="35">
+        <v>48</v>
+      </c>
+      <c r="C100" s="27">
         <f t="shared" si="7"/>
         <v>46113</v>
       </c>
-      <c r="D100" s="36"/>
+      <c r="D100" s="28"/>
       <c r="E100" t="s">
         <v>1</v>
       </c>
@@ -3374,18 +3363,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>4</v>
       </c>
       <c r="B103" t="s">
-        <v>57</v>
-      </c>
-      <c r="C103" s="35">
+        <v>50</v>
+      </c>
+      <c r="C103" s="27">
         <v>45170</v>
       </c>
-      <c r="D103" s="36"/>
+      <c r="D103" s="28"/>
       <c r="E103" t="s">
         <v>8</v>
       </c>
@@ -3394,17 +3383,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>4</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
-      </c>
-      <c r="C104" s="35">
+        <v>50</v>
+      </c>
+      <c r="C104" s="27">
         <v>45200</v>
       </c>
-      <c r="D104" s="36"/>
+      <c r="D104" s="28"/>
       <c r="E104" t="s">
         <v>8</v>
       </c>
@@ -3413,17 +3402,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>4</v>
       </c>
       <c r="B105" t="s">
-        <v>57</v>
-      </c>
-      <c r="C105" s="35">
+        <v>50</v>
+      </c>
+      <c r="C105" s="27">
         <v>45231</v>
       </c>
-      <c r="D105" s="36"/>
+      <c r="D105" s="28"/>
       <c r="E105" t="s">
         <v>8</v>
       </c>
@@ -3432,17 +3421,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>4</v>
       </c>
       <c r="B106" t="s">
-        <v>57</v>
-      </c>
-      <c r="C106" s="35">
+        <v>50</v>
+      </c>
+      <c r="C106" s="27">
         <v>45261</v>
       </c>
-      <c r="D106" s="36"/>
+      <c r="D106" s="28"/>
       <c r="E106" t="s">
         <v>8</v>
       </c>
@@ -3451,17 +3440,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>4</v>
       </c>
       <c r="B107" t="s">
-        <v>57</v>
-      </c>
-      <c r="C107" s="35">
+        <v>50</v>
+      </c>
+      <c r="C107" s="27">
         <v>45292</v>
       </c>
-      <c r="D107" s="36"/>
+      <c r="D107" s="28"/>
       <c r="E107" t="s">
         <v>8</v>
       </c>
@@ -3470,17 +3459,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>4</v>
       </c>
       <c r="B108" t="s">
-        <v>57</v>
-      </c>
-      <c r="C108" s="35">
+        <v>50</v>
+      </c>
+      <c r="C108" s="27">
         <v>45323</v>
       </c>
-      <c r="D108" s="36"/>
+      <c r="D108" s="28"/>
       <c r="E108" t="s">
         <v>8</v>
       </c>
@@ -3489,17 +3478,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>4</v>
       </c>
       <c r="B109" t="s">
-        <v>57</v>
-      </c>
-      <c r="C109" s="35">
+        <v>50</v>
+      </c>
+      <c r="C109" s="27">
         <v>45352</v>
       </c>
-      <c r="D109" s="36"/>
+      <c r="D109" s="28"/>
       <c r="E109" t="s">
         <v>8</v>
       </c>
@@ -3508,17 +3497,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>4</v>
       </c>
       <c r="B110" t="s">
-        <v>57</v>
-      </c>
-      <c r="C110" s="35">
+        <v>50</v>
+      </c>
+      <c r="C110" s="27">
         <v>45383</v>
       </c>
-      <c r="D110" s="36"/>
+      <c r="D110" s="28"/>
       <c r="E110" t="s">
         <v>8</v>
       </c>
@@ -3527,17 +3516,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>4</v>
       </c>
       <c r="B111" t="s">
-        <v>57</v>
-      </c>
-      <c r="C111" s="35">
+        <v>50</v>
+      </c>
+      <c r="C111" s="27">
         <v>45413</v>
       </c>
-      <c r="D111" s="36"/>
+      <c r="D111" s="28"/>
       <c r="E111" t="s">
         <v>8</v>
       </c>
@@ -3546,17 +3535,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>4</v>
       </c>
       <c r="B112" t="s">
-        <v>57</v>
-      </c>
-      <c r="C112" s="35">
+        <v>50</v>
+      </c>
+      <c r="C112" s="27">
         <v>45444</v>
       </c>
-      <c r="D112" s="36"/>
+      <c r="D112" s="28"/>
       <c r="E112" t="s">
         <v>8</v>
       </c>
@@ -3565,17 +3554,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>4</v>
       </c>
       <c r="B113" t="s">
-        <v>57</v>
-      </c>
-      <c r="C113" s="35">
+        <v>50</v>
+      </c>
+      <c r="C113" s="27">
         <v>45474</v>
       </c>
-      <c r="D113" s="36"/>
+      <c r="D113" s="28"/>
       <c r="E113" t="s">
         <v>8</v>
       </c>
@@ -3584,17 +3573,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>4</v>
       </c>
       <c r="B114" t="s">
-        <v>57</v>
-      </c>
-      <c r="C114" s="35">
+        <v>50</v>
+      </c>
+      <c r="C114" s="27">
         <v>45505</v>
       </c>
-      <c r="D114" s="36"/>
+      <c r="D114" s="28"/>
       <c r="E114" t="s">
         <v>8</v>
       </c>
@@ -3603,17 +3592,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>4</v>
       </c>
       <c r="B115" t="s">
-        <v>57</v>
-      </c>
-      <c r="C115" s="35">
+        <v>50</v>
+      </c>
+      <c r="C115" s="27">
         <v>45536</v>
       </c>
-      <c r="D115" s="36"/>
+      <c r="D115" s="28"/>
       <c r="E115" t="s">
         <v>8</v>
       </c>
@@ -3622,17 +3611,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>4</v>
       </c>
       <c r="B116" t="s">
-        <v>57</v>
-      </c>
-      <c r="C116" s="35">
+        <v>50</v>
+      </c>
+      <c r="C116" s="27">
         <v>45566</v>
       </c>
-      <c r="D116" s="36"/>
+      <c r="D116" s="28"/>
       <c r="E116" t="s">
         <v>8</v>
       </c>
@@ -3641,17 +3630,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>4</v>
       </c>
       <c r="B117" t="s">
-        <v>57</v>
-      </c>
-      <c r="C117" s="35">
+        <v>50</v>
+      </c>
+      <c r="C117" s="27">
         <v>45597</v>
       </c>
-      <c r="D117" s="36"/>
+      <c r="D117" s="28"/>
       <c r="E117" t="s">
         <v>8</v>
       </c>
@@ -3660,17 +3649,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>4</v>
       </c>
       <c r="B118" t="s">
-        <v>57</v>
-      </c>
-      <c r="C118" s="35">
+        <v>50</v>
+      </c>
+      <c r="C118" s="27">
         <v>45627</v>
       </c>
-      <c r="D118" s="36"/>
+      <c r="D118" s="28"/>
       <c r="E118" t="s">
         <v>8</v>
       </c>
@@ -3679,17 +3668,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>4</v>
       </c>
       <c r="B119" t="s">
-        <v>57</v>
-      </c>
-      <c r="C119" s="35">
+        <v>50</v>
+      </c>
+      <c r="C119" s="27">
         <v>45658</v>
       </c>
-      <c r="D119" s="36"/>
+      <c r="D119" s="28"/>
       <c r="E119" t="s">
         <v>8</v>
       </c>
@@ -3698,17 +3687,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>4</v>
       </c>
       <c r="B120" t="s">
-        <v>57</v>
-      </c>
-      <c r="C120" s="35">
+        <v>50</v>
+      </c>
+      <c r="C120" s="27">
         <v>45689</v>
       </c>
-      <c r="D120" s="36"/>
+      <c r="D120" s="28"/>
       <c r="E120" t="s">
         <v>8</v>
       </c>
@@ -3717,17 +3706,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>4</v>
       </c>
       <c r="B121" t="s">
-        <v>57</v>
-      </c>
-      <c r="C121" s="35">
+        <v>50</v>
+      </c>
+      <c r="C121" s="27">
         <v>45717</v>
       </c>
-      <c r="D121" s="36"/>
+      <c r="D121" s="28"/>
       <c r="E121" t="s">
         <v>8</v>
       </c>
@@ -3736,17 +3725,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>4</v>
       </c>
       <c r="B122" t="s">
-        <v>57</v>
-      </c>
-      <c r="C122" s="35">
+        <v>50</v>
+      </c>
+      <c r="C122" s="27">
         <v>45748</v>
       </c>
-      <c r="D122" s="36"/>
+      <c r="D122" s="28"/>
       <c r="E122" t="s">
         <v>8</v>
       </c>
@@ -3755,17 +3744,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>4</v>
       </c>
       <c r="B123" t="s">
-        <v>57</v>
-      </c>
-      <c r="C123" s="35">
+        <v>50</v>
+      </c>
+      <c r="C123" s="27">
         <v>45778</v>
       </c>
-      <c r="D123" s="36"/>
+      <c r="D123" s="28"/>
       <c r="E123" t="s">
         <v>8</v>
       </c>
@@ -3774,17 +3763,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>4</v>
       </c>
       <c r="B124" t="s">
-        <v>57</v>
-      </c>
-      <c r="C124" s="35">
+        <v>50</v>
+      </c>
+      <c r="C124" s="27">
         <v>45809</v>
       </c>
-      <c r="D124" s="36"/>
+      <c r="D124" s="28"/>
       <c r="E124" t="s">
         <v>8</v>
       </c>
@@ -3793,17 +3782,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>4</v>
       </c>
       <c r="B125" t="s">
-        <v>57</v>
-      </c>
-      <c r="C125" s="35">
+        <v>50</v>
+      </c>
+      <c r="C125" s="27">
         <v>45839</v>
       </c>
-      <c r="D125" s="36"/>
+      <c r="D125" s="28"/>
       <c r="E125" t="s">
         <v>8</v>
       </c>
@@ -3812,17 +3801,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>4</v>
       </c>
       <c r="B126" t="s">
-        <v>57</v>
-      </c>
-      <c r="C126" s="35">
+        <v>50</v>
+      </c>
+      <c r="C126" s="27">
         <v>45870</v>
       </c>
-      <c r="D126" s="36"/>
+      <c r="D126" s="28"/>
       <c r="E126" t="s">
         <v>8</v>
       </c>
@@ -3831,18 +3820,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>4</v>
       </c>
       <c r="B127" t="s">
-        <v>57</v>
-      </c>
-      <c r="C127" s="35">
+        <v>50</v>
+      </c>
+      <c r="C127" s="27">
         <f>EDATE(C126,1)</f>
         <v>45901</v>
       </c>
-      <c r="D127" s="36"/>
+      <c r="D127" s="28"/>
       <c r="E127" t="s">
         <v>1</v>
       </c>
@@ -3851,18 +3840,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>4</v>
       </c>
       <c r="B128" t="s">
-        <v>57</v>
-      </c>
-      <c r="C128" s="35">
+        <v>50</v>
+      </c>
+      <c r="C128" s="27">
         <f t="shared" ref="C128:C134" si="9">EDATE(C127,1)</f>
         <v>45931</v>
       </c>
-      <c r="D128" s="36"/>
+      <c r="D128" s="28"/>
       <c r="E128" t="s">
         <v>1</v>
       </c>
@@ -3871,18 +3860,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>4</v>
       </c>
       <c r="B129" t="s">
-        <v>57</v>
-      </c>
-      <c r="C129" s="35">
+        <v>50</v>
+      </c>
+      <c r="C129" s="27">
         <f t="shared" si="9"/>
         <v>45962</v>
       </c>
-      <c r="D129" s="36"/>
+      <c r="D129" s="28"/>
       <c r="E129" t="s">
         <v>1</v>
       </c>
@@ -3891,18 +3880,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>4</v>
       </c>
       <c r="B130" t="s">
-        <v>57</v>
-      </c>
-      <c r="C130" s="35">
+        <v>50</v>
+      </c>
+      <c r="C130" s="27">
         <f t="shared" si="9"/>
         <v>45992</v>
       </c>
-      <c r="D130" s="36"/>
+      <c r="D130" s="28"/>
       <c r="E130" t="s">
         <v>1</v>
       </c>
@@ -3911,18 +3900,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>4</v>
       </c>
       <c r="B131" t="s">
-        <v>57</v>
-      </c>
-      <c r="C131" s="35">
+        <v>50</v>
+      </c>
+      <c r="C131" s="27">
         <f t="shared" si="9"/>
         <v>46023</v>
       </c>
-      <c r="D131" s="36"/>
+      <c r="D131" s="28"/>
       <c r="E131" t="s">
         <v>1</v>
       </c>
@@ -3931,18 +3920,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>4</v>
       </c>
       <c r="B132" t="s">
-        <v>57</v>
-      </c>
-      <c r="C132" s="35">
+        <v>50</v>
+      </c>
+      <c r="C132" s="27">
         <f t="shared" si="9"/>
         <v>46054</v>
       </c>
-      <c r="D132" s="36"/>
+      <c r="D132" s="28"/>
       <c r="E132" t="s">
         <v>1</v>
       </c>
@@ -3951,18 +3940,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>4</v>
       </c>
       <c r="B133" t="s">
-        <v>57</v>
-      </c>
-      <c r="C133" s="35">
+        <v>50</v>
+      </c>
+      <c r="C133" s="27">
         <f t="shared" si="9"/>
         <v>46082</v>
       </c>
-      <c r="D133" s="36"/>
+      <c r="D133" s="28"/>
       <c r="E133" t="s">
         <v>1</v>
       </c>
@@ -3971,18 +3960,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>4</v>
       </c>
       <c r="B134" t="s">
-        <v>57</v>
-      </c>
-      <c r="C134" s="35">
+        <v>50</v>
+      </c>
+      <c r="C134" s="27">
         <f t="shared" si="9"/>
         <v>46113</v>
       </c>
-      <c r="D134" s="36"/>
+      <c r="D134" s="28"/>
       <c r="E134" t="s">
         <v>1</v>
       </c>
@@ -3999,102 +3988,88 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B648EA-C9CF-4199-AC21-3B599FE2C0B5}">
   <sheetPr codeName="Planilha4"/>
-  <dimension ref="A1:V25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" customWidth="1"/>
-    <col min="12" max="13" width="15.5703125" customWidth="1"/>
-    <col min="14" max="14" width="25.85546875" customWidth="1"/>
-    <col min="15" max="15" width="21.28515625" customWidth="1"/>
-    <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="42.85546875" customWidth="1"/>
-    <col min="18" max="18" width="15.85546875" customWidth="1"/>
-    <col min="19" max="19" width="17.85546875" customWidth="1"/>
-    <col min="20" max="20" width="15.42578125" customWidth="1"/>
-    <col min="21" max="21" width="18.140625" customWidth="1"/>
-    <col min="22" max="22" width="9" customWidth="1"/>
+    <col min="9" max="12" width="15.5546875" customWidth="1"/>
+    <col min="13" max="13" width="25.88671875" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="42.88671875" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" customWidth="1"/>
+    <col min="17" max="17" width="15.44140625" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" customWidth="1"/>
+    <col min="19" max="19" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="45" t="s">
         <v>14</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
-        <v>19</v>
       </c>
       <c r="B2" s="4">
         <v>44805</v>
@@ -4106,1224 +4081,1480 @@
       <c r="D2" s="5">
         <v>32</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="34">
+        <v>37</v>
+      </c>
+      <c r="F2" s="4">
+        <f>EDATE($B2,E2)-1</f>
+        <v>45930</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4">
+        <f>EDATE($B2,G2)-1</f>
+        <v>44804</v>
+      </c>
+      <c r="I2" s="5">
+        <f>(E2-D2)*30</f>
+        <v>150</v>
+      </c>
+      <c r="J2" s="31">
+        <v>49776.481999999996</v>
+      </c>
+      <c r="K2" s="31">
+        <v>30</v>
+      </c>
+      <c r="L2" s="31">
+        <f>K2*J2</f>
+        <v>1493294.46</v>
+      </c>
+      <c r="M2" s="35"/>
+      <c r="N2" s="75">
+        <v>0</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="7">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q2" s="54">
+        <v>48156918.740000002</v>
+      </c>
+      <c r="R2" s="8">
+        <f>I2*P2*Q2</f>
+        <v>2383767.4776300001</v>
+      </c>
+      <c r="S2" s="9">
+        <f>R2/Q2</f>
+        <v>4.9500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="32">
+        <v>44166</v>
+      </c>
+      <c r="C3" s="32">
+        <f t="shared" si="0"/>
+        <v>45230</v>
+      </c>
+      <c r="D3" s="31">
+        <v>35</v>
+      </c>
+      <c r="E3" s="41">
+        <v>39</v>
+      </c>
+      <c r="F3" s="4">
+        <f t="shared" ref="F3:H25" si="1">EDATE($B3,E3)-1</f>
+        <v>45351</v>
+      </c>
+      <c r="G3" s="31">
+        <v>43</v>
+      </c>
+      <c r="H3" s="4">
+        <f t="shared" si="1"/>
+        <v>45473</v>
+      </c>
+      <c r="I3" s="5">
+        <f t="shared" ref="I3:I23" si="2">(E3-D3)*30</f>
+        <v>120</v>
+      </c>
+      <c r="J3">
+        <v>68630.7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L3" s="31">
+        <f>33*J3</f>
+        <v>2264813.1</v>
+      </c>
+      <c r="M3" s="35"/>
+      <c r="N3" s="75">
+        <v>0</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="7">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q3" s="42">
+        <v>59525244</v>
+      </c>
+      <c r="R3" s="8">
+        <v>0</v>
+      </c>
+      <c r="S3" s="9">
+        <f t="shared" ref="S3:S25" si="3">R3/Q3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="10">
+        <v>45170</v>
+      </c>
+      <c r="C4" s="10">
+        <f t="shared" si="0"/>
         <v>45777</v>
       </c>
-      <c r="F2" s="11">
-        <f>EDATE(B2,K2)-1</f>
-        <v>45777</v>
-      </c>
-      <c r="G2" s="4">
-        <v>45716</v>
-      </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="4">
-        <v>45807</v>
-      </c>
-      <c r="J2" s="5">
-        <v>32</v>
-      </c>
-      <c r="K2" s="43">
-        <v>32</v>
-      </c>
-      <c r="L2" s="5">
-        <f>K2-J2</f>
+      <c r="D4" s="11">
+        <v>20</v>
+      </c>
+      <c r="E4" s="35">
+        <v>27</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="1"/>
+        <v>45991</v>
+      </c>
+      <c r="G4" s="11">
+        <v>28</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="J4" s="31">
+        <v>57623.59</v>
+      </c>
+      <c r="K4" s="31">
+        <v>24</v>
+      </c>
+      <c r="L4" s="31">
+        <f t="shared" ref="L3:L25" si="4">K4*J4</f>
+        <v>1382966.16</v>
+      </c>
+      <c r="M4" s="35"/>
+      <c r="N4" s="75">
         <v>0</v>
       </c>
-      <c r="M2" s="5">
-        <f>L2*30</f>
+      <c r="O4" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="38">
+        <v>19331059</v>
+      </c>
+      <c r="R4" s="8">
         <v>0</v>
       </c>
-      <c r="N2" s="44"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="7">
-        <v>3.3E-4</v>
-      </c>
-      <c r="S2" s="8">
-        <v>40300000</v>
-      </c>
-      <c r="T2" s="8"/>
-      <c r="U2" s="9">
-        <f>L2*30*R2*S2</f>
-        <v>0</v>
-      </c>
-      <c r="V2" s="10">
-        <f>U2/S2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="60" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="41">
-        <v>44166</v>
-      </c>
-      <c r="C3" s="41">
-        <f t="shared" si="0"/>
-        <v>45230</v>
-      </c>
-      <c r="D3" s="40">
-        <v>35</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="11">
-        <v>45535</v>
-      </c>
-      <c r="G3" s="41">
-        <v>45473</v>
-      </c>
-      <c r="H3" s="12">
-        <v>3</v>
-      </c>
-      <c r="I3" s="41">
-        <v>45322</v>
-      </c>
-      <c r="J3" s="40">
-        <v>35</v>
-      </c>
-      <c r="K3" s="50">
-        <v>38</v>
-      </c>
-      <c r="L3" s="40">
-        <f>K3-J3</f>
-        <v>3</v>
-      </c>
-      <c r="M3" s="12">
-        <f t="shared" ref="M3:M15" si="1">L3*30</f>
-        <v>90</v>
-      </c>
-      <c r="N3" s="44"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="53"/>
-      <c r="T3" s="53"/>
-      <c r="U3" s="54"/>
-      <c r="V3" s="55"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="11">
-        <v>45187</v>
-      </c>
-      <c r="C4" s="11">
-        <f t="shared" si="0"/>
-        <v>45794</v>
-      </c>
-      <c r="D4" s="12">
-        <v>20</v>
-      </c>
-      <c r="E4" s="11">
-        <v>45838</v>
-      </c>
-      <c r="F4" s="11">
-        <f t="shared" ref="F4:F21" si="2">EDATE(B4,K4)-1</f>
-        <v>45855</v>
-      </c>
-      <c r="G4" s="11">
-        <v>45869</v>
-      </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="11">
-        <v>45856</v>
-      </c>
-      <c r="J4" s="12">
-        <v>20</v>
-      </c>
-      <c r="K4" s="44">
-        <v>22</v>
-      </c>
-      <c r="L4" s="12">
-        <v>2</v>
-      </c>
-      <c r="M4" s="12">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N4" s="44"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="R4" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="S4" s="15">
-        <v>18661553.530000001</v>
-      </c>
-      <c r="T4" s="15"/>
-      <c r="U4" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="V4" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11">
-        <v>45170</v>
-      </c>
-      <c r="C5" s="11">
-        <f t="shared" si="0"/>
-        <v>45900</v>
-      </c>
-      <c r="D5" s="12">
-        <v>24</v>
-      </c>
-      <c r="E5" s="11">
-        <v>45960</v>
-      </c>
-      <c r="F5" s="11">
-        <f t="shared" si="2"/>
-        <v>45991</v>
-      </c>
-      <c r="G5" s="11">
-        <v>46053</v>
-      </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="11">
-        <v>46022</v>
-      </c>
-      <c r="J5" s="12">
-        <v>25.5</v>
-      </c>
-      <c r="K5" s="44">
-        <v>27</v>
-      </c>
-      <c r="L5" s="12">
-        <f>K5-J5</f>
-        <v>1.5</v>
-      </c>
-      <c r="M5" s="12">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="N5" s="44"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" s="17">
-        <v>3.3E-4</v>
-      </c>
-      <c r="S5" s="15">
-        <v>27799452.190000001</v>
-      </c>
-      <c r="T5" s="15"/>
-      <c r="U5" s="18">
-        <f>-L5*30*R5*S5</f>
-        <v>-412821.86502150004</v>
-      </c>
-      <c r="V5" s="19">
-        <f>U5/S5</f>
-        <v>-1.485E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="61" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="11">
-        <v>45301</v>
-      </c>
-      <c r="C6" s="11">
-        <f t="shared" si="0"/>
-        <v>46577</v>
-      </c>
-      <c r="D6" s="12">
-        <v>42</v>
-      </c>
-      <c r="E6" s="11">
-        <v>46566</v>
-      </c>
-      <c r="F6" s="11">
-        <f t="shared" si="2"/>
-        <v>46577</v>
-      </c>
-      <c r="G6" s="11">
-        <v>46691</v>
-      </c>
-      <c r="H6" s="12">
-        <v>3</v>
-      </c>
-      <c r="I6" s="11">
-        <v>46566</v>
-      </c>
-      <c r="J6" s="12">
-        <v>45</v>
-      </c>
-      <c r="K6" s="44">
-        <v>42</v>
-      </c>
-      <c r="L6" s="12">
-        <v>0</v>
-      </c>
-      <c r="M6" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N6" s="44"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="R6" s="17">
-        <v>3.3E-4</v>
-      </c>
-      <c r="S6" s="15">
-        <v>12000000</v>
-      </c>
-      <c r="T6" s="15"/>
-      <c r="U6" s="18">
-        <f>L6*30*R6*S6</f>
-        <v>0</v>
-      </c>
-      <c r="V6" s="19">
-        <f t="shared" ref="V6:V14" si="3">U6/S6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="11">
-        <v>44470</v>
-      </c>
-      <c r="C7" s="11">
-        <f t="shared" si="0"/>
-        <v>45322</v>
-      </c>
-      <c r="D7" s="12">
-        <v>28</v>
-      </c>
-      <c r="E7" s="11">
-        <v>45381</v>
-      </c>
-      <c r="F7" s="11">
-        <f t="shared" si="2"/>
-        <v>45504</v>
-      </c>
-      <c r="G7" s="11">
-        <v>45504</v>
-      </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="11">
-        <v>45504</v>
-      </c>
-      <c r="J7" s="12">
-        <v>28</v>
-      </c>
-      <c r="K7" s="44">
-        <v>34</v>
-      </c>
-      <c r="L7" s="12">
-        <f t="shared" ref="L7:L15" si="4">K7-J7</f>
-        <v>6</v>
-      </c>
-      <c r="M7" s="12">
-        <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="N7" s="44"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="R7" s="17">
-        <v>3.3E-4</v>
-      </c>
-      <c r="S7" s="15">
-        <f>35586462.12-(35586462.12*(8%+1.5%))</f>
-        <v>32205748.218599997</v>
-      </c>
-      <c r="T7" s="15"/>
-      <c r="U7" s="18">
-        <f>IF(L7*30&gt;181,(L7*30-181)*R7*S7,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V7" s="19">
+      <c r="S4" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="11">
-        <v>44682</v>
-      </c>
-      <c r="C8" s="11">
-        <f t="shared" si="0"/>
+    <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="10">
+        <v>45170</v>
+      </c>
+      <c r="C5" s="10">
+        <f t="shared" si="0"/>
+        <v>45900</v>
+      </c>
+      <c r="D5" s="11">
+        <v>24</v>
+      </c>
+      <c r="E5" s="35">
+        <v>34</v>
+      </c>
+      <c r="F5" s="4">
+        <f t="shared" si="1"/>
+        <v>46203</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="4">
+        <f t="shared" si="1"/>
+        <v>45169</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" si="2"/>
+        <v>300</v>
+      </c>
+      <c r="J5" s="31">
+        <v>67040.736666666664</v>
+      </c>
+      <c r="K5" s="31">
+        <v>24</v>
+      </c>
+      <c r="L5" s="31">
+        <f t="shared" si="4"/>
+        <v>1608977.68</v>
+      </c>
+      <c r="M5" s="35"/>
+      <c r="N5" s="75">
+        <v>0</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q5" s="38">
+        <v>30874919.829999998</v>
+      </c>
+      <c r="R5" s="8">
+        <f>Q5*0.05</f>
+        <v>1543745.9915</v>
+      </c>
+      <c r="S5" s="9">
+        <f t="shared" si="3"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="10">
+        <v>45301</v>
+      </c>
+      <c r="C6" s="10">
+        <f t="shared" si="0"/>
+        <v>46577</v>
+      </c>
+      <c r="D6" s="11">
+        <v>42</v>
+      </c>
+      <c r="E6" s="35">
+        <v>46</v>
+      </c>
+      <c r="F6" s="4">
+        <f t="shared" si="1"/>
+        <v>46700</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="4">
+        <f t="shared" si="1"/>
+        <v>45300</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="J6" s="31">
+        <v>189984.66261904765</v>
+      </c>
+      <c r="K6" s="31">
+        <v>46</v>
+      </c>
+      <c r="L6" s="31">
+        <f t="shared" si="4"/>
+        <v>8739294.4804761913</v>
+      </c>
+      <c r="M6" s="35"/>
+      <c r="N6" s="75">
+        <v>0</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q6" s="38">
+        <v>150327077.33000001</v>
+      </c>
+      <c r="R6" s="8">
+        <f>I6*P6*Q6</f>
+        <v>5952952.2622680003</v>
+      </c>
+      <c r="S6" s="9">
+        <f t="shared" si="3"/>
+        <v>3.9599999999999996E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="10">
+        <v>44470</v>
+      </c>
+      <c r="C7" s="10">
+        <f t="shared" si="0"/>
+        <v>45322</v>
+      </c>
+      <c r="D7" s="11">
+        <v>28</v>
+      </c>
+      <c r="E7" s="35">
+        <v>33</v>
+      </c>
+      <c r="F7" s="4">
+        <f t="shared" si="1"/>
+        <v>45473</v>
+      </c>
+      <c r="G7" s="11">
+        <v>34</v>
+      </c>
+      <c r="H7" s="4">
+        <f t="shared" si="1"/>
         <v>45504</v>
       </c>
-      <c r="D8" s="12">
-        <v>27</v>
-      </c>
-      <c r="E8" s="11">
-        <v>45595</v>
-      </c>
-      <c r="F8" s="11">
+      <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>45596</v>
-      </c>
-      <c r="G8" s="11">
-        <v>45687</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11">
-        <v>45595</v>
-      </c>
-      <c r="J8" s="12">
-        <v>27</v>
-      </c>
-      <c r="K8" s="44">
-        <v>30</v>
-      </c>
-      <c r="L8" s="12">
+        <v>150</v>
+      </c>
+      <c r="J7" s="31">
+        <v>42636.509999999995</v>
+      </c>
+      <c r="K7" s="31">
+        <v>26</v>
+      </c>
+      <c r="L7" s="31">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="M8" s="12">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="N8" s="44"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="R8" s="17">
+        <v>1108549.2599999998</v>
+      </c>
+      <c r="M7" s="35"/>
+      <c r="N7" s="75">
+        <v>0</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" s="15">
         <v>3.3E-4</v>
       </c>
-      <c r="S8" s="15">
-        <f>56805766.41-(56805766.41*(8%+1.5%))</f>
-        <v>51409218.601049997</v>
-      </c>
-      <c r="T8" s="15"/>
-      <c r="U8" s="18">
-        <f>IF(L8*30&gt;181,(L8*30-181)*R8*S8,0)</f>
+      <c r="Q7" s="38">
+        <v>39854406</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
-      <c r="V8" s="19">
+      <c r="S7" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="11">
-        <v>44621</v>
-      </c>
-      <c r="C9" s="11">
-        <f t="shared" si="0"/>
-        <v>45412</v>
-      </c>
-      <c r="D9" s="12">
-        <v>26</v>
-      </c>
-      <c r="E9" s="11">
+    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="10">
+        <v>44682</v>
+      </c>
+      <c r="C8" s="10">
+        <f t="shared" si="0"/>
         <v>45504</v>
       </c>
-      <c r="F9" s="11">
+      <c r="D8" s="11">
+        <v>27</v>
+      </c>
+      <c r="E8" s="35">
+        <v>33</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="1"/>
+        <v>45688</v>
+      </c>
+      <c r="G8" s="11">
+        <v>38</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="1"/>
+        <v>45838</v>
+      </c>
+      <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>45657</v>
-      </c>
-      <c r="G9" s="11">
-        <v>45687</v>
-      </c>
-      <c r="H9" s="12">
-        <v>2</v>
-      </c>
-      <c r="I9" s="11">
-        <f t="shared" ref="I9:I21" si="5">EDATE(E9,H9)</f>
-        <v>45565</v>
-      </c>
-      <c r="J9" s="12">
-        <v>26</v>
-      </c>
-      <c r="K9" s="44">
-        <v>34</v>
-      </c>
-      <c r="L9" s="12">
+        <v>180</v>
+      </c>
+      <c r="J8" s="31">
+        <v>71960.148148148146</v>
+      </c>
+      <c r="K8" s="31">
+        <v>27</v>
+      </c>
+      <c r="L8" s="31">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="M9" s="12">
-        <f t="shared" si="1"/>
-        <v>240</v>
-      </c>
-      <c r="N9" s="44"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="R9" s="17">
+        <v>1942924</v>
+      </c>
+      <c r="M8" s="35"/>
+      <c r="N8" s="75">
+        <v>0</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="15">
         <v>3.3E-4</v>
       </c>
-      <c r="S9" s="15">
-        <f>38866880.92-(38866880.92*(8%+1.5%))</f>
-        <v>35174527.232600003</v>
-      </c>
-      <c r="T9" s="15"/>
-      <c r="U9" s="18">
-        <f>-IF(L9*30&gt;181,(L9*30-181)*R9*S9,0)</f>
-        <v>-684848.04521872208</v>
-      </c>
-      <c r="V9" s="19">
-        <f t="shared" si="3"/>
-        <v>-1.9470000000000001E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="11">
-        <v>45139</v>
-      </c>
-      <c r="C10" s="11">
-        <f t="shared" si="0"/>
-        <v>45504</v>
-      </c>
-      <c r="D10" s="12">
-        <v>12</v>
-      </c>
-      <c r="E10" s="11">
-        <v>45504</v>
-      </c>
-      <c r="F10" s="11">
-        <f t="shared" si="2"/>
-        <v>45657</v>
-      </c>
-      <c r="G10" s="11">
-        <v>45687</v>
-      </c>
-      <c r="H10" s="12">
-        <v>3</v>
-      </c>
-      <c r="I10" s="11">
-        <f t="shared" si="5"/>
-        <v>45596</v>
-      </c>
-      <c r="J10" s="12">
-        <v>12</v>
-      </c>
-      <c r="K10" s="44">
-        <f>J10+5</f>
-        <v>17</v>
-      </c>
-      <c r="L10" s="12">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="M10" s="12">
-        <f t="shared" si="1"/>
-        <v>150</v>
-      </c>
-      <c r="N10" s="44"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="R10" s="17">
-        <v>3.3E-4</v>
-      </c>
-      <c r="S10" s="15">
-        <f>7702516.71-(7702516.71*(8.21307082165992%+1.5%))</f>
-        <v>6954365.8069075104</v>
-      </c>
-      <c r="T10" s="15"/>
-      <c r="U10" s="18">
-        <f>IF(L10*30&gt;181,(L10*30-181)*R10*S10,0)</f>
+      <c r="Q8" s="38">
+        <v>62491370</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
-      <c r="V10" s="19">
+      <c r="S8" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="11">
-        <v>44805</v>
-      </c>
-      <c r="C11" s="11">
-        <f t="shared" si="0"/>
-        <v>45747</v>
-      </c>
-      <c r="D11" s="12">
-        <v>31</v>
-      </c>
-      <c r="E11" s="11">
+    <row r="9" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="10">
+        <v>44621</v>
+      </c>
+      <c r="C9" s="10">
+        <f t="shared" si="0"/>
+        <v>45412</v>
+      </c>
+      <c r="D9" s="11">
+        <v>26</v>
+      </c>
+      <c r="E9" s="35">
+        <v>34</v>
+      </c>
+      <c r="F9" s="4">
+        <f t="shared" si="1"/>
+        <v>45657</v>
+      </c>
+      <c r="G9" s="11">
+        <v>39</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" si="1"/>
         <v>45808</v>
       </c>
-      <c r="F11" s="11">
+      <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>45930</v>
-      </c>
-      <c r="G11" s="11">
-        <v>45991</v>
-      </c>
-      <c r="H11" s="12">
-        <v>2</v>
-      </c>
-      <c r="I11" s="11">
-        <f t="shared" si="5"/>
-        <v>45869</v>
-      </c>
-      <c r="J11" s="12">
-        <v>31</v>
-      </c>
-      <c r="K11" s="44">
-        <v>37</v>
-      </c>
-      <c r="L11" s="12">
+        <v>240</v>
+      </c>
+      <c r="J9" s="31">
+        <v>65351.329999999994</v>
+      </c>
+      <c r="K9" s="31">
+        <v>24</v>
+      </c>
+      <c r="L9" s="31">
         <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="M11" s="12">
-        <f t="shared" si="1"/>
+        <v>1568431.92</v>
+      </c>
+      <c r="M9" s="35"/>
+      <c r="N9" s="75">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q9" s="38">
+        <v>45889672</v>
+      </c>
+      <c r="R9" s="8">
+        <f>(I9-180)*P9*Q9</f>
+        <v>908615.50559999992</v>
+      </c>
+      <c r="S9" s="9">
+        <f t="shared" si="3"/>
+        <v>1.9799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="10">
+        <v>45139</v>
+      </c>
+      <c r="C10" s="10">
+        <f t="shared" si="0"/>
+        <v>45504</v>
+      </c>
+      <c r="D10" s="11">
+        <v>12</v>
+      </c>
+      <c r="E10" s="35">
+        <v>18</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="1"/>
+        <v>45688</v>
+      </c>
+      <c r="G10" s="11">
+        <v>18</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="1"/>
+        <v>45688</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="2"/>
         <v>180</v>
       </c>
-      <c r="N11" s="44"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="R11" s="17">
+      <c r="J10" s="31">
+        <v>39906.74</v>
+      </c>
+      <c r="K10" s="31">
+        <v>12</v>
+      </c>
+      <c r="L10" s="31">
+        <f t="shared" si="4"/>
+        <v>478880.88</v>
+      </c>
+      <c r="M10" s="35"/>
+      <c r="N10" s="75">
+        <v>0</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" s="15">
         <v>3.3E-4</v>
       </c>
-      <c r="S11" s="15">
-        <f>92100480.78-(92100480.78*(9%+1.5%))</f>
-        <v>82429930.298099995</v>
-      </c>
-      <c r="T11" s="15"/>
-      <c r="U11" s="18">
-        <f>IF(L11*30&gt;181,(L11*30-181)*R11*S11,0)</f>
+      <c r="Q10" s="38">
+        <v>8442659</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
-      <c r="V11" s="19">
+      <c r="S10" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="61" t="s">
+    <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="10">
+        <v>44805</v>
+      </c>
+      <c r="C11" s="10">
+        <f t="shared" si="0"/>
+        <v>45747</v>
+      </c>
+      <c r="D11" s="11">
         <v>31</v>
       </c>
-      <c r="B12" s="11">
+      <c r="E11" s="35">
+        <v>42</v>
+      </c>
+      <c r="F11" s="4">
+        <f t="shared" si="1"/>
+        <v>46081</v>
+      </c>
+      <c r="G11" s="11">
+        <v>47</v>
+      </c>
+      <c r="H11" s="4">
+        <f t="shared" si="1"/>
+        <v>46234</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="2"/>
+        <v>330</v>
+      </c>
+      <c r="J11" s="76">
+        <v>112914.29540540541</v>
+      </c>
+      <c r="K11" s="76">
+        <v>37</v>
+      </c>
+      <c r="L11" s="31">
+        <f t="shared" si="4"/>
+        <v>4177828.93</v>
+      </c>
+      <c r="M11" s="35"/>
+      <c r="N11" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q11" s="38">
+        <v>100802866</v>
+      </c>
+      <c r="R11" s="8">
+        <f>(I11-180)*P11*Q11</f>
+        <v>4989741.8670000006</v>
+      </c>
+      <c r="S11" s="9">
+        <f t="shared" si="3"/>
+        <v>4.9500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="10">
         <v>45047</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <f t="shared" si="0"/>
         <v>46081</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>34</v>
       </c>
-      <c r="E12" s="11">
-        <f>C12</f>
+      <c r="E12" s="35">
+        <v>34</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="1"/>
         <v>46081</v>
       </c>
-      <c r="F12" s="11">
+      <c r="G12" s="11">
+        <v>34</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" si="1"/>
+        <v>46081</v>
+      </c>
+      <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>46081</v>
-      </c>
-      <c r="G12" s="11">
-        <v>46387</v>
-      </c>
-      <c r="H12" s="12">
-        <v>3</v>
-      </c>
-      <c r="I12" s="11">
-        <f t="shared" si="5"/>
-        <v>46170</v>
-      </c>
-      <c r="J12" s="12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="31">
+        <v>72429.599999999991</v>
+      </c>
+      <c r="K12" s="31">
         <v>34</v>
       </c>
-      <c r="K12" s="44">
-        <v>34</v>
-      </c>
-      <c r="L12" s="12">
+      <c r="L12" s="31">
         <f t="shared" si="4"/>
+        <v>2462606.4</v>
+      </c>
+      <c r="M12" s="35"/>
+      <c r="N12" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q12" s="38">
+        <v>129823938</v>
+      </c>
+      <c r="R12" s="8">
+        <f>I12*P12*Q12</f>
         <v>0</v>
       </c>
-      <c r="M12" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="44"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="R12" s="17">
-        <v>3.3E-4</v>
-      </c>
-      <c r="S12" s="15">
-        <f>124592079.07-(124592079.07*(8%+1.5%))</f>
-        <v>112755831.55835</v>
-      </c>
-      <c r="T12" s="15"/>
-      <c r="U12" s="18">
-        <f>IF(L12*30&gt;181,(L12*30-181)*R12*S12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V12" s="19">
+      <c r="S12" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="11">
+    <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="10">
         <v>45413</v>
       </c>
-      <c r="C13" s="11">
-        <f t="shared" si="0"/>
-        <v>46507</v>
-      </c>
-      <c r="D13" s="12">
+      <c r="C13" s="10">
+        <f t="shared" si="0"/>
+        <v>46691</v>
+      </c>
+      <c r="D13" s="11">
+        <v>42</v>
+      </c>
+      <c r="E13" s="35">
+        <v>42</v>
+      </c>
+      <c r="F13" s="4">
+        <f t="shared" si="1"/>
+        <v>46691</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="4">
+        <f t="shared" si="1"/>
+        <v>45412</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="31">
+        <v>113407.94166666668</v>
+      </c>
+      <c r="K13" s="31">
         <v>36</v>
       </c>
-      <c r="E13" s="11">
-        <f>C13</f>
-        <v>46507</v>
-      </c>
-      <c r="F13" s="11">
-        <f t="shared" si="2"/>
-        <v>46507</v>
-      </c>
-      <c r="G13" s="11">
-        <v>46660</v>
-      </c>
-      <c r="H13" s="12">
-        <v>3</v>
-      </c>
-      <c r="I13" s="11">
-        <f t="shared" si="5"/>
-        <v>46598</v>
-      </c>
-      <c r="J13" s="12">
-        <v>36</v>
-      </c>
-      <c r="K13" s="44">
-        <v>36</v>
-      </c>
-      <c r="L13" s="12">
+      <c r="L13" s="31">
         <f t="shared" si="4"/>
+        <v>4082685.9000000004</v>
+      </c>
+      <c r="M13" s="35"/>
+      <c r="N13" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q13" s="38">
+        <v>75712669</v>
+      </c>
+      <c r="R13" s="8">
+        <f>I13*P13*Q13</f>
         <v>0</v>
       </c>
-      <c r="M13" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="44"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="R13" s="17">
-        <v>3.3E-4</v>
-      </c>
-      <c r="S13" s="15">
-        <v>65573854.114900015</v>
-      </c>
-      <c r="T13" s="15"/>
-      <c r="U13" s="18">
-        <f>IF(L13*30&gt;181,(L13*30-181)*R13*S13,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V13" s="19">
+      <c r="S13" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="61" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="11">
+    <row r="14" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="10">
         <v>45444</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <f t="shared" si="0"/>
         <v>46173</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <v>24</v>
       </c>
-      <c r="E14" s="11">
-        <f>C14</f>
+      <c r="E14" s="35">
+        <v>24</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="1"/>
         <v>46173</v>
       </c>
-      <c r="F14" s="11">
+      <c r="G14" s="11"/>
+      <c r="H14" s="4">
+        <f t="shared" si="1"/>
+        <v>45443</v>
+      </c>
+      <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>46173</v>
-      </c>
-      <c r="G14" s="11">
-        <v>46325</v>
-      </c>
-      <c r="H14" s="12">
-        <v>3</v>
-      </c>
-      <c r="I14" s="11">
-        <f t="shared" si="5"/>
-        <v>46265</v>
-      </c>
-      <c r="J14" s="12">
+        <v>0</v>
+      </c>
+      <c r="J14" s="31">
+        <v>69631.679999999993</v>
+      </c>
+      <c r="K14" s="31">
         <v>24</v>
       </c>
-      <c r="K14" s="44">
-        <v>24</v>
-      </c>
-      <c r="L14" s="12">
+      <c r="L14" s="31">
         <f t="shared" si="4"/>
+        <v>1671160.3199999998</v>
+      </c>
+      <c r="M14" s="35"/>
+      <c r="N14" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q14" s="38">
+        <v>24795027</v>
+      </c>
+      <c r="R14" s="8">
+        <f>I14*P14*Q14</f>
         <v>0</v>
       </c>
-      <c r="M14" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="44"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="R14" s="17">
-        <v>3.3E-4</v>
-      </c>
-      <c r="S14" s="15">
-        <v>21768595.187699985</v>
-      </c>
-      <c r="T14" s="15"/>
-      <c r="U14" s="18">
-        <f>IF(L14*30&gt;181,(L14*30-181)*R14*S14,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V14" s="19">
+      <c r="S14" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="61" t="s">
+    <row r="15" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="10">
+        <v>45413</v>
+      </c>
+      <c r="C15" s="10">
+        <f t="shared" si="0"/>
+        <v>45716</v>
+      </c>
+      <c r="D15" s="11">
+        <v>10</v>
+      </c>
+      <c r="E15" s="35">
+        <v>12</v>
+      </c>
+      <c r="F15" s="4">
+        <f t="shared" si="1"/>
+        <v>45777</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="4">
+        <f t="shared" si="1"/>
+        <v>45412</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="J15" s="31">
+        <v>54235.135999999999</v>
+      </c>
+      <c r="K15" s="31">
+        <f>J15/10</f>
+        <v>5423.5136000000002</v>
+      </c>
+      <c r="L15" s="31">
+        <f t="shared" si="4"/>
+        <v>294144997.69384962</v>
+      </c>
+      <c r="M15" s="35"/>
+      <c r="N15" s="75">
+        <v>0</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q15" s="38">
+        <v>36372271</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
+      </c>
+      <c r="S15" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="10">
+        <v>45444</v>
+      </c>
+      <c r="C16" s="10">
+        <f t="shared" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="D16" s="11">
+        <v>8</v>
+      </c>
+      <c r="E16" s="35">
+        <v>8</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="1"/>
+        <v>45688</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="4">
+        <f t="shared" si="1"/>
+        <v>45443</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="31">
+        <v>22716.98</v>
+      </c>
+      <c r="K16" s="31">
+        <v>8</v>
+      </c>
+      <c r="L16" s="31">
+        <f t="shared" si="4"/>
+        <v>181735.84</v>
+      </c>
+      <c r="M16" s="35"/>
+      <c r="N16" s="75">
+        <v>0</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q16" s="38">
+        <v>1365707</v>
+      </c>
+      <c r="R16" s="8">
+        <f>I16*P16*Q16</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="10">
+        <v>45444</v>
+      </c>
+      <c r="C17" s="10">
+        <f t="shared" si="0"/>
+        <v>46477</v>
+      </c>
+      <c r="D17" s="11">
         <v>34</v>
       </c>
-      <c r="B15" s="11">
-        <v>45413</v>
-      </c>
-      <c r="C15" s="11">
-        <f t="shared" si="0"/>
+      <c r="E17" s="35">
+        <v>34</v>
+      </c>
+      <c r="F17" s="4">
+        <f t="shared" si="1"/>
+        <v>46477</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="4">
+        <f t="shared" si="1"/>
+        <v>45443</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="31">
+        <v>82372.476666666669</v>
+      </c>
+      <c r="K17" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L17" s="31">
+        <f>39*J17</f>
+        <v>3212526.5900000003</v>
+      </c>
+      <c r="M17" s="35"/>
+      <c r="N17" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q17" s="38">
+        <v>82688581</v>
+      </c>
+      <c r="R17" s="8">
+        <f>I17*P17*Q17</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="10">
+        <v>45536</v>
+      </c>
+      <c r="C18" s="10">
+        <f t="shared" si="0"/>
+        <v>46477</v>
+      </c>
+      <c r="D18" s="11">
+        <v>31</v>
+      </c>
+      <c r="E18" s="35">
+        <v>31</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="1"/>
+        <v>46477</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="4">
+        <f t="shared" si="1"/>
         <v>45535</v>
       </c>
-      <c r="D15" s="12">
-        <v>4</v>
-      </c>
-      <c r="E15" s="11">
-        <v>45534</v>
-      </c>
-      <c r="F15" s="11">
+      <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>45900</v>
-      </c>
-      <c r="G15" s="11">
-        <v>45534</v>
-      </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="11">
-        <f t="shared" si="5"/>
-        <v>45534</v>
-      </c>
-      <c r="J15" s="12">
-        <v>16</v>
-      </c>
-      <c r="K15" s="44">
-        <v>16</v>
-      </c>
-      <c r="L15" s="12">
+        <v>0</v>
+      </c>
+      <c r="J18" s="31">
+        <v>72603.663636363635</v>
+      </c>
+      <c r="K18" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="L18" s="31">
+        <f>31*J18</f>
+        <v>2250713.5727272728</v>
+      </c>
+      <c r="M18" s="35"/>
+      <c r="N18" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q18" s="38">
+        <v>61763786</v>
+      </c>
+      <c r="R18" s="8">
+        <f>I18*P18*Q18</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="10">
+        <v>45536</v>
+      </c>
+      <c r="C19" s="10">
+        <f t="shared" si="0"/>
+        <v>46265</v>
+      </c>
+      <c r="D19" s="11">
+        <v>24</v>
+      </c>
+      <c r="E19" s="35">
+        <v>24</v>
+      </c>
+      <c r="F19" s="4">
+        <f t="shared" si="1"/>
+        <v>46265</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="4">
+        <f t="shared" si="1"/>
+        <v>45535</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="31">
+        <v>65164.644999999997</v>
+      </c>
+      <c r="K19" s="31">
+        <v>24</v>
+      </c>
+      <c r="L19" s="31">
         <f t="shared" si="4"/>
+        <v>1563951.48</v>
+      </c>
+      <c r="M19" s="35"/>
+      <c r="N19" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q19" s="38">
+        <v>33840813</v>
+      </c>
+      <c r="R19" s="8">
+        <f>I19*P19*Q19</f>
         <v>0</v>
       </c>
-      <c r="M15" s="12">
-        <f t="shared" si="1"/>
+      <c r="S19" s="9">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N15" s="44"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="R15" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="S15" s="15">
-        <f>33039908.6100987</f>
-        <v>33039908.610098701</v>
-      </c>
-      <c r="T15" s="15"/>
-      <c r="U15" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="V15" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="11">
-        <v>45444</v>
-      </c>
-      <c r="C16" s="11">
-        <f t="shared" si="0"/>
-        <v>45688</v>
-      </c>
-      <c r="D16" s="12">
-        <v>8</v>
-      </c>
-      <c r="E16" s="11">
-        <f t="shared" ref="E16:E21" si="6">C16</f>
-        <v>45688</v>
-      </c>
-      <c r="F16" s="11">
+    </row>
+    <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="10">
+        <v>46113</v>
+      </c>
+      <c r="C20" s="10">
+        <f t="shared" si="0"/>
+        <v>46418</v>
+      </c>
+      <c r="D20" s="11">
+        <v>10</v>
+      </c>
+      <c r="E20" s="35">
+        <v>12</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="1"/>
+        <v>46477</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="4">
+        <f t="shared" si="1"/>
+        <v>46112</v>
+      </c>
+      <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>45688</v>
-      </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="11">
-        <f t="shared" si="5"/>
-        <v>45688</v>
-      </c>
-      <c r="J16" s="12"/>
-      <c r="K16" s="44">
-        <v>8</v>
-      </c>
-      <c r="L16" s="12">
-        <f t="shared" ref="L16" si="7">K16-J16</f>
-        <v>8</v>
-      </c>
-      <c r="M16" s="12">
-        <f t="shared" ref="M16:M21" si="8">L16*30</f>
-        <v>240</v>
-      </c>
-      <c r="N16" s="44"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="19"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="11">
-        <v>45444</v>
-      </c>
-      <c r="C17" s="11">
-        <f t="shared" si="0"/>
-        <v>46477</v>
-      </c>
-      <c r="D17" s="12">
-        <v>34</v>
-      </c>
-      <c r="E17" s="11">
-        <f t="shared" si="6"/>
-        <v>46477</v>
-      </c>
-      <c r="F17" s="11">
+        <v>60</v>
+      </c>
+      <c r="J20" s="31">
+        <v>30434.447999999997</v>
+      </c>
+      <c r="K20" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="L20" s="31">
+        <f>10*J20</f>
+        <v>304344.48</v>
+      </c>
+      <c r="M20" s="35"/>
+      <c r="N20" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q20" s="38">
+        <v>1946684</v>
+      </c>
+      <c r="R20" s="8">
+        <f>I20*P20*Q20</f>
+        <v>38544.343199999996</v>
+      </c>
+      <c r="S20" s="9">
+        <f t="shared" si="3"/>
+        <v>1.9799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="16">
+        <v>45627</v>
+      </c>
+      <c r="C21" s="16">
+        <f t="shared" si="0"/>
+        <v>46053</v>
+      </c>
+      <c r="D21" s="33">
+        <v>14</v>
+      </c>
+      <c r="E21" s="36">
+        <v>17</v>
+      </c>
+      <c r="F21" s="4">
+        <f t="shared" si="1"/>
+        <v>46142</v>
+      </c>
+      <c r="G21" s="33"/>
+      <c r="H21" s="4">
+        <f t="shared" si="1"/>
+        <v>45626</v>
+      </c>
+      <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>46446</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="12">
-        <v>3</v>
-      </c>
-      <c r="I17" s="11">
-        <f t="shared" si="5"/>
-        <v>46568</v>
-      </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="44">
-        <v>33</v>
-      </c>
-      <c r="L17" s="12">
-        <v>34</v>
-      </c>
-      <c r="M17" s="12">
-        <f t="shared" si="8"/>
-        <v>1020</v>
-      </c>
-      <c r="N17" s="44"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="18"/>
-      <c r="V17" s="19"/>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="11">
-        <v>45536</v>
-      </c>
-      <c r="C18" s="11">
-        <f t="shared" si="0"/>
-        <v>46477</v>
-      </c>
-      <c r="D18" s="12">
-        <v>31</v>
-      </c>
-      <c r="E18" s="11">
-        <f t="shared" si="6"/>
-        <v>46477</v>
-      </c>
-      <c r="F18" s="11">
+        <v>90</v>
+      </c>
+      <c r="J21" s="72">
+        <v>43235.649999999994</v>
+      </c>
+      <c r="K21" s="72">
+        <v>12</v>
+      </c>
+      <c r="L21" s="31">
+        <f t="shared" si="4"/>
+        <v>518827.79999999993</v>
+      </c>
+      <c r="M21" s="36"/>
+      <c r="N21" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q21" s="39">
+        <v>14696272</v>
+      </c>
+      <c r="R21" s="8">
+        <v>0</v>
+      </c>
+      <c r="S21" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="71">
+        <v>45992</v>
+      </c>
+      <c r="C22" s="71">
+        <f>EDATE(B22,D22)-1</f>
+        <v>47361</v>
+      </c>
+      <c r="D22">
+        <v>45</v>
+      </c>
+      <c r="E22" s="74">
+        <v>45</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="1"/>
+        <v>47361</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" si="1"/>
+        <v>45991</v>
+      </c>
+      <c r="I22" s="5">
+        <f>(E22-D22)*30</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="73">
+        <v>186189.96111111113</v>
+      </c>
+      <c r="K22" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="L22" s="31">
+        <f>45*J22</f>
+        <v>8378548.2500000009</v>
+      </c>
+      <c r="N22" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O22" s="78" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q22" s="65">
+        <v>23961874</v>
+      </c>
+      <c r="R22" s="8">
+        <f>I22*P22*Q22</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="71">
+        <v>46082</v>
+      </c>
+      <c r="C23" s="71">
+        <f>EDATE(B23,D23)-1</f>
+        <v>47452</v>
+      </c>
+      <c r="D23">
+        <v>45</v>
+      </c>
+      <c r="E23" s="74">
+        <v>45</v>
+      </c>
+      <c r="F23" s="4">
+        <f t="shared" si="1"/>
+        <v>47452</v>
+      </c>
+      <c r="H23" s="4">
+        <f t="shared" si="1"/>
+        <v>46081</v>
+      </c>
+      <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>46418</v>
-      </c>
-      <c r="G18" s="11"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="11">
-        <f t="shared" si="5"/>
-        <v>46477</v>
-      </c>
-      <c r="J18" s="12"/>
-      <c r="K18" s="44">
-        <v>29</v>
-      </c>
-      <c r="L18" s="12">
-        <v>32</v>
-      </c>
-      <c r="M18" s="12">
-        <f t="shared" si="8"/>
-        <v>960</v>
-      </c>
-      <c r="N18" s="44"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="15"/>
-      <c r="T18" s="15"/>
-      <c r="U18" s="18"/>
-      <c r="V18" s="19"/>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="11">
-        <v>45536</v>
-      </c>
-      <c r="C19" s="11">
-        <f t="shared" si="0"/>
-        <v>46265</v>
-      </c>
-      <c r="D19" s="12">
+        <v>0</v>
+      </c>
+      <c r="J23" s="73">
+        <v>92468.744888888876</v>
+      </c>
+      <c r="K23" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="L23" s="31">
+        <f>45*J23</f>
+        <v>4161093.5199999996</v>
+      </c>
+      <c r="N23" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" s="15">
+        <v>3.3E-4</v>
+      </c>
+      <c r="Q23" s="65">
+        <v>109238942</v>
+      </c>
+      <c r="R23" s="8">
+        <f>I23*P23*Q23</f>
+        <v>0</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="71">
+        <v>46143</v>
+      </c>
+      <c r="C24" s="71">
+        <f>EDATE(B24,D24)-1</f>
+        <v>47057</v>
+      </c>
+      <c r="D24">
+        <v>30</v>
+      </c>
+      <c r="E24" s="74">
+        <v>28</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="1"/>
+        <v>46996</v>
+      </c>
+      <c r="H24" s="4">
+        <f t="shared" si="1"/>
+        <v>46142</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0</v>
+      </c>
+      <c r="J24" s="73">
+        <v>86570.127999999997</v>
+      </c>
+      <c r="K24" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="L24" s="31">
+        <f>30*J24</f>
+        <v>2597103.84</v>
+      </c>
+      <c r="N24" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O24" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="P24" s="30">
+        <f>0.01/30</f>
+        <v>3.3333333333333332E-4</v>
+      </c>
+      <c r="Q24" s="65">
+        <v>52846811</v>
+      </c>
+      <c r="R24" s="8">
+        <f>I24*P24*Q24</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="71">
+        <v>45931</v>
+      </c>
+      <c r="C25" s="71">
+        <f>EDATE(B25,D25)-1</f>
+        <v>46843</v>
+      </c>
+      <c r="D25">
+        <v>30</v>
+      </c>
+      <c r="E25" s="74">
+        <v>27</v>
+      </c>
+      <c r="F25" s="4">
+        <f t="shared" si="1"/>
+        <v>46752</v>
+      </c>
+      <c r="H25" s="4">
+        <f t="shared" si="1"/>
+        <v>45930</v>
+      </c>
+      <c r="I25" s="5">
+        <v>0</v>
+      </c>
+      <c r="J25" s="73">
+        <v>59174.37</v>
+      </c>
+      <c r="K25" s="73">
         <v>24</v>
       </c>
-      <c r="E19" s="11">
-        <f t="shared" si="6"/>
-        <v>46265</v>
-      </c>
-      <c r="F19" s="11">
-        <f t="shared" si="2"/>
-        <v>46265</v>
-      </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="12">
-        <v>3</v>
-      </c>
-      <c r="I19" s="11">
-        <f t="shared" si="5"/>
-        <v>46356</v>
-      </c>
-      <c r="J19" s="12"/>
-      <c r="K19" s="44">
-        <v>24</v>
-      </c>
-      <c r="L19" s="12">
-        <v>24</v>
-      </c>
-      <c r="M19" s="12">
-        <f t="shared" si="8"/>
-        <v>720</v>
-      </c>
-      <c r="N19" s="44"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="19"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="11">
-        <v>45627</v>
-      </c>
-      <c r="C20" s="11">
-        <f t="shared" si="0"/>
-        <v>45991</v>
-      </c>
-      <c r="D20" s="12">
-        <v>12</v>
-      </c>
-      <c r="E20" s="11">
-        <f t="shared" si="6"/>
-        <v>45991</v>
-      </c>
-      <c r="F20" s="11">
-        <f t="shared" si="2"/>
-        <v>45991</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="11">
-        <f t="shared" si="5"/>
-        <v>45991</v>
-      </c>
-      <c r="J20" s="12"/>
-      <c r="K20" s="44">
-        <v>12</v>
-      </c>
-      <c r="L20" s="12">
-        <v>12</v>
-      </c>
-      <c r="M20" s="12">
-        <f t="shared" si="8"/>
-        <v>360</v>
-      </c>
-      <c r="N20" s="44"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="19"/>
-    </row>
-    <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="20">
-        <v>45627</v>
-      </c>
-      <c r="C21" s="20">
-        <f t="shared" si="0"/>
-        <v>46053</v>
-      </c>
-      <c r="D21" s="42">
-        <v>14</v>
-      </c>
-      <c r="E21" s="20">
-        <f t="shared" si="6"/>
-        <v>46053</v>
-      </c>
-      <c r="F21" s="20">
-        <f t="shared" si="2"/>
-        <v>46356</v>
-      </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20">
-        <f t="shared" si="5"/>
-        <v>46053</v>
-      </c>
-      <c r="J21" s="20"/>
-      <c r="K21" s="45">
-        <v>24</v>
-      </c>
-      <c r="L21" s="42">
-        <v>14</v>
-      </c>
-      <c r="M21" s="42">
-        <f t="shared" si="8"/>
-        <v>420</v>
-      </c>
-      <c r="N21" s="45"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="22"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="25"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="77" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="77" t="s">
-        <v>78</v>
+      <c r="L25" s="31">
+        <f t="shared" si="4"/>
+        <v>1420184.8800000001</v>
+      </c>
+      <c r="N25" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O25" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="P25" s="28">
+        <v>0.02</v>
+      </c>
+      <c r="Q25" s="65">
+        <v>22244837</v>
+      </c>
+      <c r="R25" s="80">
+        <f>IF(I25&gt;0,Q25*P25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V21" xr:uid="{33CAF822-3328-4366-8D56-AAC829B41FCE}"/>
+  <autoFilter ref="A1:S21" xr:uid="{33CAF822-3328-4366-8D56-AAC829B41FCE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -5332,1004 +5563,1004 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9847408C-B23C-4D48-83D1-CB6301E525D5}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="36.42578125" customWidth="1"/>
-    <col min="3" max="8" width="27.85546875" customWidth="1"/>
-    <col min="9" max="9" width="36.42578125" style="76" customWidth="1"/>
-    <col min="10" max="10" width="36.42578125" customWidth="1"/>
-    <col min="11" max="11" width="24.5703125" customWidth="1"/>
+    <col min="1" max="2" width="36.44140625" customWidth="1"/>
+    <col min="3" max="8" width="27.88671875" customWidth="1"/>
+    <col min="9" max="9" width="36.44140625" style="62" customWidth="1"/>
+    <col min="10" max="10" width="36.44140625" customWidth="1"/>
+    <col min="11" max="11" width="24.5546875" customWidth="1"/>
     <col min="12" max="12" width="26" customWidth="1"/>
-    <col min="13" max="13" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="255.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="49" t="s">
-        <v>65</v>
+      <c r="B1" s="40" t="s">
+        <v>54</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="63" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="68">
+    </row>
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="54">
         <v>48156918.740000002</v>
       </c>
-      <c r="D2" s="46">
+      <c r="D2" s="37">
         <v>53387212.439999998</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="14">
         <f t="shared" ref="E2:E25" si="0">C2-D2</f>
         <v>-5230293.6999999955</v>
       </c>
-      <c r="F2" s="68">
+      <c r="F2" s="54">
         <f>C2+69000*30</f>
         <v>50226918.740000002</v>
       </c>
-      <c r="G2" s="68">
+      <c r="G2" s="54">
         <f>D2+69000*30</f>
         <v>55457212.439999998</v>
       </c>
-      <c r="H2" s="70">
+      <c r="H2" s="56">
         <f t="shared" ref="H2:H25" si="1">F2-G2</f>
         <v>-5230293.6999999955</v>
       </c>
-      <c r="I2" s="74"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="32">
+      <c r="I2" s="60"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="24">
         <v>0</v>
       </c>
-      <c r="M2" s="27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="60" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="56">
+      <c r="M2" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="42">
         <v>59525244</v>
       </c>
-      <c r="D3" s="56">
+      <c r="D3" s="42">
         <v>58080033</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="14">
         <f t="shared" si="0"/>
         <v>1445211</v>
       </c>
-      <c r="F3" s="69">
+      <c r="F3" s="55">
         <v>65435040</v>
       </c>
-      <c r="G3" s="69">
+      <c r="G3" s="55">
         <v>64131852</v>
       </c>
-      <c r="H3" s="70">
+      <c r="H3" s="56">
         <f t="shared" si="1"/>
         <v>1303188</v>
       </c>
-      <c r="I3" s="75">
+      <c r="I3" s="61">
         <f>H3/2</f>
         <v>651594</v>
       </c>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="58"/>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="47">
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="44"/>
+    </row>
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="38">
         <v>19331059</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="38">
         <v>19955779.719999999</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="14">
         <f t="shared" si="0"/>
         <v>-624720.71999999881</v>
       </c>
-      <c r="F4" s="70">
+      <c r="F4" s="56">
         <v>21050207.140000001</v>
       </c>
-      <c r="G4" s="70">
+      <c r="G4" s="56">
         <v>21674927.719999999</v>
       </c>
-      <c r="H4" s="70">
+      <c r="H4" s="56">
         <f t="shared" si="1"/>
         <v>-624720.57999999821</v>
       </c>
-      <c r="I4" s="30"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="32">
+      <c r="I4" s="22"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="24">
         <v>0.05</v>
       </c>
-      <c r="M4" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="47">
+      <c r="M4" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="38">
         <v>30874919.829999998</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="38">
         <v>35244059.479999997</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="14">
         <f t="shared" si="0"/>
         <v>-4369139.6499999985</v>
       </c>
-      <c r="F5" s="70">
+      <c r="F5" s="56">
         <v>33962411.810000002</v>
       </c>
-      <c r="G5" s="70">
+      <c r="G5" s="56">
         <v>38367858</v>
       </c>
-      <c r="H5" s="70">
+      <c r="H5" s="56">
         <f t="shared" si="1"/>
         <v>-4405446.1899999976</v>
       </c>
-      <c r="I5" s="75"/>
-      <c r="J5" s="29">
+      <c r="I5" s="61"/>
+      <c r="J5" s="21">
         <f>F5*1.02-G5</f>
         <v>-3726197.9538000003</v>
       </c>
-      <c r="K5" s="67">
+      <c r="K5" s="53">
         <f>E5-J5</f>
         <v>-642941.69619999826</v>
       </c>
-      <c r="L5" s="32">
+      <c r="L5" s="24">
         <v>0.02</v>
       </c>
-      <c r="M5" s="26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="61" t="s">
+      <c r="M5" s="18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="47">
+      <c r="B6" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="38">
         <v>150327077.33000001</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="38">
         <v>150520956.53</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="14">
         <f t="shared" si="0"/>
         <v>-193879.19999998808</v>
       </c>
-      <c r="F6" s="70">
+      <c r="F6" s="56">
         <f>C6+12000000</f>
         <v>162327077.33000001</v>
       </c>
-      <c r="G6" s="70">
+      <c r="G6" s="56">
         <f>D6+12000000</f>
         <v>162520956.53</v>
       </c>
-      <c r="H6" s="70">
+      <c r="H6" s="56">
         <f t="shared" si="1"/>
         <v>-193879.19999998808</v>
       </c>
-      <c r="I6" s="30"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="32">
+      <c r="I6" s="22"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="24">
         <v>0</v>
       </c>
-      <c r="M6" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="47">
+      <c r="M6" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="38">
         <v>39854406</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="38">
         <v>40338984</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="14">
         <f t="shared" si="0"/>
         <v>-484578</v>
       </c>
-      <c r="F7" s="70">
+      <c r="F7" s="56">
         <v>46829325</v>
       </c>
-      <c r="G7" s="70">
+      <c r="G7" s="56">
         <v>47401429</v>
       </c>
-      <c r="H7" s="70">
+      <c r="H7" s="56">
         <f t="shared" si="1"/>
         <v>-572104</v>
       </c>
-      <c r="I7" s="30"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="32">
+      <c r="I7" s="22"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="24">
         <v>0.05</v>
       </c>
-      <c r="M7" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="47">
+      <c r="M7" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="38">
         <v>62491370</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="38">
         <v>63861618</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="14">
         <f t="shared" si="0"/>
         <v>-1370248</v>
       </c>
-      <c r="F8" s="70">
+      <c r="F8" s="56">
         <v>72470092</v>
       </c>
-      <c r="G8" s="70">
+      <c r="G8" s="56">
         <v>73487464</v>
       </c>
-      <c r="H8" s="70">
+      <c r="H8" s="56">
         <f t="shared" si="1"/>
         <v>-1017372</v>
       </c>
-      <c r="I8" s="30"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="32">
+      <c r="I8" s="22"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="24">
         <v>0.05</v>
       </c>
-      <c r="M8" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="47">
+      <c r="M8" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="38">
         <v>45889672</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="38">
         <v>51065876</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <f t="shared" si="0"/>
         <v>-5176204</v>
       </c>
-      <c r="F9" s="70">
+      <c r="F9" s="56">
         <v>53560258</v>
       </c>
-      <c r="G9" s="70">
+      <c r="G9" s="56">
         <v>58251311</v>
       </c>
-      <c r="H9" s="70">
+      <c r="H9" s="56">
         <f t="shared" si="1"/>
         <v>-4691053</v>
       </c>
-      <c r="I9" s="30"/>
-      <c r="J9" s="29">
+      <c r="I9" s="22"/>
+      <c r="J9" s="21">
         <f>F9*1.05-G9</f>
         <v>-2013040.099999994</v>
       </c>
-      <c r="K9" s="72">
+      <c r="K9" s="58">
         <f>H9-J9</f>
         <v>-2678012.900000006</v>
       </c>
-      <c r="L9" s="32">
+      <c r="L9" s="24">
         <v>0.05</v>
       </c>
-      <c r="M9" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="47">
+      <c r="M9" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="38">
         <v>8442659</v>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="38">
         <v>7398017</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="14">
         <f t="shared" si="0"/>
         <v>1044642</v>
       </c>
-      <c r="F10" s="70">
+      <c r="F10" s="56">
         <v>9547400</v>
       </c>
-      <c r="G10" s="70">
+      <c r="G10" s="56">
         <v>8565310</v>
       </c>
-      <c r="H10" s="70">
+      <c r="H10" s="56">
         <f t="shared" si="1"/>
         <v>982090</v>
       </c>
-      <c r="I10" s="75">
+      <c r="I10" s="61">
         <f>H10/2</f>
         <v>491045</v>
       </c>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="32">
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="24">
         <v>0.05</v>
       </c>
-      <c r="M10" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="47">
+      <c r="M10" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="38">
         <v>100802866</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="38">
         <v>122850415</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="14">
         <f t="shared" si="0"/>
         <v>-22047549</v>
       </c>
-      <c r="F11" s="70">
+      <c r="F11" s="56">
         <v>119092682</v>
       </c>
-      <c r="G11" s="70">
+      <c r="G11" s="56">
         <v>141675593</v>
       </c>
-      <c r="H11" s="70">
+      <c r="H11" s="56">
         <f t="shared" si="1"/>
         <v>-22582911</v>
       </c>
-      <c r="I11" s="30"/>
-      <c r="J11" s="29">
+      <c r="I11" s="22"/>
+      <c r="J11" s="21">
         <f>F11*1.05-G11</f>
         <v>-16628276.899999991</v>
       </c>
-      <c r="K11" s="72">
+      <c r="K11" s="58">
         <f>H11-J11</f>
         <v>-5954634.1000000089</v>
       </c>
-      <c r="L11" s="32">
+      <c r="L11" s="24">
         <v>0.05</v>
       </c>
-      <c r="M11" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="61" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="47">
+      <c r="M11" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="38">
         <v>129823938</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="38">
         <v>122195945</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <f t="shared" si="0"/>
         <v>7627993</v>
       </c>
-      <c r="F12" s="70">
+      <c r="F12" s="56">
         <v>146118995</v>
       </c>
-      <c r="G12" s="70">
+      <c r="G12" s="56">
         <v>138624131</v>
       </c>
-      <c r="H12" s="70">
+      <c r="H12" s="56">
         <f t="shared" si="1"/>
         <v>7494864</v>
       </c>
-      <c r="I12" s="75">
+      <c r="I12" s="61">
         <f>H12/2</f>
         <v>3747432</v>
       </c>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="32">
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="24">
         <v>0.05</v>
       </c>
-      <c r="M12" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="47">
+      <c r="M12" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="38">
         <v>75712669</v>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="38">
         <v>73410513</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="14">
         <f t="shared" si="0"/>
         <v>2302156</v>
       </c>
-      <c r="F13" s="70">
+      <c r="F13" s="56">
         <v>87931471</v>
       </c>
-      <c r="G13" s="70">
+      <c r="G13" s="56">
         <v>86021054</v>
       </c>
-      <c r="H13" s="70">
+      <c r="H13" s="56">
         <f t="shared" si="1"/>
         <v>1910417</v>
       </c>
-      <c r="I13" s="75">
+      <c r="I13" s="61">
         <f>H13/2</f>
         <v>955208.5</v>
       </c>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="32">
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="24">
         <v>0.05</v>
       </c>
-      <c r="M13" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="61" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="47">
+      <c r="M13" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="38">
         <v>24795027</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="38">
         <v>26487463</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <f t="shared" si="0"/>
         <v>-1692436</v>
       </c>
-      <c r="F14" s="70">
+      <c r="F14" s="56">
         <v>28475524</v>
       </c>
-      <c r="G14" s="70">
+      <c r="G14" s="56">
         <v>30400424</v>
       </c>
-      <c r="H14" s="70">
+      <c r="H14" s="56">
         <f t="shared" si="1"/>
         <v>-1924900</v>
       </c>
-      <c r="I14" s="75"/>
-      <c r="J14" s="29">
+      <c r="I14" s="61"/>
+      <c r="J14" s="21">
         <f>F14*1.05-G14</f>
         <v>-501123.79999999702</v>
       </c>
-      <c r="K14" s="29"/>
-      <c r="L14" s="32">
+      <c r="K14" s="21"/>
+      <c r="L14" s="24">
         <v>0.05</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="47">
+      <c r="M14" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="38">
         <v>36372271</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="38">
         <v>32419520</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <f t="shared" si="0"/>
         <v>3952751</v>
       </c>
-      <c r="F15" s="70">
+      <c r="F15" s="56">
         <v>40149969</v>
       </c>
-      <c r="G15" s="70">
+      <c r="G15" s="56">
         <v>36213024</v>
       </c>
-      <c r="H15" s="70">
+      <c r="H15" s="56">
         <f t="shared" si="1"/>
         <v>3936945</v>
       </c>
-      <c r="I15" s="75">
+      <c r="I15" s="61">
         <f t="shared" ref="I15:I21" si="2">H15/2</f>
         <v>1968472.5</v>
       </c>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="32">
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="24">
         <v>0.05</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="47">
+      <c r="M15" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="38">
         <v>1365707</v>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="38">
         <v>1250665</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <f t="shared" si="0"/>
         <v>115042</v>
       </c>
-      <c r="F16" s="70">
+      <c r="F16" s="56">
         <v>1790524</v>
       </c>
-      <c r="G16" s="70">
+      <c r="G16" s="56">
         <v>1654734</v>
       </c>
-      <c r="H16" s="70">
+      <c r="H16" s="56">
         <f t="shared" si="1"/>
         <v>135790</v>
       </c>
-      <c r="I16" s="75">
+      <c r="I16" s="61">
         <f t="shared" si="2"/>
         <v>67895</v>
       </c>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="32">
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="24">
         <v>0.05</v>
       </c>
-      <c r="M16" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="47">
+      <c r="M16" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="38">
         <v>82688581</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="38">
         <v>80937877</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <f t="shared" si="0"/>
         <v>1750704</v>
       </c>
-      <c r="F17" s="70">
+      <c r="F17" s="56">
         <v>93683893</v>
       </c>
-      <c r="G17" s="70">
+      <c r="G17" s="56">
         <v>92050528</v>
       </c>
-      <c r="H17" s="70">
+      <c r="H17" s="56">
         <f t="shared" si="1"/>
         <v>1633365</v>
       </c>
-      <c r="I17" s="75">
+      <c r="I17" s="61">
         <f t="shared" si="2"/>
         <v>816682.5</v>
       </c>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="32">
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="24">
         <v>0.05</v>
       </c>
-      <c r="M17" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="47">
+      <c r="M17" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="38">
         <v>61763786</v>
       </c>
-      <c r="D18" s="47">
+      <c r="D18" s="38">
         <v>60160767</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="14">
         <f t="shared" si="0"/>
         <v>1603019</v>
       </c>
-      <c r="F18" s="70">
+      <c r="F18" s="56">
         <v>72678266</v>
       </c>
-      <c r="G18" s="70">
+      <c r="G18" s="56">
         <v>71428986</v>
       </c>
-      <c r="H18" s="70">
+      <c r="H18" s="56">
         <f t="shared" si="1"/>
         <v>1249280</v>
       </c>
-      <c r="I18" s="30">
+      <c r="I18" s="22">
         <f t="shared" si="2"/>
         <v>624640</v>
       </c>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="32">
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="24">
         <v>0.05</v>
       </c>
-      <c r="M18" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="61" t="s">
+      <c r="M18" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="47">
+    </row>
+    <row r="19" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="38">
         <v>33840813</v>
       </c>
-      <c r="D19" s="47">
+      <c r="D19" s="38">
         <v>33391850</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="14">
         <f t="shared" si="0"/>
         <v>448963</v>
       </c>
-      <c r="F19" s="70">
+      <c r="F19" s="56">
         <v>38072977</v>
       </c>
-      <c r="G19" s="70">
+      <c r="G19" s="56">
         <v>38037592</v>
       </c>
-      <c r="H19" s="70">
+      <c r="H19" s="56">
         <f t="shared" si="1"/>
         <v>35385</v>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="22">
         <f t="shared" si="2"/>
         <v>17692.5</v>
       </c>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="32">
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="24">
         <v>0.05</v>
       </c>
-      <c r="M19" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="47">
+      <c r="M19" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="38">
         <v>1946684</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="38">
         <v>1853035</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="14">
         <f t="shared" si="0"/>
         <v>93649</v>
       </c>
-      <c r="F20" s="70">
+      <c r="F20" s="56">
         <v>2352968</v>
       </c>
-      <c r="G20" s="70">
+      <c r="G20" s="56">
         <v>2285300</v>
       </c>
-      <c r="H20" s="70">
+      <c r="H20" s="56">
         <f t="shared" si="1"/>
         <v>67668</v>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="22">
         <f t="shared" si="2"/>
         <v>33834</v>
       </c>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="32">
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="24">
         <v>0.05</v>
       </c>
-      <c r="M20" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="48">
+      <c r="M20" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="39">
         <v>14696272</v>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="39">
         <v>14610275</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="17">
         <f t="shared" si="0"/>
         <v>85997</v>
       </c>
-      <c r="F21" s="71">
+      <c r="F21" s="57">
         <v>19083934</v>
       </c>
-      <c r="G21" s="71">
+      <c r="G21" s="57">
         <v>18860352</v>
       </c>
-      <c r="H21" s="71">
+      <c r="H21" s="57">
         <f t="shared" si="1"/>
         <v>223582</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="23">
         <f t="shared" si="2"/>
         <v>111791</v>
       </c>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="32">
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="24">
         <v>0.05</v>
       </c>
-      <c r="M21" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="77" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="79">
+      <c r="M21" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="65">
         <v>23961874</v>
       </c>
-      <c r="D22" s="79">
+      <c r="D22" s="65">
         <v>22426604.09</v>
       </c>
-      <c r="E22" s="78">
+      <c r="E22" s="64">
         <f t="shared" si="0"/>
         <v>1535269.9100000001</v>
       </c>
-      <c r="F22" s="78">
+      <c r="F22" s="64">
         <f>C22+1804851</f>
         <v>25766725</v>
       </c>
-      <c r="G22" s="78">
+      <c r="G22" s="64">
         <f>D22+1804851</f>
         <v>24231455.09</v>
       </c>
-      <c r="H22" s="71">
+      <c r="H22" s="57">
         <f t="shared" si="1"/>
         <v>1535269.9100000001</v>
       </c>
-      <c r="I22" s="80">
+      <c r="I22" s="66">
         <f>H22*0.4</f>
         <v>614107.96400000004</v>
       </c>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="81"/>
-      <c r="M22" s="82" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="65" t="s">
+      <c r="J22" s="66"/>
+      <c r="K22" s="66"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="79">
+    </row>
+    <row r="23" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="65">
         <v>109238942</v>
       </c>
-      <c r="D23" s="79">
+      <c r="D23" s="65">
         <v>109001590</v>
       </c>
-      <c r="E23" s="78">
+      <c r="E23" s="64">
         <f t="shared" si="0"/>
         <v>237352</v>
       </c>
-      <c r="F23" s="78">
+      <c r="F23" s="64">
         <v>121776982</v>
       </c>
-      <c r="G23" s="78">
+      <c r="G23" s="64">
         <v>121716005</v>
       </c>
-      <c r="H23" s="78">
+      <c r="H23" s="64">
         <f t="shared" si="1"/>
         <v>60977</v>
       </c>
-      <c r="I23" s="80">
+      <c r="I23" s="66">
         <f>H23/2</f>
         <v>30488.5</v>
       </c>
-      <c r="J23" s="29"/>
-      <c r="K23" s="80"/>
-      <c r="L23" s="32">
+      <c r="J23" s="21"/>
+      <c r="K23" s="66"/>
+      <c r="L23" s="24">
         <v>0.05</v>
       </c>
-      <c r="M23" s="82"/>
-    </row>
-    <row r="24" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="77" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="65" t="s">
+      <c r="M23" s="68"/>
+    </row>
+    <row r="24" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="79">
+      <c r="B24" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="65">
         <v>52846811</v>
       </c>
-      <c r="D24" s="79">
+      <c r="D24" s="65">
         <v>51158048</v>
       </c>
-      <c r="E24" s="78">
+      <c r="E24" s="64">
         <f t="shared" si="0"/>
         <v>1688763</v>
       </c>
-      <c r="F24" s="78">
+      <c r="F24" s="64">
         <f>C24+4392755</f>
         <v>57239566</v>
       </c>
-      <c r="G24" s="78">
+      <c r="G24" s="64">
         <f>D24+4392755</f>
         <v>55550803</v>
       </c>
-      <c r="H24" s="78">
+      <c r="H24" s="64">
         <f t="shared" si="1"/>
         <v>1688763</v>
       </c>
-      <c r="I24" s="80">
+      <c r="I24" s="66">
         <f>H24*0.4</f>
         <v>675505.20000000007</v>
       </c>
-      <c r="J24" s="29"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="81">
+      <c r="J24" s="21"/>
+      <c r="K24" s="66"/>
+      <c r="L24" s="67">
         <v>0.04</v>
       </c>
-      <c r="M24" s="82" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="77" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="79">
+      <c r="M24" s="68" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="65">
         <v>22244837</v>
       </c>
-      <c r="D25" s="83">
+      <c r="D25" s="69">
         <v>22328076</v>
       </c>
-      <c r="E25" s="78">
+      <c r="E25" s="64">
         <f t="shared" si="0"/>
         <v>-83239</v>
       </c>
-      <c r="F25" s="84">
+      <c r="F25" s="70">
         <f>C25+1908100</f>
         <v>24152937</v>
       </c>
-      <c r="G25" s="84">
+      <c r="G25" s="70">
         <f>D25+1908100</f>
         <v>24236176</v>
       </c>
-      <c r="H25" s="78">
+      <c r="H25" s="64">
         <f t="shared" si="1"/>
         <v>-83239</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="73"/>
+    <row r="26" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="59"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L21" xr:uid="{F826C8AD-E55D-43EC-8E13-5835E0D42917}"/>

--- a/INFORMAÇÕES_PROJETOS.xlsx
+++ b/INFORMAÇÕES_PROJETOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HomePC\.gemini\antigravity-ide\scratch\analise-dre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FB826C-3122-4368-9A26-D94C0D47D88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF744CD-C47E-46B2-977E-84C94F8F53F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="706" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="706" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="10" state="hidden" r:id="rId1"/>
@@ -739,7 +739,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -950,12 +950,11 @@
     <xf numFmtId="16" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1349,17 +1348,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BCC6A2B-3058-4004-816D-7182CED8014F}">
   <dimension ref="A1:I134"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.109375" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1379,7 +1378,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1400,7 +1399,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1421,7 +1420,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1442,7 +1441,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1463,7 +1462,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1484,7 +1483,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1505,7 +1504,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1526,7 +1525,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1547,7 +1546,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1568,7 +1567,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1589,7 +1588,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1610,7 +1609,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1631,7 +1630,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1652,7 +1651,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1673,7 +1672,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1694,7 +1693,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1715,7 +1714,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1736,7 +1735,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1757,7 +1756,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1778,7 +1777,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1799,7 +1798,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1820,7 +1819,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1841,7 +1840,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1862,7 +1861,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1883,7 +1882,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1902,7 +1901,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1921,7 +1920,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1940,7 +1939,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1959,7 +1958,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1978,7 +1977,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1997,7 +1996,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -2016,7 +2015,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -2035,7 +2034,7 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -2056,7 +2055,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -2077,7 +2076,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -2098,7 +2097,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -2119,7 +2118,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -2140,7 +2139,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -2161,7 +2160,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -2182,7 +2181,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -2203,7 +2202,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -2224,7 +2223,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -2245,7 +2244,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -2266,7 +2265,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -2287,7 +2286,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -2308,7 +2307,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -2329,7 +2328,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -2350,7 +2349,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -2371,7 +2370,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -2392,7 +2391,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -2413,7 +2412,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -2434,7 +2433,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -2455,7 +2454,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -2476,7 +2475,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -2497,7 +2496,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -2518,7 +2517,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -2539,7 +2538,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -2558,7 +2557,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -2577,7 +2576,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -2596,7 +2595,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -2615,7 +2614,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -2634,7 +2633,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -2653,7 +2652,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -2672,7 +2671,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -2691,7 +2690,7 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -2719,7 +2718,7 @@
         <v>2.5976243171854298E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -2747,7 +2746,7 @@
         <v>4.4489038312087614E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -2775,7 +2774,7 @@
         <v>4.9493272643934147E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -2803,7 +2802,7 @@
         <v>4.9113724641000805E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>4</v>
       </c>
@@ -2834,7 +2833,7 @@
         <v>6.3615727856344131E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>4</v>
       </c>
@@ -2855,7 +2854,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>4</v>
       </c>
@@ -2876,7 +2875,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>4</v>
       </c>
@@ -2897,7 +2896,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>4</v>
       </c>
@@ -2918,7 +2917,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -2937,7 +2936,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>4</v>
       </c>
@@ -2956,7 +2955,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -2975,7 +2974,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -2994,7 +2993,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -3013,7 +3012,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -3032,7 +3031,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -3051,7 +3050,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -3070,7 +3069,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -3089,7 +3088,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -3108,7 +3107,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -3127,7 +3126,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -3146,7 +3145,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -3165,7 +3164,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -3184,7 +3183,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -3223,7 +3222,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -3243,7 +3242,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -3263,7 +3262,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -3283,7 +3282,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -3303,7 +3302,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>4</v>
       </c>
@@ -3323,7 +3322,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -3343,7 +3342,7 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -3363,8 +3362,8 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -3383,7 +3382,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>4</v>
       </c>
@@ -3402,7 +3401,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>4</v>
       </c>
@@ -3421,7 +3420,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>4</v>
       </c>
@@ -3440,7 +3439,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>4</v>
       </c>
@@ -3459,7 +3458,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -3478,7 +3477,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -3497,7 +3496,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -3516,7 +3515,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -3535,7 +3534,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>4</v>
       </c>
@@ -3554,7 +3553,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>4</v>
       </c>
@@ -3573,7 +3572,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>4</v>
       </c>
@@ -3592,7 +3591,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>4</v>
       </c>
@@ -3611,7 +3610,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>4</v>
       </c>
@@ -3630,7 +3629,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -3649,7 +3648,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>4</v>
       </c>
@@ -3668,7 +3667,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>4</v>
       </c>
@@ -3687,7 +3686,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>4</v>
       </c>
@@ -3706,7 +3705,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>4</v>
       </c>
@@ -3725,7 +3724,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>4</v>
       </c>
@@ -3744,7 +3743,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -3763,7 +3762,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -3782,7 +3781,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>4</v>
       </c>
@@ -3801,7 +3800,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>4</v>
       </c>
@@ -3820,7 +3819,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -3840,7 +3839,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -3860,7 +3859,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>4</v>
       </c>
@@ -3880,7 +3879,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -3900,7 +3899,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -3920,7 +3919,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -3940,7 +3939,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -3960,7 +3959,7 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>4</v>
       </c>
@@ -3989,26 +3988,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B648EA-C9CF-4199-AC21-3B599FE2C0B5}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="20.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="12" width="15.5546875" customWidth="1"/>
-    <col min="13" max="13" width="25.88671875" customWidth="1"/>
+    <col min="9" max="12" width="15.5703125" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" customWidth="1"/>
     <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="42.88671875" customWidth="1"/>
-    <col min="16" max="16" width="15.88671875" customWidth="1"/>
-    <col min="17" max="17" width="15.44140625" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" customWidth="1"/>
+    <col min="15" max="15" width="42.85546875" customWidth="1"/>
+    <col min="16" max="16" width="15.85546875" customWidth="1"/>
+    <col min="17" max="17" width="15.42578125" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" customWidth="1"/>
     <col min="19" max="19" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -4067,7 +4066,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="45" t="s">
         <v>14</v>
       </c>
@@ -4129,7 +4128,7 @@
         <v>4.9500000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="46" t="s">
         <v>57</v>
       </c>
@@ -4192,7 +4191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="47" t="s">
         <v>16</v>
       </c>
@@ -4231,7 +4230,7 @@
         <v>24</v>
       </c>
       <c r="L4" s="31">
-        <f t="shared" ref="L3:L25" si="4">K4*J4</f>
+        <f t="shared" ref="L4:L25" si="4">K4*J4</f>
         <v>1382966.16</v>
       </c>
       <c r="M4" s="35"/>
@@ -4255,7 +4254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="47" t="s">
         <v>76</v>
       </c>
@@ -4317,7 +4316,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>77</v>
       </c>
@@ -4379,7 +4378,7 @@
         <v>3.9599999999999996E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="47" t="s">
         <v>20</v>
       </c>
@@ -4442,7 +4441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>22</v>
       </c>
@@ -4505,7 +4504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="47" t="s">
         <v>23</v>
       </c>
@@ -4569,7 +4568,7 @@
         <v>1.9799999999999998E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>24</v>
       </c>
@@ -4632,7 +4631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
         <v>25</v>
       </c>
@@ -4696,7 +4695,7 @@
         <v>4.9500000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
         <v>26</v>
       </c>
@@ -4760,7 +4759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
         <v>27</v>
       </c>
@@ -4822,7 +4821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
         <v>28</v>
       </c>
@@ -4884,7 +4883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
         <v>29</v>
       </c>
@@ -4946,7 +4945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="47" t="s">
         <v>30</v>
       </c>
@@ -5008,7 +5007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
         <v>31</v>
       </c>
@@ -5070,7 +5069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
         <v>32</v>
       </c>
@@ -5132,7 +5131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
         <v>33</v>
       </c>
@@ -5194,7 +5193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="47" t="s">
         <v>61</v>
       </c>
@@ -5256,7 +5255,7 @@
         <v>1.9799999999999998E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48" t="s">
         <v>62</v>
       </c>
@@ -5317,7 +5316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="63" t="s">
         <v>80</v>
       </c>
@@ -5374,7 +5373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="63" t="s">
         <v>63</v>
       </c>
@@ -5434,7 +5433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="63" t="s">
         <v>79</v>
       </c>
@@ -5494,7 +5493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="63" t="s">
         <v>78</v>
       </c>
@@ -5535,7 +5534,7 @@
       <c r="N25" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="O25" s="79" t="s">
+      <c r="O25" t="s">
         <v>96</v>
       </c>
       <c r="P25" s="28">
@@ -5544,7 +5543,7 @@
       <c r="Q25" s="65">
         <v>22244837</v>
       </c>
-      <c r="R25" s="80">
+      <c r="R25" s="8">
         <f>IF(I25&gt;0,Q25*P25,0)</f>
         <v>0</v>
       </c>
@@ -5562,19 +5561,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9847408C-B23C-4D48-83D1-CB6301E525D5}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M29"/>
+  <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="36.44140625" customWidth="1"/>
-    <col min="3" max="8" width="27.88671875" customWidth="1"/>
-    <col min="9" max="9" width="36.44140625" style="62" customWidth="1"/>
-    <col min="10" max="10" width="36.44140625" customWidth="1"/>
-    <col min="11" max="11" width="24.5546875" customWidth="1"/>
+    <col min="1" max="2" width="36.42578125" customWidth="1"/>
+    <col min="3" max="8" width="27.85546875" customWidth="1"/>
+    <col min="9" max="9" width="36.42578125" style="62" customWidth="1"/>
+    <col min="10" max="10" width="36.42578125" customWidth="1"/>
+    <col min="11" max="11" width="24.5703125" customWidth="1"/>
     <col min="12" max="12" width="26" customWidth="1"/>
-    <col min="13" max="13" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -5615,7 +5614,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
         <v>14</v>
       </c>
@@ -5645,7 +5644,10 @@
         <v>-5230293.6999999955</v>
       </c>
       <c r="I2" s="60"/>
-      <c r="J2" s="20"/>
+      <c r="J2" s="79">
+        <f>H2</f>
+        <v>-5230293.6999999955</v>
+      </c>
       <c r="K2" s="20"/>
       <c r="L2" s="24">
         <v>0</v>
@@ -5654,7 +5656,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="46" t="s">
         <v>57</v>
       </c>
@@ -5690,7 +5692,7 @@
       <c r="L3" s="24"/>
       <c r="M3" s="44"/>
     </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="47" t="s">
         <v>16</v>
       </c>
@@ -5727,7 +5729,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
         <v>4</v>
       </c>
@@ -5770,7 +5772,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
         <v>3</v>
       </c>
@@ -5809,7 +5811,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
         <v>20</v>
       </c>
@@ -5846,7 +5848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
         <v>22</v>
       </c>
@@ -5883,7 +5885,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
         <v>23</v>
       </c>
@@ -5926,7 +5928,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="s">
         <v>24</v>
       </c>
@@ -5966,7 +5968,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
         <v>25</v>
       </c>
@@ -6009,7 +6011,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="47" t="s">
         <v>26</v>
       </c>
@@ -6049,7 +6051,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="47" t="s">
         <v>27</v>
       </c>
@@ -6089,7 +6091,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="s">
         <v>28</v>
       </c>
@@ -6129,7 +6131,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="47" t="s">
         <v>29</v>
       </c>
@@ -6169,7 +6171,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="47" t="s">
         <v>30</v>
       </c>
@@ -6209,7 +6211,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="47" t="s">
         <v>31</v>
       </c>
@@ -6249,7 +6251,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="s">
         <v>32</v>
       </c>
@@ -6289,7 +6291,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="47" t="s">
         <v>33</v>
       </c>
@@ -6329,7 +6331,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="47" t="s">
         <v>61</v>
       </c>
@@ -6369,7 +6371,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48" t="s">
         <v>62</v>
       </c>
@@ -6409,7 +6411,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="63" t="s">
         <v>67</v>
       </c>
@@ -6449,7 +6451,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="63" t="s">
         <v>63</v>
       </c>
@@ -6487,7 +6489,7 @@
       </c>
       <c r="M23" s="68"/>
     </row>
-    <row r="24" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="63" t="s">
         <v>64</v>
       </c>
@@ -6529,7 +6531,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="63" t="s">
         <v>65</v>
       </c>
@@ -6559,8 +6561,14 @@
         <v>-83239</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="59"/>
+    </row>
+    <row r="29" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J29">
+        <f>K15</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L21" xr:uid="{F826C8AD-E55D-43EC-8E13-5835E0D42917}"/>

--- a/INFORMAÇÕES_PROJETOS.xlsx
+++ b/INFORMAÇÕES_PROJETOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HomePC\.gemini\antigravity-ide\scratch\analise-dre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF744CD-C47E-46B2-977E-84C94F8F53F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52994B1-8463-4E53-A436-A34225F1D57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="706" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="706" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="10" state="hidden" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="99">
   <si>
     <t>Data</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>Custo orçamento</t>
+  </si>
+  <si>
+    <t>Manacás</t>
   </si>
 </sst>
 </file>
@@ -730,7 +733,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -738,8 +741,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -756,18 +763,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -777,13 +772,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -933,7 +922,6 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -946,25 +934,94 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="3" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="11">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Moeda 2" xfId="3" xr:uid="{C0FF9126-00DE-4190-9C3C-F6D7468CCAAC}"/>
+    <cellStyle name="Moeda 2 2" xfId="8" xr:uid="{22319C29-7133-4769-9B31-E72B5FAA01C8}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="5" xr:uid="{656CAE0D-1432-40E1-81CE-6AA4FCD47D9B}"/>
     <cellStyle name="Normal 3" xfId="4" xr:uid="{EBE32B57-3A64-47D9-86CD-CFBCAE7F9C6A}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
+    <cellStyle name="Vírgula" xfId="7" builtinId="3"/>
     <cellStyle name="Vírgula 2" xfId="6" xr:uid="{89465CD8-BC01-4B98-945C-EFB7C7259A58}"/>
+    <cellStyle name="Vírgula 2 2" xfId="9" xr:uid="{93CF2253-3E0F-433A-9121-5729E6685649}"/>
+    <cellStyle name="Vírgula 3" xfId="10" xr:uid="{0E7D6DEA-73F3-4B73-B1B3-AB786BEF434C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1348,17 +1405,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BCC6A2B-3058-4004-816D-7182CED8014F}">
   <dimension ref="A1:I134"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1368,7 +1425,7 @@
       <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="19" t="s">
         <v>43</v>
       </c>
       <c r="E1" t="s">
@@ -1378,14 +1435,14 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="21">
         <v>45170</v>
       </c>
       <c r="D2">
@@ -1399,14 +1456,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="21">
         <v>45200</v>
       </c>
       <c r="D3">
@@ -1420,14 +1477,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="21">
         <v>45231</v>
       </c>
       <c r="D4">
@@ -1441,14 +1498,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="21">
         <v>45261</v>
       </c>
       <c r="D5">
@@ -1462,14 +1519,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="21">
         <v>45292</v>
       </c>
       <c r="D6">
@@ -1483,14 +1540,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="21">
         <v>45323</v>
       </c>
       <c r="D7">
@@ -1504,14 +1561,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="21">
         <v>45352</v>
       </c>
       <c r="D8">
@@ -1525,14 +1582,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="21">
         <v>45383</v>
       </c>
       <c r="D9">
@@ -1546,14 +1603,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="21">
         <v>45413</v>
       </c>
       <c r="D10">
@@ -1567,14 +1624,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
       <c r="B11" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="21">
         <v>45444</v>
       </c>
       <c r="D11">
@@ -1588,14 +1645,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
       <c r="B12" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="21">
         <v>45474</v>
       </c>
       <c r="D12">
@@ -1609,14 +1666,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="B13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="21">
         <v>45505</v>
       </c>
       <c r="D13">
@@ -1630,14 +1687,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="B14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="21">
         <v>45536</v>
       </c>
       <c r="D14">
@@ -1651,14 +1708,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
       <c r="B15" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="21">
         <v>45566</v>
       </c>
       <c r="D15">
@@ -1672,14 +1729,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
       <c r="B16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="21">
         <v>45597</v>
       </c>
       <c r="D16">
@@ -1693,14 +1750,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
       <c r="B17" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="21">
         <v>45627</v>
       </c>
       <c r="D17">
@@ -1714,14 +1771,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
       <c r="B18" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="21">
         <v>45658</v>
       </c>
       <c r="D18">
@@ -1735,14 +1792,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
       <c r="B19" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="21">
         <v>45689</v>
       </c>
       <c r="D19">
@@ -1756,14 +1813,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
       <c r="B20" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="21">
         <v>45717</v>
       </c>
       <c r="D20">
@@ -1777,14 +1834,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
       <c r="B21" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="21">
         <v>45748</v>
       </c>
       <c r="D21">
@@ -1798,14 +1855,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="21">
         <v>45778</v>
       </c>
       <c r="D22">
@@ -1819,14 +1876,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
       <c r="B23" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="21">
         <v>45809</v>
       </c>
       <c r="D23">
@@ -1840,14 +1897,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
       <c r="B24" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="21">
         <v>45839</v>
       </c>
       <c r="D24">
@@ -1861,14 +1918,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
       <c r="B25" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="21">
         <v>45870</v>
       </c>
       <c r="D25">
@@ -1882,14 +1939,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
       <c r="B26" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="21">
         <f>EDATE(C25,1)</f>
         <v>45901</v>
       </c>
@@ -1901,14 +1958,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="21">
         <f t="shared" ref="C27:C29" si="1">EDATE(C26,1)</f>
         <v>45931</v>
       </c>
@@ -1920,14 +1977,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="21">
         <f t="shared" si="1"/>
         <v>45962</v>
       </c>
@@ -1939,14 +1996,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="21">
         <f t="shared" si="1"/>
         <v>45992</v>
       </c>
@@ -1958,14 +2015,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="21">
         <f t="shared" ref="C30:C33" si="2">EDATE(C29,1)</f>
         <v>46023</v>
       </c>
@@ -1977,14 +2034,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>4</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="21">
         <f t="shared" si="2"/>
         <v>46054</v>
       </c>
@@ -1996,14 +2053,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="21">
         <f t="shared" si="2"/>
         <v>46082</v>
       </c>
@@ -2015,14 +2072,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>4</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="21">
         <f t="shared" si="2"/>
         <v>46113</v>
       </c>
@@ -2034,14 +2091,14 @@
         <v>HALL DESIGN Margem</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>4</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="21">
         <v>45170</v>
       </c>
       <c r="D35">
@@ -2055,14 +2112,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
       <c r="B36" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="21">
         <v>45200</v>
       </c>
       <c r="D36">
@@ -2076,14 +2133,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>4</v>
       </c>
       <c r="B37" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="21">
         <v>45231</v>
       </c>
       <c r="D37">
@@ -2097,14 +2154,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>4</v>
       </c>
       <c r="B38" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="21">
         <v>45261</v>
       </c>
       <c r="D38">
@@ -2118,14 +2175,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="21">
         <v>45292</v>
       </c>
       <c r="D39">
@@ -2139,14 +2196,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="21">
         <v>45323</v>
       </c>
       <c r="D40">
@@ -2160,14 +2217,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="21">
         <v>45352</v>
       </c>
       <c r="D41">
@@ -2181,14 +2238,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="21">
         <v>45383</v>
       </c>
       <c r="D42">
@@ -2202,14 +2259,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="21">
         <v>45413</v>
       </c>
       <c r="D43">
@@ -2223,14 +2280,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>4</v>
       </c>
       <c r="B44" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="21">
         <v>45444</v>
       </c>
       <c r="D44">
@@ -2244,14 +2301,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>4</v>
       </c>
       <c r="B45" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="21">
         <v>45474</v>
       </c>
       <c r="D45">
@@ -2265,14 +2322,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>4</v>
       </c>
       <c r="B46" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="21">
         <v>45505</v>
       </c>
       <c r="D46">
@@ -2286,14 +2343,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>4</v>
       </c>
       <c r="B47" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="21">
         <v>45536</v>
       </c>
       <c r="D47">
@@ -2307,14 +2364,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>4</v>
       </c>
       <c r="B48" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="21">
         <v>45566</v>
       </c>
       <c r="D48">
@@ -2328,14 +2385,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>4</v>
       </c>
       <c r="B49" t="s">
         <v>47</v>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="21">
         <v>45597</v>
       </c>
       <c r="D49">
@@ -2349,14 +2406,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>4</v>
       </c>
       <c r="B50" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="21">
         <v>45627</v>
       </c>
       <c r="D50">
@@ -2370,14 +2427,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>4</v>
       </c>
       <c r="B51" t="s">
         <v>47</v>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="21">
         <v>45658</v>
       </c>
       <c r="D51">
@@ -2391,14 +2448,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>4</v>
       </c>
       <c r="B52" t="s">
         <v>47</v>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="21">
         <v>45689</v>
       </c>
       <c r="D52">
@@ -2412,14 +2469,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>4</v>
       </c>
       <c r="B53" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="21">
         <v>45717</v>
       </c>
       <c r="D53">
@@ -2433,14 +2490,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>4</v>
       </c>
       <c r="B54" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="21">
         <v>45748</v>
       </c>
       <c r="D54">
@@ -2454,14 +2511,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>4</v>
       </c>
       <c r="B55" t="s">
         <v>47</v>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="21">
         <v>45778</v>
       </c>
       <c r="D55">
@@ -2475,14 +2532,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>4</v>
       </c>
       <c r="B56" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="21">
         <v>45809</v>
       </c>
       <c r="D56">
@@ -2496,14 +2553,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>4</v>
       </c>
       <c r="B57" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="21">
         <v>45839</v>
       </c>
       <c r="D57">
@@ -2517,14 +2574,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>4</v>
       </c>
       <c r="B58" t="s">
         <v>47</v>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="21">
         <v>45870</v>
       </c>
       <c r="D58">
@@ -2538,14 +2595,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>4</v>
       </c>
       <c r="B59" t="s">
         <v>47</v>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="21">
         <f>EDATE(C58,1)</f>
         <v>45901</v>
       </c>
@@ -2557,14 +2614,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>4</v>
       </c>
       <c r="B60" t="s">
         <v>47</v>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="21">
         <f t="shared" ref="C60:C66" si="4">EDATE(C59,1)</f>
         <v>45931</v>
       </c>
@@ -2576,14 +2633,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>4</v>
       </c>
       <c r="B61" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="21">
         <f t="shared" si="4"/>
         <v>45962</v>
       </c>
@@ -2595,14 +2652,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>4</v>
       </c>
       <c r="B62" t="s">
         <v>47</v>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="21">
         <f t="shared" si="4"/>
         <v>45992</v>
       </c>
@@ -2614,14 +2671,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>4</v>
       </c>
       <c r="B63" t="s">
         <v>47</v>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="21">
         <f t="shared" si="4"/>
         <v>46023</v>
       </c>
@@ -2633,14 +2690,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>4</v>
       </c>
       <c r="B64" t="s">
         <v>47</v>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="21">
         <f t="shared" si="4"/>
         <v>46054</v>
       </c>
@@ -2652,14 +2709,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>4</v>
       </c>
       <c r="B65" t="s">
         <v>47</v>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="21">
         <f t="shared" si="4"/>
         <v>46082</v>
       </c>
@@ -2671,14 +2728,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>4</v>
       </c>
       <c r="B66" t="s">
         <v>47</v>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="21">
         <f t="shared" si="4"/>
         <v>46113</v>
       </c>
@@ -2690,14 +2747,14 @@
         <v>HALL DESIGN Resultado</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>4</v>
       </c>
       <c r="B69" t="s">
         <v>48</v>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="21">
         <v>45170</v>
       </c>
       <c r="E69" t="s">
@@ -2707,25 +2764,25 @@
         <f>A69&amp;" "&amp;B69</f>
         <v>HALL DESIGN Despesas ADM</v>
       </c>
-      <c r="G69" s="29">
+      <c r="G69" s="23">
         <v>58347.72</v>
       </c>
       <c r="H69">
         <v>2246195.4800000004</v>
       </c>
-      <c r="I69" s="30">
+      <c r="I69" s="24">
         <f>G69/H69</f>
         <v>2.5976243171854298E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>4</v>
       </c>
       <c r="B70" t="s">
         <v>48</v>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="21">
         <v>45200</v>
       </c>
       <c r="E70" t="s">
@@ -2735,25 +2792,25 @@
         <f t="shared" ref="F70:F100" si="5">A70&amp;" "&amp;B70</f>
         <v>HALL DESIGN Despesas ADM</v>
       </c>
-      <c r="G70" s="29">
+      <c r="G70" s="23">
         <v>96382.45</v>
       </c>
       <c r="H70">
         <v>2166431.41</v>
       </c>
-      <c r="I70" s="30">
+      <c r="I70" s="24">
         <f t="shared" ref="I70:I73" si="6">G70/H70</f>
         <v>4.4489038312087614E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>4</v>
       </c>
       <c r="B71" t="s">
         <v>48</v>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="21">
         <v>45231</v>
       </c>
       <c r="E71" t="s">
@@ -2763,25 +2820,25 @@
         <f t="shared" si="5"/>
         <v>HALL DESIGN Despesas ADM</v>
       </c>
-      <c r="G71" s="29">
+      <c r="G71" s="23">
         <v>96730.39</v>
       </c>
       <c r="H71">
         <v>1954414.9099999997</v>
       </c>
-      <c r="I71" s="30">
+      <c r="I71" s="24">
         <f t="shared" si="6"/>
         <v>4.9493272643934147E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>4</v>
       </c>
       <c r="B72" t="s">
         <v>48</v>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="21">
         <v>45261</v>
       </c>
       <c r="E72" t="s">
@@ -2791,28 +2848,28 @@
         <f t="shared" si="5"/>
         <v>HALL DESIGN Despesas ADM</v>
       </c>
-      <c r="G72" s="29">
+      <c r="G72" s="23">
         <v>97200.11</v>
       </c>
       <c r="H72">
         <v>1979082.44</v>
       </c>
-      <c r="I72" s="30">
+      <c r="I72" s="24">
         <f t="shared" si="6"/>
         <v>4.9113724641000805E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>4</v>
       </c>
       <c r="B73" t="s">
         <v>48</v>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="21">
         <v>45292</v>
       </c>
-      <c r="D73" s="26">
+      <c r="D73" s="20">
         <v>2.5976243171854298E-2</v>
       </c>
       <c r="E73" t="s">
@@ -2822,28 +2879,28 @@
         <f t="shared" si="5"/>
         <v>HALL DESIGN Despesas ADM</v>
       </c>
-      <c r="G73" s="29">
+      <c r="G73" s="23">
         <v>138632.12</v>
       </c>
       <c r="H73">
         <v>2179211.41</v>
       </c>
-      <c r="I73" s="30">
+      <c r="I73" s="24">
         <f t="shared" si="6"/>
         <v>6.3615727856344131E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>4</v>
       </c>
       <c r="B74" t="s">
         <v>48</v>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="21">
         <v>45323</v>
       </c>
-      <c r="D74" s="26">
+      <c r="D74" s="20">
         <v>4.4489038312087614E-2</v>
       </c>
       <c r="E74" t="s">
@@ -2854,17 +2911,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>4</v>
       </c>
       <c r="B75" t="s">
         <v>48</v>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="21">
         <v>45352</v>
       </c>
-      <c r="D75" s="26">
+      <c r="D75" s="20">
         <v>4.9493272643934147E-2</v>
       </c>
       <c r="E75" t="s">
@@ -2875,17 +2932,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>4</v>
       </c>
       <c r="B76" t="s">
         <v>48</v>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="21">
         <v>45383</v>
       </c>
-      <c r="D76" s="26">
+      <c r="D76" s="20">
         <v>4.9113724641000805E-2</v>
       </c>
       <c r="E76" t="s">
@@ -2896,17 +2953,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>4</v>
       </c>
       <c r="B77" t="s">
         <v>48</v>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="21">
         <v>45413</v>
       </c>
-      <c r="D77" s="26">
+      <c r="D77" s="20">
         <v>6.3615727856344131E-2</v>
       </c>
       <c r="E77" t="s">
@@ -2917,17 +2974,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>4</v>
       </c>
       <c r="B78" t="s">
         <v>48</v>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="21">
         <v>45444</v>
       </c>
-      <c r="D78" s="28"/>
+      <c r="D78" s="22"/>
       <c r="E78" t="s">
         <v>1</v>
       </c>
@@ -2936,17 +2993,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>4</v>
       </c>
       <c r="B79" t="s">
         <v>48</v>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="21">
         <v>45474</v>
       </c>
-      <c r="D79" s="28"/>
+      <c r="D79" s="22"/>
       <c r="E79" t="s">
         <v>1</v>
       </c>
@@ -2955,17 +3012,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>4</v>
       </c>
       <c r="B80" t="s">
         <v>48</v>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="21">
         <v>45505</v>
       </c>
-      <c r="D80" s="28"/>
+      <c r="D80" s="22"/>
       <c r="E80" t="s">
         <v>1</v>
       </c>
@@ -2974,17 +3031,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>4</v>
       </c>
       <c r="B81" t="s">
         <v>48</v>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="21">
         <v>45536</v>
       </c>
-      <c r="D81" s="28"/>
+      <c r="D81" s="22"/>
       <c r="E81" t="s">
         <v>1</v>
       </c>
@@ -2993,17 +3050,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>4</v>
       </c>
       <c r="B82" t="s">
         <v>48</v>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="21">
         <v>45566</v>
       </c>
-      <c r="D82" s="28"/>
+      <c r="D82" s="22"/>
       <c r="E82" t="s">
         <v>1</v>
       </c>
@@ -3012,17 +3069,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>4</v>
       </c>
       <c r="B83" t="s">
         <v>48</v>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="21">
         <v>45597</v>
       </c>
-      <c r="D83" s="28"/>
+      <c r="D83" s="22"/>
       <c r="E83" t="s">
         <v>1</v>
       </c>
@@ -3031,17 +3088,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>4</v>
       </c>
       <c r="B84" t="s">
         <v>48</v>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="21">
         <v>45627</v>
       </c>
-      <c r="D84" s="28"/>
+      <c r="D84" s="22"/>
       <c r="E84" t="s">
         <v>1</v>
       </c>
@@ -3050,17 +3107,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>4</v>
       </c>
       <c r="B85" t="s">
         <v>48</v>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="21">
         <v>45658</v>
       </c>
-      <c r="D85" s="28"/>
+      <c r="D85" s="22"/>
       <c r="E85" t="s">
         <v>1</v>
       </c>
@@ -3069,17 +3126,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>4</v>
       </c>
       <c r="B86" t="s">
         <v>48</v>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="21">
         <v>45689</v>
       </c>
-      <c r="D86" s="28"/>
+      <c r="D86" s="22"/>
       <c r="E86" t="s">
         <v>1</v>
       </c>
@@ -3088,17 +3145,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>4</v>
       </c>
       <c r="B87" t="s">
         <v>48</v>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="21">
         <v>45717</v>
       </c>
-      <c r="D87" s="28"/>
+      <c r="D87" s="22"/>
       <c r="E87" t="s">
         <v>1</v>
       </c>
@@ -3107,17 +3164,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>4</v>
       </c>
       <c r="B88" t="s">
         <v>48</v>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="21">
         <v>45748</v>
       </c>
-      <c r="D88" s="28"/>
+      <c r="D88" s="22"/>
       <c r="E88" t="s">
         <v>1</v>
       </c>
@@ -3126,17 +3183,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>4</v>
       </c>
       <c r="B89" t="s">
         <v>48</v>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="21">
         <v>45778</v>
       </c>
-      <c r="D89" s="28"/>
+      <c r="D89" s="22"/>
       <c r="E89" t="s">
         <v>1</v>
       </c>
@@ -3145,17 +3202,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>4</v>
       </c>
       <c r="B90" t="s">
         <v>48</v>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="21">
         <v>45809</v>
       </c>
-      <c r="D90" s="28"/>
+      <c r="D90" s="22"/>
       <c r="E90" t="s">
         <v>1</v>
       </c>
@@ -3164,17 +3221,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>4</v>
       </c>
       <c r="B91" t="s">
         <v>48</v>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="21">
         <v>45839</v>
       </c>
-      <c r="D91" s="28"/>
+      <c r="D91" s="22"/>
       <c r="E91" t="s">
         <v>1</v>
       </c>
@@ -3183,17 +3240,17 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>4</v>
       </c>
       <c r="B92" t="s">
         <v>48</v>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="21">
         <v>45870</v>
       </c>
-      <c r="D92" s="28"/>
+      <c r="D92" s="22"/>
       <c r="E92" t="s">
         <v>1</v>
       </c>
@@ -3202,18 +3259,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>4</v>
       </c>
       <c r="B93" t="s">
         <v>48</v>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="21">
         <f>EDATE(C92,1)</f>
         <v>45901</v>
       </c>
-      <c r="D93" s="28"/>
+      <c r="D93" s="22"/>
       <c r="E93" t="s">
         <v>1</v>
       </c>
@@ -3222,18 +3279,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>4</v>
       </c>
       <c r="B94" t="s">
         <v>48</v>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="21">
         <f t="shared" ref="C94:C100" si="7">EDATE(C93,1)</f>
         <v>45931</v>
       </c>
-      <c r="D94" s="28"/>
+      <c r="D94" s="22"/>
       <c r="E94" t="s">
         <v>1</v>
       </c>
@@ -3242,18 +3299,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>4</v>
       </c>
       <c r="B95" t="s">
         <v>48</v>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="21">
         <f t="shared" si="7"/>
         <v>45962</v>
       </c>
-      <c r="D95" s="28"/>
+      <c r="D95" s="22"/>
       <c r="E95" t="s">
         <v>1</v>
       </c>
@@ -3262,18 +3319,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>4</v>
       </c>
       <c r="B96" t="s">
         <v>48</v>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="21">
         <f t="shared" si="7"/>
         <v>45992</v>
       </c>
-      <c r="D96" s="28"/>
+      <c r="D96" s="22"/>
       <c r="E96" t="s">
         <v>1</v>
       </c>
@@ -3282,18 +3339,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>4</v>
       </c>
       <c r="B97" t="s">
         <v>48</v>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="21">
         <f t="shared" si="7"/>
         <v>46023</v>
       </c>
-      <c r="D97" s="28"/>
+      <c r="D97" s="22"/>
       <c r="E97" t="s">
         <v>1</v>
       </c>
@@ -3302,18 +3359,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>4</v>
       </c>
       <c r="B98" t="s">
         <v>48</v>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="21">
         <f t="shared" si="7"/>
         <v>46054</v>
       </c>
-      <c r="D98" s="28"/>
+      <c r="D98" s="22"/>
       <c r="E98" t="s">
         <v>1</v>
       </c>
@@ -3322,18 +3379,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>4</v>
       </c>
       <c r="B99" t="s">
         <v>48</v>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="21">
         <f t="shared" si="7"/>
         <v>46082</v>
       </c>
-      <c r="D99" s="28"/>
+      <c r="D99" s="22"/>
       <c r="E99" t="s">
         <v>1</v>
       </c>
@@ -3342,18 +3399,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>4</v>
       </c>
       <c r="B100" t="s">
         <v>48</v>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="21">
         <f t="shared" si="7"/>
         <v>46113</v>
       </c>
-      <c r="D100" s="28"/>
+      <c r="D100" s="22"/>
       <c r="E100" t="s">
         <v>1</v>
       </c>
@@ -3362,18 +3419,18 @@
         <v>HALL DESIGN Despesas ADM</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>4</v>
       </c>
       <c r="B103" t="s">
         <v>50</v>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="21">
         <v>45170</v>
       </c>
-      <c r="D103" s="28"/>
+      <c r="D103" s="22"/>
       <c r="E103" t="s">
         <v>8</v>
       </c>
@@ -3382,17 +3439,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>4</v>
       </c>
       <c r="B104" t="s">
         <v>50</v>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="21">
         <v>45200</v>
       </c>
-      <c r="D104" s="28"/>
+      <c r="D104" s="22"/>
       <c r="E104" t="s">
         <v>8</v>
       </c>
@@ -3401,17 +3458,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>4</v>
       </c>
       <c r="B105" t="s">
         <v>50</v>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="21">
         <v>45231</v>
       </c>
-      <c r="D105" s="28"/>
+      <c r="D105" s="22"/>
       <c r="E105" t="s">
         <v>8</v>
       </c>
@@ -3420,17 +3477,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>4</v>
       </c>
       <c r="B106" t="s">
         <v>50</v>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="21">
         <v>45261</v>
       </c>
-      <c r="D106" s="28"/>
+      <c r="D106" s="22"/>
       <c r="E106" t="s">
         <v>8</v>
       </c>
@@ -3439,17 +3496,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>4</v>
       </c>
       <c r="B107" t="s">
         <v>50</v>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="21">
         <v>45292</v>
       </c>
-      <c r="D107" s="28"/>
+      <c r="D107" s="22"/>
       <c r="E107" t="s">
         <v>8</v>
       </c>
@@ -3458,17 +3515,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>4</v>
       </c>
       <c r="B108" t="s">
         <v>50</v>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="21">
         <v>45323</v>
       </c>
-      <c r="D108" s="28"/>
+      <c r="D108" s="22"/>
       <c r="E108" t="s">
         <v>8</v>
       </c>
@@ -3477,17 +3534,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>4</v>
       </c>
       <c r="B109" t="s">
         <v>50</v>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="21">
         <v>45352</v>
       </c>
-      <c r="D109" s="28"/>
+      <c r="D109" s="22"/>
       <c r="E109" t="s">
         <v>8</v>
       </c>
@@ -3496,17 +3553,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>4</v>
       </c>
       <c r="B110" t="s">
         <v>50</v>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="21">
         <v>45383</v>
       </c>
-      <c r="D110" s="28"/>
+      <c r="D110" s="22"/>
       <c r="E110" t="s">
         <v>8</v>
       </c>
@@ -3515,17 +3572,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>4</v>
       </c>
       <c r="B111" t="s">
         <v>50</v>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="21">
         <v>45413</v>
       </c>
-      <c r="D111" s="28"/>
+      <c r="D111" s="22"/>
       <c r="E111" t="s">
         <v>8</v>
       </c>
@@ -3534,17 +3591,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>4</v>
       </c>
       <c r="B112" t="s">
         <v>50</v>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="21">
         <v>45444</v>
       </c>
-      <c r="D112" s="28"/>
+      <c r="D112" s="22"/>
       <c r="E112" t="s">
         <v>8</v>
       </c>
@@ -3553,17 +3610,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>4</v>
       </c>
       <c r="B113" t="s">
         <v>50</v>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="21">
         <v>45474</v>
       </c>
-      <c r="D113" s="28"/>
+      <c r="D113" s="22"/>
       <c r="E113" t="s">
         <v>8</v>
       </c>
@@ -3572,17 +3629,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>4</v>
       </c>
       <c r="B114" t="s">
         <v>50</v>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="21">
         <v>45505</v>
       </c>
-      <c r="D114" s="28"/>
+      <c r="D114" s="22"/>
       <c r="E114" t="s">
         <v>8</v>
       </c>
@@ -3591,17 +3648,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>4</v>
       </c>
       <c r="B115" t="s">
         <v>50</v>
       </c>
-      <c r="C115" s="27">
+      <c r="C115" s="21">
         <v>45536</v>
       </c>
-      <c r="D115" s="28"/>
+      <c r="D115" s="22"/>
       <c r="E115" t="s">
         <v>8</v>
       </c>
@@ -3610,17 +3667,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>4</v>
       </c>
       <c r="B116" t="s">
         <v>50</v>
       </c>
-      <c r="C116" s="27">
+      <c r="C116" s="21">
         <v>45566</v>
       </c>
-      <c r="D116" s="28"/>
+      <c r="D116" s="22"/>
       <c r="E116" t="s">
         <v>8</v>
       </c>
@@ -3629,17 +3686,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>4</v>
       </c>
       <c r="B117" t="s">
         <v>50</v>
       </c>
-      <c r="C117" s="27">
+      <c r="C117" s="21">
         <v>45597</v>
       </c>
-      <c r="D117" s="28"/>
+      <c r="D117" s="22"/>
       <c r="E117" t="s">
         <v>8</v>
       </c>
@@ -3648,17 +3705,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>4</v>
       </c>
       <c r="B118" t="s">
         <v>50</v>
       </c>
-      <c r="C118" s="27">
+      <c r="C118" s="21">
         <v>45627</v>
       </c>
-      <c r="D118" s="28"/>
+      <c r="D118" s="22"/>
       <c r="E118" t="s">
         <v>8</v>
       </c>
@@ -3667,17 +3724,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>4</v>
       </c>
       <c r="B119" t="s">
         <v>50</v>
       </c>
-      <c r="C119" s="27">
+      <c r="C119" s="21">
         <v>45658</v>
       </c>
-      <c r="D119" s="28"/>
+      <c r="D119" s="22"/>
       <c r="E119" t="s">
         <v>8</v>
       </c>
@@ -3686,17 +3743,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>4</v>
       </c>
       <c r="B120" t="s">
         <v>50</v>
       </c>
-      <c r="C120" s="27">
+      <c r="C120" s="21">
         <v>45689</v>
       </c>
-      <c r="D120" s="28"/>
+      <c r="D120" s="22"/>
       <c r="E120" t="s">
         <v>8</v>
       </c>
@@ -3705,17 +3762,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>4</v>
       </c>
       <c r="B121" t="s">
         <v>50</v>
       </c>
-      <c r="C121" s="27">
+      <c r="C121" s="21">
         <v>45717</v>
       </c>
-      <c r="D121" s="28"/>
+      <c r="D121" s="22"/>
       <c r="E121" t="s">
         <v>8</v>
       </c>
@@ -3724,17 +3781,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>4</v>
       </c>
       <c r="B122" t="s">
         <v>50</v>
       </c>
-      <c r="C122" s="27">
+      <c r="C122" s="21">
         <v>45748</v>
       </c>
-      <c r="D122" s="28"/>
+      <c r="D122" s="22"/>
       <c r="E122" t="s">
         <v>8</v>
       </c>
@@ -3743,17 +3800,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>4</v>
       </c>
       <c r="B123" t="s">
         <v>50</v>
       </c>
-      <c r="C123" s="27">
+      <c r="C123" s="21">
         <v>45778</v>
       </c>
-      <c r="D123" s="28"/>
+      <c r="D123" s="22"/>
       <c r="E123" t="s">
         <v>8</v>
       </c>
@@ -3762,17 +3819,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>4</v>
       </c>
       <c r="B124" t="s">
         <v>50</v>
       </c>
-      <c r="C124" s="27">
+      <c r="C124" s="21">
         <v>45809</v>
       </c>
-      <c r="D124" s="28"/>
+      <c r="D124" s="22"/>
       <c r="E124" t="s">
         <v>8</v>
       </c>
@@ -3781,17 +3838,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>4</v>
       </c>
       <c r="B125" t="s">
         <v>50</v>
       </c>
-      <c r="C125" s="27">
+      <c r="C125" s="21">
         <v>45839</v>
       </c>
-      <c r="D125" s="28"/>
+      <c r="D125" s="22"/>
       <c r="E125" t="s">
         <v>8</v>
       </c>
@@ -3800,17 +3857,17 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>4</v>
       </c>
       <c r="B126" t="s">
         <v>50</v>
       </c>
-      <c r="C126" s="27">
+      <c r="C126" s="21">
         <v>45870</v>
       </c>
-      <c r="D126" s="28"/>
+      <c r="D126" s="22"/>
       <c r="E126" t="s">
         <v>8</v>
       </c>
@@ -3819,18 +3876,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>4</v>
       </c>
       <c r="B127" t="s">
         <v>50</v>
       </c>
-      <c r="C127" s="27">
+      <c r="C127" s="21">
         <f>EDATE(C126,1)</f>
         <v>45901</v>
       </c>
-      <c r="D127" s="28"/>
+      <c r="D127" s="22"/>
       <c r="E127" t="s">
         <v>1</v>
       </c>
@@ -3839,18 +3896,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>4</v>
       </c>
       <c r="B128" t="s">
         <v>50</v>
       </c>
-      <c r="C128" s="27">
+      <c r="C128" s="21">
         <f t="shared" ref="C128:C134" si="9">EDATE(C127,1)</f>
         <v>45931</v>
       </c>
-      <c r="D128" s="28"/>
+      <c r="D128" s="22"/>
       <c r="E128" t="s">
         <v>1</v>
       </c>
@@ -3859,18 +3916,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>4</v>
       </c>
       <c r="B129" t="s">
         <v>50</v>
       </c>
-      <c r="C129" s="27">
+      <c r="C129" s="21">
         <f t="shared" si="9"/>
         <v>45962</v>
       </c>
-      <c r="D129" s="28"/>
+      <c r="D129" s="22"/>
       <c r="E129" t="s">
         <v>1</v>
       </c>
@@ -3879,18 +3936,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>4</v>
       </c>
       <c r="B130" t="s">
         <v>50</v>
       </c>
-      <c r="C130" s="27">
+      <c r="C130" s="21">
         <f t="shared" si="9"/>
         <v>45992</v>
       </c>
-      <c r="D130" s="28"/>
+      <c r="D130" s="22"/>
       <c r="E130" t="s">
         <v>1</v>
       </c>
@@ -3899,18 +3956,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>4</v>
       </c>
       <c r="B131" t="s">
         <v>50</v>
       </c>
-      <c r="C131" s="27">
+      <c r="C131" s="21">
         <f t="shared" si="9"/>
         <v>46023</v>
       </c>
-      <c r="D131" s="28"/>
+      <c r="D131" s="22"/>
       <c r="E131" t="s">
         <v>1</v>
       </c>
@@ -3919,18 +3976,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>4</v>
       </c>
       <c r="B132" t="s">
         <v>50</v>
       </c>
-      <c r="C132" s="27">
+      <c r="C132" s="21">
         <f t="shared" si="9"/>
         <v>46054</v>
       </c>
-      <c r="D132" s="28"/>
+      <c r="D132" s="22"/>
       <c r="E132" t="s">
         <v>1</v>
       </c>
@@ -3939,18 +3996,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>4</v>
       </c>
       <c r="B133" t="s">
         <v>50</v>
       </c>
-      <c r="C133" s="27">
+      <c r="C133" s="21">
         <f t="shared" si="9"/>
         <v>46082</v>
       </c>
-      <c r="D133" s="28"/>
+      <c r="D133" s="22"/>
       <c r="E133" t="s">
         <v>1</v>
       </c>
@@ -3959,18 +4016,18 @@
         <v>HALL DESIGN % Receita liquida geral</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>4</v>
       </c>
       <c r="B134" t="s">
         <v>50</v>
       </c>
-      <c r="C134" s="27">
+      <c r="C134" s="21">
         <f t="shared" si="9"/>
         <v>46113</v>
       </c>
-      <c r="D134" s="28"/>
+      <c r="D134" s="22"/>
       <c r="E134" t="s">
         <v>1</v>
       </c>
@@ -3988,26 +4045,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B648EA-C9CF-4199-AC21-3B599FE2C0B5}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="12" width="15.5703125" customWidth="1"/>
-    <col min="13" max="13" width="25.85546875" customWidth="1"/>
+    <col min="9" max="12" width="15.5546875" customWidth="1"/>
+    <col min="13" max="13" width="25.88671875" customWidth="1"/>
     <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="42.85546875" customWidth="1"/>
-    <col min="16" max="16" width="15.85546875" customWidth="1"/>
-    <col min="17" max="17" width="15.42578125" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" customWidth="1"/>
+    <col min="15" max="15" width="42.88671875" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" customWidth="1"/>
+    <col min="17" max="17" width="15.44140625" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" customWidth="1"/>
     <col min="19" max="19" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -4066,8 +4123,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+    <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="81" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="4">
@@ -4080,7 +4137,7 @@
       <c r="D2" s="5">
         <v>32</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="28">
         <v>37</v>
       </c>
       <c r="F2" s="4">
@@ -4096,60 +4153,60 @@
         <f>(E2-D2)*30</f>
         <v>150</v>
       </c>
-      <c r="J2" s="31">
+      <c r="J2" s="25">
         <v>49776.481999999996</v>
       </c>
-      <c r="K2" s="31">
+      <c r="K2" s="25">
         <v>30</v>
       </c>
-      <c r="L2" s="31">
+      <c r="L2" s="25">
         <f>K2*J2</f>
         <v>1493294.46</v>
       </c>
-      <c r="M2" s="35"/>
-      <c r="N2" s="75">
+      <c r="M2" s="29"/>
+      <c r="N2" s="68">
         <v>0</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="71">
         <v>3.3E-4</v>
       </c>
-      <c r="Q2" s="54">
+      <c r="Q2" s="72">
         <v>48156918.740000002</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="73">
         <f>I2*P2*Q2</f>
         <v>2383767.4776300001</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="74">
         <f>R2/Q2</f>
         <v>4.9500000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="46" t="s">
+    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="26">
         <v>44166</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="26">
         <f t="shared" si="0"/>
         <v>45230</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="25">
         <v>35</v>
       </c>
-      <c r="E3" s="41">
+      <c r="E3" s="35">
         <v>39</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" ref="F3:H25" si="1">EDATE($B3,E3)-1</f>
         <v>45351</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="25">
         <v>43</v>
       </c>
       <c r="H3" s="4">
@@ -4160,59 +4217,59 @@
         <f t="shared" ref="I3:I23" si="2">(E3-D3)*30</f>
         <v>120</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="84">
         <v>68630.7</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="25">
         <f>33*J3</f>
         <v>2264813.1</v>
       </c>
-      <c r="M3" s="35"/>
-      <c r="N3" s="75">
+      <c r="M3" s="29"/>
+      <c r="N3" s="68">
         <v>0</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="71">
         <v>3.3E-4</v>
       </c>
-      <c r="Q3" s="42">
+      <c r="Q3" s="75">
         <v>59525244</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="73">
         <v>0</v>
       </c>
-      <c r="S3" s="9">
+      <c r="S3" s="74">
         <f t="shared" ref="S3:S25" si="3">R3/Q3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
+    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="6">
         <v>45170</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="6">
         <f t="shared" si="0"/>
         <v>45777</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="7">
         <v>20</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="29">
         <v>27</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="1"/>
         <v>45991</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="7">
         <v>28</v>
       </c>
       <c r="H4" s="4">
@@ -4223,59 +4280,59 @@
         <f t="shared" si="2"/>
         <v>210</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="25">
         <v>57623.59</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="25">
         <v>24</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="25">
         <f t="shared" ref="L4:L25" si="4">K4*J4</f>
         <v>1382966.16</v>
       </c>
-      <c r="M4" s="35"/>
-      <c r="N4" s="75">
+      <c r="M4" s="29"/>
+      <c r="N4" s="68">
         <v>0</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="77">
         <v>19331059</v>
       </c>
-      <c r="R4" s="8">
+      <c r="R4" s="73">
         <v>0</v>
       </c>
-      <c r="S4" s="9">
+      <c r="S4" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
+    <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="6">
         <v>45170</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="6">
         <f t="shared" si="0"/>
         <v>45900</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="7">
         <v>24</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="29">
         <v>34</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="1"/>
         <v>46203</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="7"/>
       <c r="H5" s="4">
         <f t="shared" si="1"/>
         <v>45169</v>
@@ -4284,60 +4341,60 @@
         <f t="shared" si="2"/>
         <v>300</v>
       </c>
-      <c r="J5" s="31">
+      <c r="J5" s="25">
         <v>67040.736666666664</v>
       </c>
-      <c r="K5" s="31">
+      <c r="K5" s="25">
         <v>24</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="25">
         <f t="shared" si="4"/>
         <v>1608977.68</v>
       </c>
-      <c r="M5" s="35"/>
-      <c r="N5" s="75">
+      <c r="M5" s="29"/>
+      <c r="N5" s="68">
         <v>0</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="O5" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q5" s="38">
+      <c r="Q5" s="77">
         <v>30874919.829999998</v>
       </c>
-      <c r="R5" s="8">
+      <c r="R5" s="73">
         <f>Q5*0.05</f>
         <v>1543745.9915</v>
       </c>
-      <c r="S5" s="9">
+      <c r="S5" s="74">
         <f t="shared" si="3"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
+    <row r="6" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="6">
         <v>45301</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="6">
         <f t="shared" si="0"/>
         <v>46577</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="7">
         <v>42</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="29">
         <v>46</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="1"/>
         <v>46700</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="7"/>
       <c r="H6" s="4">
         <f t="shared" si="1"/>
         <v>45300</v>
@@ -4346,60 +4403,60 @@
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="J6" s="31">
+      <c r="J6" s="25">
         <v>189984.66261904765</v>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="25">
         <v>46</v>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="25">
         <f t="shared" si="4"/>
         <v>8739294.4804761913</v>
       </c>
-      <c r="M6" s="35"/>
-      <c r="N6" s="75">
+      <c r="M6" s="29"/>
+      <c r="N6" s="68">
         <v>0</v>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q6" s="38">
+      <c r="Q6" s="77">
         <v>150327077.33000001</v>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="73">
         <f>I6*P6*Q6</f>
         <v>5952952.2622680003</v>
       </c>
-      <c r="S6" s="9">
+      <c r="S6" s="74">
         <f t="shared" si="3"/>
         <v>3.9599999999999996E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="s">
+    <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="6">
         <v>44470</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="6">
         <f t="shared" si="0"/>
         <v>45322</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="7">
         <v>28</v>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="29">
         <v>33</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" si="1"/>
         <v>45473</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="7">
         <v>34</v>
       </c>
       <c r="H7" s="4">
@@ -4410,59 +4467,59 @@
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="25">
         <v>42636.509999999995</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="25">
         <v>26</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="25">
         <f t="shared" si="4"/>
         <v>1108549.2599999998</v>
       </c>
-      <c r="M7" s="35"/>
-      <c r="N7" s="75">
+      <c r="M7" s="29"/>
+      <c r="N7" s="68">
         <v>0</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="O7" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P7" s="15">
+      <c r="P7" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q7" s="38">
+      <c r="Q7" s="77">
         <v>39854406</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="73">
         <v>0</v>
       </c>
-      <c r="S7" s="9">
+      <c r="S7" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="10">
+    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="85" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="6">
         <v>44682</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="6">
         <f t="shared" si="0"/>
         <v>45504</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="7">
         <v>27</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="29">
         <v>33</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
         <v>45688</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="7">
         <v>38</v>
       </c>
       <c r="H8" s="4">
@@ -4473,59 +4530,59 @@
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="25">
         <v>71960.148148148146</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="25">
         <v>27</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="25">
         <f t="shared" si="4"/>
         <v>1942924</v>
       </c>
-      <c r="M8" s="35"/>
-      <c r="N8" s="75">
+      <c r="M8" s="29"/>
+      <c r="N8" s="68">
         <v>0</v>
       </c>
-      <c r="O8" s="12" t="s">
+      <c r="O8" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q8" s="38">
+      <c r="Q8" s="77">
         <v>62491370</v>
       </c>
-      <c r="R8" s="8">
+      <c r="R8" s="73">
         <v>0</v>
       </c>
-      <c r="S8" s="9">
+      <c r="S8" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
+    <row r="9" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="6">
         <v>44621</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="6">
         <f t="shared" si="0"/>
         <v>45412</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="7">
         <v>26</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="29">
         <v>34</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="1"/>
         <v>45657</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="7">
         <v>39</v>
       </c>
       <c r="H9" s="4">
@@ -4536,60 +4593,60 @@
         <f t="shared" si="2"/>
         <v>240</v>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="25">
         <v>65351.329999999994</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="25">
         <v>24</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="25">
         <f t="shared" si="4"/>
         <v>1568431.92</v>
       </c>
-      <c r="M9" s="35"/>
-      <c r="N9" s="75">
+      <c r="M9" s="29"/>
+      <c r="N9" s="68">
         <v>0</v>
       </c>
-      <c r="O9" s="12" t="s">
+      <c r="O9" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P9" s="15">
+      <c r="P9" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q9" s="38">
+      <c r="Q9" s="77">
         <v>45889672</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="73">
         <f>(I9-180)*P9*Q9</f>
         <v>908615.50559999992</v>
       </c>
-      <c r="S9" s="9">
+      <c r="S9" s="74">
         <f t="shared" si="3"/>
         <v>1.9799999999999998E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="47" t="s">
+    <row r="10" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="6">
         <v>45139</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="6">
         <f t="shared" si="0"/>
         <v>45504</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="7">
         <v>12</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="29">
         <v>18</v>
       </c>
       <c r="F10" s="4">
         <f t="shared" si="1"/>
         <v>45688</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="7">
         <v>18</v>
       </c>
       <c r="H10" s="4">
@@ -4600,59 +4657,59 @@
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="25">
         <v>39906.74</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="25">
         <v>12</v>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="25">
         <f t="shared" si="4"/>
         <v>478880.88</v>
       </c>
-      <c r="M10" s="35"/>
-      <c r="N10" s="75">
+      <c r="M10" s="29"/>
+      <c r="N10" s="68">
         <v>0</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P10" s="15">
+      <c r="P10" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q10" s="38">
+      <c r="Q10" s="77">
         <v>8442659</v>
       </c>
-      <c r="R10" s="8">
+      <c r="R10" s="73">
         <v>0</v>
       </c>
-      <c r="S10" s="9">
+      <c r="S10" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+    <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="6">
         <v>44805</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="6">
         <f t="shared" si="0"/>
         <v>45747</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="7">
         <v>31</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="29">
         <v>42</v>
       </c>
       <c r="F11" s="4">
         <f t="shared" si="1"/>
         <v>46081</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="7">
         <v>47</v>
       </c>
       <c r="H11" s="4">
@@ -4663,60 +4720,60 @@
         <f t="shared" si="2"/>
         <v>330</v>
       </c>
-      <c r="J11" s="76">
+      <c r="J11" s="86">
         <v>112914.29540540541</v>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="86">
         <v>37</v>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="25">
         <f t="shared" si="4"/>
         <v>4177828.93</v>
       </c>
-      <c r="M11" s="35"/>
-      <c r="N11" s="75" t="s">
+      <c r="M11" s="29"/>
+      <c r="N11" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="O11" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q11" s="38">
+      <c r="Q11" s="77">
         <v>100802866</v>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="73">
         <f>(I11-180)*P11*Q11</f>
         <v>4989741.8670000006</v>
       </c>
-      <c r="S11" s="9">
+      <c r="S11" s="74">
         <f t="shared" si="3"/>
         <v>4.9500000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="47" t="s">
+    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="6">
         <v>45047</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="6">
         <f t="shared" si="0"/>
         <v>46081</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="7">
         <v>34</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="29">
         <v>34</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="1"/>
         <v>46081</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="7">
         <v>34</v>
       </c>
       <c r="H12" s="4">
@@ -4727,184 +4784,188 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J12" s="31">
+      <c r="J12" s="25">
         <v>72429.599999999991</v>
       </c>
-      <c r="K12" s="31">
+      <c r="K12" s="25">
         <v>34</v>
       </c>
-      <c r="L12" s="31">
+      <c r="L12" s="25">
         <f t="shared" si="4"/>
         <v>2462606.4</v>
       </c>
-      <c r="M12" s="35"/>
-      <c r="N12" s="75" t="s">
+      <c r="M12" s="29"/>
+      <c r="N12" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O12" s="12" t="s">
+      <c r="O12" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P12" s="15">
+      <c r="P12" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q12" s="38">
+      <c r="Q12" s="77">
         <v>129823938</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="73">
         <f>I12*P12*Q12</f>
         <v>0</v>
       </c>
-      <c r="S12" s="9">
+      <c r="S12" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="47" t="s">
+    <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="6">
         <v>45413</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="6">
         <f t="shared" si="0"/>
         <v>46691</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="7">
         <v>42</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="29">
+        <v>39</v>
+      </c>
+      <c r="F13" s="4">
+        <f t="shared" si="1"/>
+        <v>46599</v>
+      </c>
+      <c r="G13" s="7">
         <v>42</v>
       </c>
-      <c r="F13" s="4">
+      <c r="H13" s="4">
         <f t="shared" si="1"/>
         <v>46691</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>45412</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="31">
+        <v>-90</v>
+      </c>
+      <c r="J13" s="25">
         <v>113407.94166666668</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="25">
         <v>36</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="25">
         <f t="shared" si="4"/>
         <v>4082685.9000000004</v>
       </c>
-      <c r="M13" s="35"/>
-      <c r="N13" s="75" t="s">
+      <c r="M13" s="29"/>
+      <c r="N13" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="O13" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P13" s="15">
+      <c r="P13" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q13" s="38">
+      <c r="Q13" s="77">
         <v>75712669</v>
       </c>
-      <c r="R13" s="8">
+      <c r="R13" s="73">
         <f>I13*P13*Q13</f>
-        <v>0</v>
-      </c>
-      <c r="S13" s="9">
+        <v>-2248666.2693000003</v>
+      </c>
+      <c r="S13" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+        <v>-2.9700000000000004E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="6">
         <v>45444</v>
       </c>
-      <c r="C14" s="10">
-        <f t="shared" si="0"/>
-        <v>46173</v>
-      </c>
-      <c r="D14" s="11">
-        <v>24</v>
-      </c>
-      <c r="E14" s="35">
-        <v>24</v>
+      <c r="C14" s="6">
+        <f t="shared" si="0"/>
+        <v>46356</v>
+      </c>
+      <c r="D14" s="7">
+        <v>30</v>
+      </c>
+      <c r="E14" s="29">
+        <v>27</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="1"/>
-        <v>46173</v>
-      </c>
-      <c r="G14" s="11"/>
+        <v>46265</v>
+      </c>
+      <c r="G14" s="7">
+        <v>30</v>
+      </c>
       <c r="H14" s="4">
         <f t="shared" si="1"/>
-        <v>45443</v>
+        <v>46356</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="31">
+        <v>-90</v>
+      </c>
+      <c r="J14" s="25">
         <v>69631.679999999993</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="25">
         <v>24</v>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="25">
         <f t="shared" si="4"/>
         <v>1671160.3199999998</v>
       </c>
-      <c r="M14" s="35"/>
-      <c r="N14" s="75" t="s">
+      <c r="M14" s="29"/>
+      <c r="N14" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="O14" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P14" s="15">
+      <c r="P14" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q14" s="38">
+      <c r="Q14" s="77">
         <v>24795027</v>
       </c>
-      <c r="R14" s="8">
+      <c r="R14" s="73">
         <f>I14*P14*Q14</f>
-        <v>0</v>
-      </c>
-      <c r="S14" s="9">
+        <v>-736412.30189999996</v>
+      </c>
+      <c r="S14" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="47" t="s">
+        <v>-2.9699999999999997E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="6">
         <v>45413</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="6">
         <f t="shared" si="0"/>
         <v>45716</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="7">
         <v>10</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="29">
         <v>12</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="1"/>
         <v>45777</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="7"/>
       <c r="H15" s="4">
         <f t="shared" si="1"/>
         <v>45412</v>
@@ -4913,60 +4974,59 @@
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="J15" s="31">
+      <c r="J15" s="25">
         <v>54235.135999999999</v>
       </c>
-      <c r="K15" s="31">
-        <f>J15/10</f>
-        <v>5423.5136000000002</v>
-      </c>
-      <c r="L15" s="31">
+      <c r="K15" s="25">
+        <v>10</v>
+      </c>
+      <c r="L15" s="25">
         <f t="shared" si="4"/>
-        <v>294144997.69384962</v>
-      </c>
-      <c r="M15" s="35"/>
-      <c r="N15" s="75">
+        <v>542351.35999999999</v>
+      </c>
+      <c r="M15" s="29"/>
+      <c r="N15" s="68">
         <v>0</v>
       </c>
-      <c r="O15" s="12" t="s">
+      <c r="O15" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="P15" s="13" t="s">
+      <c r="P15" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="Q15" s="38">
+      <c r="Q15" s="77">
         <v>36372271</v>
       </c>
-      <c r="R15" s="8">
+      <c r="R15" s="73">
         <v>0</v>
       </c>
-      <c r="S15" s="9">
+      <c r="S15" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="47" t="s">
+    <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="6">
         <v>45444</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="6">
         <f t="shared" si="0"/>
         <v>45688</v>
       </c>
-      <c r="D16" s="11">
-        <v>8</v>
-      </c>
-      <c r="E16" s="35">
+      <c r="D16" s="7">
+        <v>8</v>
+      </c>
+      <c r="E16" s="29">
         <v>8</v>
       </c>
       <c r="F16" s="4">
         <f t="shared" si="1"/>
         <v>45688</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="G16" s="7"/>
       <c r="H16" s="4">
         <f t="shared" si="1"/>
         <v>45443</v>
@@ -4975,308 +5035,314 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J16" s="31">
+      <c r="J16" s="25">
         <v>22716.98</v>
       </c>
-      <c r="K16" s="31">
-        <v>8</v>
-      </c>
-      <c r="L16" s="31">
+      <c r="K16" s="25">
+        <v>8</v>
+      </c>
+      <c r="L16" s="25">
         <f t="shared" si="4"/>
         <v>181735.84</v>
       </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="75">
+      <c r="M16" s="29"/>
+      <c r="N16" s="68">
         <v>0</v>
       </c>
-      <c r="O16" s="12" t="s">
+      <c r="O16" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P16" s="15">
+      <c r="P16" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q16" s="38">
+      <c r="Q16" s="77">
         <v>1365707</v>
       </c>
-      <c r="R16" s="8">
+      <c r="R16" s="73">
         <f>I16*P16*Q16</f>
         <v>0</v>
       </c>
-      <c r="S16" s="9">
+      <c r="S16" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="47" t="s">
+    <row r="17" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="6">
         <v>45444</v>
       </c>
-      <c r="C17" s="10">
-        <f t="shared" si="0"/>
-        <v>46477</v>
-      </c>
-      <c r="D17" s="11">
-        <v>34</v>
-      </c>
-      <c r="E17" s="35">
-        <v>34</v>
+      <c r="C17" s="6">
+        <f t="shared" si="0"/>
+        <v>46630</v>
+      </c>
+      <c r="D17" s="7">
+        <v>39</v>
+      </c>
+      <c r="E17" s="29">
+        <v>36</v>
       </c>
       <c r="F17" s="4">
         <f t="shared" si="1"/>
-        <v>46477</v>
-      </c>
-      <c r="G17" s="11"/>
+        <v>46538</v>
+      </c>
+      <c r="G17" s="7"/>
       <c r="H17" s="4">
         <f t="shared" si="1"/>
         <v>45443</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="31">
+        <v>-90</v>
+      </c>
+      <c r="J17" s="25">
         <v>82372.476666666669</v>
       </c>
-      <c r="K17" s="31" t="s">
+      <c r="K17" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="25">
         <f>39*J17</f>
         <v>3212526.5900000003</v>
       </c>
-      <c r="M17" s="35"/>
-      <c r="N17" s="75" t="s">
+      <c r="M17" s="29"/>
+      <c r="N17" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O17" s="12" t="s">
+      <c r="O17" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="15">
+      <c r="P17" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q17" s="38">
+      <c r="Q17" s="77">
         <v>82688581</v>
       </c>
-      <c r="R17" s="8">
+      <c r="R17" s="73">
         <f>I17*P17*Q17</f>
-        <v>0</v>
-      </c>
-      <c r="S17" s="9">
+        <v>-2455850.8557000002</v>
+      </c>
+      <c r="S17" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="47" t="s">
+        <v>-2.9700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="6">
         <v>45536</v>
       </c>
-      <c r="C18" s="10">
-        <f t="shared" si="0"/>
-        <v>46477</v>
-      </c>
-      <c r="D18" s="11">
-        <v>31</v>
-      </c>
-      <c r="E18" s="35">
-        <v>31</v>
+      <c r="C18" s="6">
+        <f t="shared" si="0"/>
+        <v>46873</v>
+      </c>
+      <c r="D18" s="7">
+        <v>44</v>
+      </c>
+      <c r="E18" s="29">
+        <v>41</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="1"/>
-        <v>46477</v>
-      </c>
-      <c r="G18" s="11"/>
+        <v>46783</v>
+      </c>
+      <c r="G18" s="7">
+        <v>44</v>
+      </c>
       <c r="H18" s="4">
         <f t="shared" si="1"/>
-        <v>45535</v>
+        <v>46873</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="31">
+        <v>-90</v>
+      </c>
+      <c r="J18" s="25">
         <v>72603.663636363635</v>
       </c>
-      <c r="K18" s="31" t="s">
+      <c r="K18" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="25">
         <f>31*J18</f>
         <v>2250713.5727272728</v>
       </c>
-      <c r="M18" s="35"/>
-      <c r="N18" s="75" t="s">
+      <c r="M18" s="29"/>
+      <c r="N18" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O18" s="12" t="s">
+      <c r="O18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P18" s="15">
+      <c r="P18" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q18" s="38">
+      <c r="Q18" s="77">
         <v>61763786</v>
       </c>
-      <c r="R18" s="8">
+      <c r="R18" s="73">
         <f>I18*P18*Q18</f>
-        <v>0</v>
-      </c>
-      <c r="S18" s="9">
+        <v>-1834384.4442</v>
+      </c>
+      <c r="S18" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+        <v>-2.9700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="6">
         <v>45536</v>
       </c>
-      <c r="C19" s="10">
-        <f t="shared" si="0"/>
-        <v>46265</v>
-      </c>
-      <c r="D19" s="11">
-        <v>24</v>
-      </c>
-      <c r="E19" s="35">
-        <v>24</v>
+      <c r="C19" s="6">
+        <f t="shared" si="0"/>
+        <v>46446</v>
+      </c>
+      <c r="D19" s="7">
+        <v>30</v>
+      </c>
+      <c r="E19" s="29">
+        <v>27</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="1"/>
-        <v>46265</v>
-      </c>
-      <c r="G19" s="11"/>
+        <v>46356</v>
+      </c>
+      <c r="G19" s="7">
+        <v>30</v>
+      </c>
       <c r="H19" s="4">
         <f t="shared" si="1"/>
-        <v>45535</v>
+        <v>46446</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="31">
+        <v>-90</v>
+      </c>
+      <c r="J19" s="25">
         <v>65164.644999999997</v>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="25">
         <v>24</v>
       </c>
-      <c r="L19" s="31">
+      <c r="L19" s="25">
         <f t="shared" si="4"/>
         <v>1563951.48</v>
       </c>
-      <c r="M19" s="35"/>
-      <c r="N19" s="75" t="s">
+      <c r="M19" s="29"/>
+      <c r="N19" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O19" s="12" t="s">
+      <c r="O19" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P19" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q19" s="38">
+      <c r="Q19" s="77">
         <v>33840813</v>
       </c>
-      <c r="R19" s="8">
+      <c r="R19" s="73">
         <f>I19*P19*Q19</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="9">
+        <v>-1005072.1461</v>
+      </c>
+      <c r="S19" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="47" t="s">
+        <v>-2.9700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="6">
         <v>46113</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="6">
         <f t="shared" si="0"/>
         <v>46418</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="7">
         <v>10</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="29">
         <v>12</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
         <v>46477</v>
       </c>
-      <c r="G20" s="11"/>
+      <c r="G20" s="7">
+        <v>10</v>
+      </c>
       <c r="H20" s="4">
         <f t="shared" si="1"/>
-        <v>46112</v>
+        <v>46418</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="J20" s="31">
+      <c r="J20" s="25">
         <v>30434.447999999997</v>
       </c>
-      <c r="K20" s="77" t="s">
+      <c r="K20" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="25">
         <f>10*J20</f>
         <v>304344.48</v>
       </c>
-      <c r="M20" s="35"/>
-      <c r="N20" s="75" t="s">
+      <c r="M20" s="29"/>
+      <c r="N20" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O20" s="12" t="s">
+      <c r="O20" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P20" s="15">
+      <c r="P20" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q20" s="38">
+      <c r="Q20" s="77">
         <v>1946684</v>
       </c>
-      <c r="R20" s="8">
+      <c r="R20" s="73">
         <f>I20*P20*Q20</f>
         <v>38544.343199999996</v>
       </c>
-      <c r="S20" s="9">
+      <c r="S20" s="74">
         <f t="shared" si="3"/>
         <v>1.9799999999999998E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="48" t="s">
+    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="10">
         <v>45627</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="10">
         <f t="shared" si="0"/>
         <v>46053</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="27">
         <v>14</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="30">
         <v>17</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" si="1"/>
         <v>46142</v>
       </c>
-      <c r="G21" s="33"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="4">
         <f t="shared" si="1"/>
         <v>45626</v>
@@ -5285,58 +5351,59 @@
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="J21" s="72">
+      <c r="J21" s="65">
         <v>43235.649999999994</v>
       </c>
-      <c r="K21" s="72">
+      <c r="K21" s="65">
         <v>12</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="25">
         <f t="shared" si="4"/>
         <v>518827.79999999993</v>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="75" t="s">
+      <c r="M21" s="30"/>
+      <c r="N21" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O21" s="12" t="s">
+      <c r="O21" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P21" s="15">
+      <c r="P21" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q21" s="39">
+      <c r="Q21" s="79">
         <v>14696272</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="73">
         <v>0</v>
       </c>
-      <c r="S21" s="9">
+      <c r="S21" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="63" t="s">
+    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="71">
+      <c r="B22" s="89">
         <v>45992</v>
       </c>
-      <c r="C22" s="71">
+      <c r="C22" s="89">
         <f>EDATE(B22,D22)-1</f>
         <v>47361</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="84">
         <v>45</v>
       </c>
-      <c r="E22" s="74">
+      <c r="E22" s="67">
         <v>45</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="1"/>
         <v>47361</v>
       </c>
+      <c r="G22" s="84"/>
       <c r="H22" s="4">
         <f t="shared" si="1"/>
         <v>45991</v>
@@ -5345,55 +5412,58 @@
         <f>(E22-D22)*30</f>
         <v>0</v>
       </c>
-      <c r="J22" s="73">
+      <c r="J22" s="66">
         <v>186189.96111111113</v>
       </c>
-      <c r="K22" s="73" t="s">
+      <c r="K22" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="25">
         <f>45*J22</f>
         <v>8378548.2500000009</v>
       </c>
-      <c r="N22" s="75" t="s">
+      <c r="M22" s="84"/>
+      <c r="N22" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O22" s="78" t="s">
+      <c r="O22" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="Q22" s="65">
+      <c r="P22" s="84"/>
+      <c r="Q22" s="80">
         <v>23961874</v>
       </c>
-      <c r="R22" s="8">
+      <c r="R22" s="73">
         <f>I22*P22*Q22</f>
         <v>0</v>
       </c>
-      <c r="S22" s="9">
+      <c r="S22" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="63" t="s">
+    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="71">
+      <c r="B23" s="89">
         <v>46082</v>
       </c>
-      <c r="C23" s="71">
+      <c r="C23" s="89">
         <f>EDATE(B23,D23)-1</f>
         <v>47452</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="84">
         <v>45</v>
       </c>
-      <c r="E23" s="74">
+      <c r="E23" s="67">
         <v>45</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="1"/>
         <v>47452</v>
       </c>
+      <c r="G23" s="84"/>
       <c r="H23" s="4">
         <f t="shared" si="1"/>
         <v>46081</v>
@@ -5402,58 +5472,60 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J23" s="73">
+      <c r="J23" s="66">
         <v>92468.744888888876</v>
       </c>
-      <c r="K23" s="73" t="s">
+      <c r="K23" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="25">
         <f>45*J23</f>
         <v>4161093.5199999996</v>
       </c>
-      <c r="N23" s="75" t="s">
+      <c r="M23" s="84"/>
+      <c r="N23" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O23" s="12" t="s">
+      <c r="O23" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="P23" s="15">
+      <c r="P23" s="78">
         <v>3.3E-4</v>
       </c>
-      <c r="Q23" s="65">
+      <c r="Q23" s="80">
         <v>109238942</v>
       </c>
-      <c r="R23" s="8">
+      <c r="R23" s="73">
         <f>I23*P23*Q23</f>
         <v>0</v>
       </c>
-      <c r="S23" s="9">
+      <c r="S23" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="63" t="s">
+    <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="71">
+      <c r="B24" s="89">
         <v>46143</v>
       </c>
-      <c r="C24" s="71">
+      <c r="C24" s="89">
         <f>EDATE(B24,D24)-1</f>
         <v>47057</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="84">
         <v>30</v>
       </c>
-      <c r="E24" s="74">
+      <c r="E24" s="67">
         <v>28</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="1"/>
         <v>46996</v>
       </c>
+      <c r="G24" s="84"/>
       <c r="H24" s="4">
         <f t="shared" si="1"/>
         <v>46142</v>
@@ -5461,59 +5533,61 @@
       <c r="I24" s="5">
         <v>0</v>
       </c>
-      <c r="J24" s="73">
+      <c r="J24" s="66">
         <v>86570.127999999997</v>
       </c>
-      <c r="K24" s="73" t="s">
+      <c r="K24" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="25">
         <f>30*J24</f>
         <v>2597103.84</v>
       </c>
-      <c r="N24" s="75" t="s">
+      <c r="M24" s="84"/>
+      <c r="N24" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O24" s="78" t="s">
+      <c r="O24" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="P24" s="30">
+      <c r="P24" s="91">
         <f>0.01/30</f>
         <v>3.3333333333333332E-4</v>
       </c>
-      <c r="Q24" s="65">
+      <c r="Q24" s="80">
         <v>52846811</v>
       </c>
-      <c r="R24" s="8">
+      <c r="R24" s="73">
         <f>I24*P24*Q24</f>
         <v>0</v>
       </c>
-      <c r="S24" s="9">
+      <c r="S24" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="63" t="s">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="88" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="71">
+      <c r="B25" s="89">
         <v>45931</v>
       </c>
-      <c r="C25" s="71">
+      <c r="C25" s="89">
         <f>EDATE(B25,D25)-1</f>
         <v>46843</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="84">
         <v>30</v>
       </c>
-      <c r="E25" s="74">
+      <c r="E25" s="67">
         <v>27</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="1"/>
         <v>46752</v>
       </c>
+      <c r="G25" s="84"/>
       <c r="H25" s="4">
         <f t="shared" si="1"/>
         <v>45930</v>
@@ -5521,33 +5595,34 @@
       <c r="I25" s="5">
         <v>0</v>
       </c>
-      <c r="J25" s="73">
+      <c r="J25" s="66">
         <v>59174.37</v>
       </c>
-      <c r="K25" s="73">
+      <c r="K25" s="66">
         <v>24</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="25">
         <f t="shared" si="4"/>
         <v>1420184.8800000001</v>
       </c>
-      <c r="N25" s="75" t="s">
+      <c r="M25" s="84"/>
+      <c r="N25" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="O25" t="s">
+      <c r="O25" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="P25" s="28">
+      <c r="P25" s="92">
         <v>0.02</v>
       </c>
-      <c r="Q25" s="65">
+      <c r="Q25" s="80">
         <v>22244837</v>
       </c>
-      <c r="R25" s="8">
+      <c r="R25" s="73">
         <f>IF(I25&gt;0,Q25*P25,0)</f>
         <v>0</v>
       </c>
-      <c r="S25" s="9">
+      <c r="S25" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5562,22 +5637,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9847408C-B23C-4D48-83D1-CB6301E525D5}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="36.42578125" customWidth="1"/>
-    <col min="3" max="8" width="27.85546875" customWidth="1"/>
-    <col min="9" max="9" width="36.42578125" style="62" customWidth="1"/>
-    <col min="10" max="10" width="36.42578125" customWidth="1"/>
-    <col min="11" max="11" width="24.5703125" customWidth="1"/>
+    <col min="1" max="2" width="36.44140625" customWidth="1"/>
+    <col min="3" max="8" width="27.88671875" customWidth="1"/>
+    <col min="9" max="9" width="36.44140625" style="56" customWidth="1"/>
+    <col min="10" max="10" width="36.44140625" customWidth="1"/>
+    <col min="11" max="11" width="24.5546875" customWidth="1"/>
     <col min="12" max="12" width="26" customWidth="1"/>
-    <col min="13" max="13" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="255.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="34" t="s">
         <v>54</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -5614,957 +5689,957 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="54">
+      <c r="C2" s="48">
         <v>48156918.740000002</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="31">
         <v>53387212.439999998</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <f t="shared" ref="E2:E25" si="0">C2-D2</f>
         <v>-5230293.6999999955</v>
       </c>
-      <c r="F2" s="54">
+      <c r="F2" s="48">
         <f>C2+69000*30</f>
         <v>50226918.740000002</v>
       </c>
-      <c r="G2" s="54">
+      <c r="G2" s="48">
         <f>D2+69000*30</f>
         <v>55457212.439999998</v>
       </c>
-      <c r="H2" s="56">
+      <c r="H2" s="50">
         <f t="shared" ref="H2:H25" si="1">F2-G2</f>
         <v>-5230293.6999999955</v>
       </c>
-      <c r="I2" s="60"/>
-      <c r="J2" s="79">
+      <c r="I2" s="54"/>
+      <c r="J2" s="70">
         <f>H2</f>
         <v>-5230293.6999999955</v>
       </c>
-      <c r="K2" s="20"/>
-      <c r="L2" s="24">
+      <c r="K2" s="14"/>
+      <c r="L2" s="18">
         <v>0</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="42">
+      <c r="C3" s="36">
         <v>59525244</v>
       </c>
-      <c r="D3" s="42">
+      <c r="D3" s="36">
         <v>58080033</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="9">
         <f t="shared" si="0"/>
         <v>1445211</v>
       </c>
-      <c r="F3" s="55">
+      <c r="F3" s="49">
         <v>65435040</v>
       </c>
-      <c r="G3" s="55">
+      <c r="G3" s="49">
         <v>64131852</v>
       </c>
-      <c r="H3" s="56">
+      <c r="H3" s="50">
         <f t="shared" si="1"/>
         <v>1303188</v>
       </c>
-      <c r="I3" s="61">
+      <c r="I3" s="55">
         <f>H3/2</f>
         <v>651594</v>
       </c>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="44"/>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="38"/>
+    </row>
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="38">
+      <c r="C4" s="32">
         <v>19331059</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="32">
         <v>19955779.719999999</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="9">
         <f t="shared" si="0"/>
         <v>-624720.71999999881</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="50">
         <v>21050207.140000001</v>
       </c>
-      <c r="G4" s="56">
+      <c r="G4" s="50">
         <v>21674927.719999999</v>
       </c>
-      <c r="H4" s="56">
+      <c r="H4" s="50">
         <f t="shared" si="1"/>
         <v>-624720.57999999821</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="24">
+      <c r="I4" s="16"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="18">
         <v>0.05</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="51" t="s">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="38">
-        <v>30874919.829999998</v>
-      </c>
-      <c r="D5" s="38">
-        <v>35244059.479999997</v>
-      </c>
-      <c r="E5" s="14">
-        <f t="shared" si="0"/>
-        <v>-4369139.6499999985</v>
-      </c>
-      <c r="F5" s="56">
-        <v>33962411.810000002</v>
-      </c>
-      <c r="G5" s="56">
-        <v>38367858</v>
-      </c>
-      <c r="H5" s="56">
-        <f t="shared" si="1"/>
-        <v>-4405446.1899999976</v>
-      </c>
-      <c r="I5" s="61"/>
-      <c r="J5" s="21">
+      <c r="C5" s="93">
+        <v>32037558.562449805</v>
+      </c>
+      <c r="D5" s="93">
+        <v>35280366.018542625</v>
+      </c>
+      <c r="E5" s="9">
+        <f t="shared" si="0"/>
+        <v>-3242807.4560928196</v>
+      </c>
+      <c r="F5" s="50">
+        <v>35241314.420000002</v>
+      </c>
+      <c r="G5" s="50">
+        <v>38484121.869999997</v>
+      </c>
+      <c r="H5" s="50">
+        <f t="shared" si="1"/>
+        <v>-3242807.4499999955</v>
+      </c>
+      <c r="I5" s="55"/>
+      <c r="J5" s="15">
         <f>F5*1.02-G5</f>
-        <v>-3726197.9538000003</v>
-      </c>
-      <c r="K5" s="53">
+        <v>-2537981.1615999937</v>
+      </c>
+      <c r="K5" s="47">
         <f>E5-J5</f>
-        <v>-642941.69619999826</v>
-      </c>
-      <c r="L5" s="24">
+        <v>-704826.29449282587</v>
+      </c>
+      <c r="L5" s="18">
         <v>0.02</v>
       </c>
-      <c r="M5" s="18" t="s">
+      <c r="M5" s="12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="32">
         <v>150327077.33000001</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="32">
         <v>150520956.53</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="9">
         <f t="shared" si="0"/>
         <v>-193879.19999998808</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="50">
         <f>C6+12000000</f>
         <v>162327077.33000001</v>
       </c>
-      <c r="G6" s="56">
+      <c r="G6" s="50">
         <f>D6+12000000</f>
         <v>162520956.53</v>
       </c>
-      <c r="H6" s="56">
+      <c r="H6" s="50">
         <f t="shared" si="1"/>
         <v>-193879.19999998808</v>
       </c>
-      <c r="I6" s="22"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="24">
+      <c r="I6" s="16"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="18">
         <v>0</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="32">
         <v>39854406</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="32">
         <v>40338984</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="9">
         <f t="shared" si="0"/>
         <v>-484578</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="50">
         <v>46829325</v>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="50">
         <v>47401429</v>
       </c>
-      <c r="H7" s="56">
+      <c r="H7" s="50">
         <f t="shared" si="1"/>
         <v>-572104</v>
       </c>
-      <c r="I7" s="22"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="24">
+      <c r="I7" s="16"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="18">
         <v>0.05</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="32">
         <v>62491370</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="32">
         <v>63861618</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="9">
         <f t="shared" si="0"/>
         <v>-1370248</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="50">
         <v>72470092</v>
       </c>
-      <c r="G8" s="56">
+      <c r="G8" s="50">
         <v>73487464</v>
       </c>
-      <c r="H8" s="56">
+      <c r="H8" s="50">
         <f t="shared" si="1"/>
         <v>-1017372</v>
       </c>
-      <c r="I8" s="22"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="24">
+      <c r="I8" s="16"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="18">
         <v>0.05</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="47" t="s">
+    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="32">
         <v>45889672</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="32">
         <v>51065876</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="9">
         <f t="shared" si="0"/>
         <v>-5176204</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="50">
         <v>53560258</v>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="50">
         <v>58251311</v>
       </c>
-      <c r="H9" s="56">
+      <c r="H9" s="50">
         <f t="shared" si="1"/>
         <v>-4691053</v>
       </c>
-      <c r="I9" s="22"/>
-      <c r="J9" s="21">
+      <c r="I9" s="16"/>
+      <c r="J9" s="15">
         <f>F9*1.05-G9</f>
         <v>-2013040.099999994</v>
       </c>
-      <c r="K9" s="58">
+      <c r="K9" s="52">
         <f>H9-J9</f>
         <v>-2678012.900000006</v>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="18">
         <v>0.05</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47" t="s">
+    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="32">
         <v>8442659</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="32">
         <v>7398017</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="9">
         <f t="shared" si="0"/>
         <v>1044642</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="50">
         <v>9547400</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G10" s="50">
         <v>8565310</v>
       </c>
-      <c r="H10" s="56">
+      <c r="H10" s="50">
         <f t="shared" si="1"/>
         <v>982090</v>
       </c>
-      <c r="I10" s="61">
+      <c r="I10" s="55">
         <f>H10/2</f>
         <v>491045</v>
       </c>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="24">
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="18">
         <v>0.05</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
+    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="32">
         <v>100802866</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="32">
         <v>122850415</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="9">
         <f t="shared" si="0"/>
         <v>-22047549</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="50">
         <v>119092682</v>
       </c>
-      <c r="G11" s="56">
+      <c r="G11" s="50">
         <v>141675593</v>
       </c>
-      <c r="H11" s="56">
+      <c r="H11" s="50">
         <f t="shared" si="1"/>
         <v>-22582911</v>
       </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="21">
+      <c r="I11" s="16"/>
+      <c r="J11" s="15">
         <f>F11*1.05-G11</f>
         <v>-16628276.899999991</v>
       </c>
-      <c r="K11" s="58">
+      <c r="K11" s="52">
         <f>H11-J11</f>
         <v>-5954634.1000000089</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="18">
         <v>0.05</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="47" t="s">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="32">
         <v>129823938</v>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="32">
         <v>122195945</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="9">
         <f t="shared" si="0"/>
         <v>7627993</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="50">
         <v>146118995</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="50">
         <v>138624131</v>
       </c>
-      <c r="H12" s="56">
+      <c r="H12" s="50">
         <f t="shared" si="1"/>
         <v>7494864</v>
       </c>
-      <c r="I12" s="61">
+      <c r="I12" s="55">
         <f>H12/2</f>
         <v>3747432</v>
       </c>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="24">
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="18">
         <v>0.05</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47" t="s">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="32">
         <v>75712669</v>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="32">
         <v>73410513</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="9">
         <f t="shared" si="0"/>
         <v>2302156</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="50">
         <v>87931471</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G13" s="50">
         <v>86021054</v>
       </c>
-      <c r="H13" s="56">
+      <c r="H13" s="50">
         <f t="shared" si="1"/>
         <v>1910417</v>
       </c>
-      <c r="I13" s="61">
+      <c r="I13" s="55">
         <f>H13/2</f>
         <v>955208.5</v>
       </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="24">
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="18">
         <v>0.05</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="32">
         <v>24795027</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="32">
         <v>26487463</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="9">
         <f t="shared" si="0"/>
         <v>-1692436</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="50">
         <v>28475524</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G14" s="50">
         <v>30400424</v>
       </c>
-      <c r="H14" s="56">
+      <c r="H14" s="50">
         <f t="shared" si="1"/>
         <v>-1924900</v>
       </c>
-      <c r="I14" s="61"/>
-      <c r="J14" s="21">
+      <c r="I14" s="55"/>
+      <c r="J14" s="15">
         <f>F14*1.05-G14</f>
         <v>-501123.79999999702</v>
       </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="24">
+      <c r="K14" s="15"/>
+      <c r="L14" s="18">
         <v>0.05</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="47" t="s">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="32">
         <v>36372271</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="32">
         <v>32419520</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="9">
         <f t="shared" si="0"/>
         <v>3952751</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="50">
         <v>40149969</v>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="50">
         <v>36213024</v>
       </c>
-      <c r="H15" s="56">
+      <c r="H15" s="50">
         <f t="shared" si="1"/>
         <v>3936945</v>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="55">
         <f t="shared" ref="I15:I21" si="2">H15/2</f>
         <v>1968472.5</v>
       </c>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="24">
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="18">
         <v>0.05</v>
       </c>
-      <c r="M15" s="12" t="s">
+      <c r="M15" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="47" t="s">
+    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="32">
         <v>1365707</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="32">
         <v>1250665</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="9">
         <f t="shared" si="0"/>
         <v>115042</v>
       </c>
-      <c r="F16" s="56">
+      <c r="F16" s="50">
         <v>1790524</v>
       </c>
-      <c r="G16" s="56">
+      <c r="G16" s="50">
         <v>1654734</v>
       </c>
-      <c r="H16" s="56">
+      <c r="H16" s="50">
         <f t="shared" si="1"/>
         <v>135790</v>
       </c>
-      <c r="I16" s="61">
+      <c r="I16" s="55">
         <f t="shared" si="2"/>
         <v>67895</v>
       </c>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="24">
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="18">
         <v>0.05</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="47" t="s">
+    <row r="17" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="32">
         <v>82688581</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="32">
         <v>80937877</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="9">
         <f t="shared" si="0"/>
         <v>1750704</v>
       </c>
-      <c r="F17" s="56">
+      <c r="F17" s="50">
         <v>93683893</v>
       </c>
-      <c r="G17" s="56">
+      <c r="G17" s="50">
         <v>92050528</v>
       </c>
-      <c r="H17" s="56">
+      <c r="H17" s="50">
         <f t="shared" si="1"/>
         <v>1633365</v>
       </c>
-      <c r="I17" s="61">
+      <c r="I17" s="55">
         <f t="shared" si="2"/>
         <v>816682.5</v>
       </c>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="24">
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="18">
         <v>0.05</v>
       </c>
-      <c r="M17" s="12" t="s">
+      <c r="M17" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
+    <row r="18" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="38">
+      <c r="C18" s="32">
         <v>61763786</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="32">
         <v>60160767</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="9">
         <f t="shared" si="0"/>
         <v>1603019</v>
       </c>
-      <c r="F18" s="56">
+      <c r="F18" s="50">
         <v>72678266</v>
       </c>
-      <c r="G18" s="56">
+      <c r="G18" s="50">
         <v>71428986</v>
       </c>
-      <c r="H18" s="56">
+      <c r="H18" s="50">
         <f t="shared" si="1"/>
         <v>1249280</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="16">
         <f t="shared" si="2"/>
         <v>624640</v>
       </c>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="24">
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="18">
         <v>0.05</v>
       </c>
-      <c r="M18" s="12" t="s">
+      <c r="M18" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
+    <row r="19" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="32">
         <v>33840813</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="32">
         <v>33391850</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="9">
         <f t="shared" si="0"/>
         <v>448963</v>
       </c>
-      <c r="F19" s="56">
+      <c r="F19" s="50">
         <v>38072977</v>
       </c>
-      <c r="G19" s="56">
+      <c r="G19" s="50">
         <v>38037592</v>
       </c>
-      <c r="H19" s="56">
+      <c r="H19" s="50">
         <f t="shared" si="1"/>
         <v>35385</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="16">
         <f t="shared" si="2"/>
         <v>17692.5</v>
       </c>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="24">
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="18">
         <v>0.05</v>
       </c>
-      <c r="M19" s="12" t="s">
+      <c r="M19" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
+    <row r="20" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="32">
         <v>1946684</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="32">
         <v>1853035</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="9">
         <f t="shared" si="0"/>
         <v>93649</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="50">
         <v>2352968</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="50">
         <v>2285300</v>
       </c>
-      <c r="H20" s="56">
+      <c r="H20" s="50">
         <f t="shared" si="1"/>
         <v>67668</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="16">
         <f t="shared" si="2"/>
         <v>33834</v>
       </c>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="24">
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="18">
         <v>0.05</v>
       </c>
-      <c r="M20" s="12" t="s">
+      <c r="M20" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="48" t="s">
+    <row r="21" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="39">
+      <c r="C21" s="33">
         <v>14696272</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="33">
         <v>14610275</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="11">
         <f t="shared" si="0"/>
         <v>85997</v>
       </c>
-      <c r="F21" s="57">
+      <c r="F21" s="51">
         <v>19083934</v>
       </c>
-      <c r="G21" s="57">
+      <c r="G21" s="51">
         <v>18860352</v>
       </c>
-      <c r="H21" s="57">
+      <c r="H21" s="51">
         <f t="shared" si="1"/>
         <v>223582</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="17">
         <f t="shared" si="2"/>
         <v>111791</v>
       </c>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="24">
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="18">
         <v>0.05</v>
       </c>
-      <c r="M21" s="12" t="s">
+      <c r="M21" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="63" t="s">
+    <row r="22" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="65">
+      <c r="C22" s="59">
         <v>23961874</v>
       </c>
-      <c r="D22" s="65">
+      <c r="D22" s="59">
         <v>22426604.09</v>
       </c>
-      <c r="E22" s="64">
+      <c r="E22" s="58">
         <f t="shared" si="0"/>
         <v>1535269.9100000001</v>
       </c>
-      <c r="F22" s="64">
+      <c r="F22" s="58">
         <f>C22+1804851</f>
         <v>25766725</v>
       </c>
-      <c r="G22" s="64">
+      <c r="G22" s="58">
         <f>D22+1804851</f>
         <v>24231455.09</v>
       </c>
-      <c r="H22" s="57">
+      <c r="H22" s="51">
         <f t="shared" si="1"/>
         <v>1535269.9100000001</v>
       </c>
-      <c r="I22" s="66">
+      <c r="I22" s="60">
         <f>H22*0.4</f>
         <v>614107.96400000004</v>
       </c>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="67"/>
-      <c r="M22" s="68" t="s">
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="62" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="63" t="s">
+    <row r="23" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="65">
+      <c r="C23" s="59">
         <v>109238942</v>
       </c>
-      <c r="D23" s="65">
+      <c r="D23" s="59">
         <v>109001590</v>
       </c>
-      <c r="E23" s="64">
+      <c r="E23" s="58">
         <f t="shared" si="0"/>
         <v>237352</v>
       </c>
-      <c r="F23" s="64">
+      <c r="F23" s="58">
         <v>121776982</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G23" s="58">
         <v>121716005</v>
       </c>
-      <c r="H23" s="64">
+      <c r="H23" s="58">
         <f t="shared" si="1"/>
         <v>60977</v>
       </c>
-      <c r="I23" s="66">
+      <c r="I23" s="60">
         <f>H23/2</f>
         <v>30488.5</v>
       </c>
-      <c r="J23" s="21"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="24">
+      <c r="J23" s="15"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="18">
         <v>0.05</v>
       </c>
-      <c r="M23" s="68"/>
-    </row>
-    <row r="24" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="63" t="s">
+      <c r="M23" s="62"/>
+    </row>
+    <row r="24" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="65">
+      <c r="C24" s="59">
         <v>52846811</v>
       </c>
-      <c r="D24" s="65">
+      <c r="D24" s="59">
         <v>51158048</v>
       </c>
-      <c r="E24" s="64">
+      <c r="E24" s="58">
         <f t="shared" si="0"/>
         <v>1688763</v>
       </c>
-      <c r="F24" s="64">
+      <c r="F24" s="58">
         <f>C24+4392755</f>
         <v>57239566</v>
       </c>
-      <c r="G24" s="64">
+      <c r="G24" s="58">
         <f>D24+4392755</f>
         <v>55550803</v>
       </c>
-      <c r="H24" s="64">
+      <c r="H24" s="58">
         <f t="shared" si="1"/>
         <v>1688763</v>
       </c>
-      <c r="I24" s="66">
+      <c r="I24" s="60">
         <f>H24*0.4</f>
         <v>675505.20000000007</v>
       </c>
-      <c r="J24" s="21"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="67">
+      <c r="J24" s="15"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="61">
         <v>0.04</v>
       </c>
-      <c r="M24" s="68" t="s">
+      <c r="M24" s="62" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="63" t="s">
+    <row r="25" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="65">
+      <c r="C25" s="59">
         <v>22244837</v>
       </c>
-      <c r="D25" s="69">
+      <c r="D25" s="63">
         <v>22328076</v>
       </c>
-      <c r="E25" s="64">
+      <c r="E25" s="58">
         <f t="shared" si="0"/>
         <v>-83239</v>
       </c>
-      <c r="F25" s="70">
+      <c r="F25" s="64">
         <f>C25+1908100</f>
         <v>24152937</v>
       </c>
-      <c r="G25" s="70">
+      <c r="G25" s="64">
         <f>D25+1908100</f>
         <v>24236176</v>
       </c>
-      <c r="H25" s="64">
+      <c r="H25" s="58">
         <f t="shared" si="1"/>
         <v>-83239</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="59"/>
-    </row>
-    <row r="29" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="53"/>
+    </row>
+    <row r="29" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J29">
         <f>K15</f>
         <v>0</v>
